--- a/プロジェクト型演習_成果物_TasBo_ログイン.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_ログイン.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER111\Desktop\新しいフォルダー (2)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER110\Desktop\プロジェクト演習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{861D069F-BFDE-4833-9E6A-9BD54ED653F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68AED1EF-2936-4620-A850-C7929BFDE03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙 " sheetId="11" r:id="rId1"/>
@@ -1980,407 +1980,407 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="58" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="59" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="60" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="60" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="14" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="60" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="58" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="59" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="60" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2440,20 +2440,20 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>21021</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1028700</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>55608</xdr:rowOff>
+      <xdr:colOff>952500</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>95251</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71A901B1-CF93-D7E1-9E2F-DBA46C305BBE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F74218C-648A-3DE0-9B17-2DC2B2AAFD14}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2469,8 +2469,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="1097346"/>
-          <a:ext cx="8743950" cy="3920787"/>
+          <a:off x="0" y="1076326"/>
+          <a:ext cx="8667750" cy="4305300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3352,85 +3352,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1" thickBot="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1" thickTop="1">
-      <c r="C2" s="106" t="s">
+      <c r="C2" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="107"/>
-      <c r="J2" s="107"/>
-      <c r="K2" s="107"/>
-      <c r="L2" s="107"/>
-      <c r="M2" s="107"/>
-      <c r="N2" s="107"/>
-      <c r="O2" s="107"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
+      <c r="O2" s="114"/>
       <c r="P2" s="66"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="105"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="105"/>
-      <c r="I3" s="105"/>
-      <c r="J3" s="105"/>
-      <c r="K3" s="105"/>
-      <c r="L3" s="105"/>
-      <c r="M3" s="105"/>
-      <c r="N3" s="105"/>
-      <c r="O3" s="105"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="83"/>
+      <c r="O3" s="83"/>
       <c r="P3" s="66"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="105"/>
-      <c r="K4" s="105"/>
-      <c r="L4" s="105"/>
-      <c r="M4" s="105"/>
-      <c r="N4" s="105"/>
-      <c r="O4" s="105"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="83"/>
+      <c r="K4" s="83"/>
+      <c r="L4" s="83"/>
+      <c r="M4" s="83"/>
+      <c r="N4" s="83"/>
+      <c r="O4" s="83"/>
       <c r="P4" s="66"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="105"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="105"/>
-      <c r="H5" s="105"/>
-      <c r="I5" s="105"/>
-      <c r="J5" s="105"/>
-      <c r="K5" s="105"/>
-      <c r="L5" s="105"/>
-      <c r="M5" s="105"/>
-      <c r="N5" s="105"/>
-      <c r="O5" s="105"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="83"/>
+      <c r="K5" s="83"/>
+      <c r="L5" s="83"/>
+      <c r="M5" s="83"/>
+      <c r="N5" s="83"/>
+      <c r="O5" s="83"/>
       <c r="P5" s="66"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1" thickBot="1">
-      <c r="C6" s="105"/>
-      <c r="D6" s="105"/>
-      <c r="E6" s="105"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="105"/>
-      <c r="H6" s="105"/>
-      <c r="I6" s="105"/>
-      <c r="J6" s="105"/>
-      <c r="K6" s="105"/>
-      <c r="L6" s="105"/>
-      <c r="M6" s="105"/>
-      <c r="N6" s="105"/>
-      <c r="O6" s="105"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="83"/>
+      <c r="L6" s="83"/>
+      <c r="M6" s="83"/>
+      <c r="N6" s="83"/>
+      <c r="O6" s="83"/>
       <c r="P6" s="66"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1" thickTop="1">
@@ -3450,46 +3450,46 @@
       <c r="P7" s="66"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="108" t="s">
+      <c r="E8" s="115" t="s">
         <v>105</v>
       </c>
-      <c r="F8" s="105"/>
-      <c r="G8" s="105"/>
-      <c r="H8" s="105"/>
-      <c r="I8" s="105"/>
-      <c r="J8" s="105"/>
-      <c r="K8" s="105"/>
-      <c r="L8" s="105"/>
-      <c r="M8" s="105"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="83"/>
+      <c r="L8" s="83"/>
+      <c r="M8" s="83"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="101" t="s">
+      <c r="G13" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="103"/>
-      <c r="I13" s="109">
+      <c r="H13" s="74"/>
+      <c r="I13" s="116">
         <v>46175</v>
       </c>
-      <c r="J13" s="102"/>
-      <c r="K13" s="103"/>
+      <c r="J13" s="76"/>
+      <c r="K13" s="74"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="101"/>
-      <c r="H14" s="103"/>
-      <c r="I14" s="101"/>
-      <c r="J14" s="102"/>
-      <c r="K14" s="103"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="76"/>
+      <c r="K14" s="74"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="101"/>
-      <c r="H15" s="103"/>
-      <c r="I15" s="101"/>
-      <c r="J15" s="102"/>
-      <c r="K15" s="103"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="74"/>
+      <c r="I15" s="111"/>
+      <c r="J15" s="76"/>
+      <c r="K15" s="74"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="65"/>
@@ -3498,13 +3498,13 @@
       <c r="J16" s="65"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="104" t="s">
+      <c r="G17" s="112" t="s">
         <v>104</v>
       </c>
-      <c r="H17" s="105"/>
-      <c r="I17" s="105"/>
-      <c r="J17" s="105"/>
-      <c r="K17" s="105"/>
+      <c r="H17" s="83"/>
+      <c r="I17" s="83"/>
+      <c r="J17" s="83"/>
+      <c r="K17" s="83"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4519,19 +4519,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="139" t="s">
+      <c r="B1" s="80"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="138"/>
-      <c r="F1" s="139" t="s">
+      <c r="E1" s="90"/>
+      <c r="F1" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="138"/>
+      <c r="G1" s="90"/>
       <c r="H1" s="69" t="s">
         <v>5</v>
       </c>
@@ -4543,192 +4543,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="132"/>
-      <c r="B2" s="105"/>
-      <c r="C2" s="133"/>
-      <c r="D2" s="140" t="s">
+      <c r="A2" s="82"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="92" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="141"/>
-      <c r="F2" s="140" t="s">
+      <c r="E2" s="93"/>
+      <c r="F2" s="92" t="s">
         <v>109</v>
       </c>
-      <c r="G2" s="141"/>
-      <c r="H2" s="144">
+      <c r="G2" s="93"/>
+      <c r="H2" s="96">
         <v>46175</v>
       </c>
-      <c r="I2" s="147" t="s">
+      <c r="I2" s="99" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="124"/>
+      <c r="J2" s="70"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="132"/>
-      <c r="B3" s="105"/>
-      <c r="C3" s="133"/>
-      <c r="D3" s="142"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="142"/>
-      <c r="G3" s="133"/>
-      <c r="H3" s="145"/>
-      <c r="I3" s="145"/>
-      <c r="J3" s="125"/>
+      <c r="A3" s="82"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="71"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="134"/>
-      <c r="B4" s="135"/>
-      <c r="C4" s="136"/>
-      <c r="D4" s="143"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="143"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="126"/>
+      <c r="A4" s="85"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="72"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="137" t="s">
+      <c r="A5" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="121"/>
-      <c r="C5" s="138"/>
-      <c r="D5" s="120" t="s">
+      <c r="B5" s="89"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="100" t="s">
         <v>107</v>
       </c>
-      <c r="E5" s="121"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
-      <c r="H5" s="121"/>
-      <c r="I5" s="121"/>
-      <c r="J5" s="122"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="101"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="112" t="s">
+      <c r="A6" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="102"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="123" t="s">
+      <c r="B6" s="76"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="102" t="s">
         <v>114</v>
       </c>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="102"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="111"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="78"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="112" t="s">
+      <c r="A7" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="102"/>
-      <c r="C7" s="103"/>
-      <c r="D7" s="123" t="s">
+      <c r="B7" s="76"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="102" t="s">
         <v>113</v>
       </c>
-      <c r="E7" s="102"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="111"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="76"/>
+      <c r="I7" s="76"/>
+      <c r="J7" s="78"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="112" t="s">
+      <c r="A8" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="102"/>
-      <c r="C8" s="103"/>
-      <c r="D8" s="110" t="s">
+      <c r="B8" s="76"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="77" t="s">
         <v>112</v>
       </c>
-      <c r="E8" s="102"/>
-      <c r="F8" s="102"/>
-      <c r="G8" s="102"/>
-      <c r="H8" s="102"/>
-      <c r="I8" s="102"/>
-      <c r="J8" s="111"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="78"/>
     </row>
     <row r="9" spans="1:10" ht="106.5" customHeight="1">
-      <c r="A9" s="113" t="s">
+      <c r="A9" s="103" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="116" t="s">
+      <c r="B9" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="103"/>
-      <c r="D9" s="110" t="s">
+      <c r="C9" s="74"/>
+      <c r="D9" s="77" t="s">
         <v>115</v>
       </c>
-      <c r="E9" s="102"/>
-      <c r="F9" s="102"/>
-      <c r="G9" s="102"/>
-      <c r="H9" s="102"/>
-      <c r="I9" s="102"/>
-      <c r="J9" s="111"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="78"/>
     </row>
     <row r="10" spans="1:10" ht="126.75" customHeight="1">
-      <c r="A10" s="114"/>
-      <c r="B10" s="116" t="s">
+      <c r="A10" s="104"/>
+      <c r="B10" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="103"/>
-      <c r="D10" s="110" t="s">
+      <c r="C10" s="74"/>
+      <c r="D10" s="77" t="s">
         <v>116</v>
       </c>
-      <c r="E10" s="102"/>
-      <c r="F10" s="102"/>
-      <c r="G10" s="102"/>
-      <c r="H10" s="102"/>
-      <c r="I10" s="102"/>
-      <c r="J10" s="111"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
+      <c r="J10" s="78"/>
     </row>
     <row r="11" spans="1:10" ht="51.75" customHeight="1">
-      <c r="A11" s="115"/>
-      <c r="B11" s="116" t="s">
+      <c r="A11" s="105"/>
+      <c r="B11" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="103"/>
-      <c r="D11" s="110" t="s">
+      <c r="C11" s="74"/>
+      <c r="D11" s="77" t="s">
         <v>106</v>
       </c>
-      <c r="E11" s="102"/>
-      <c r="F11" s="102"/>
-      <c r="G11" s="102"/>
-      <c r="H11" s="102"/>
-      <c r="I11" s="102"/>
-      <c r="J11" s="111"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76"/>
+      <c r="J11" s="78"/>
     </row>
     <row r="12" spans="1:10" ht="48.75" customHeight="1">
-      <c r="A12" s="112" t="s">
+      <c r="A12" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="102"/>
-      <c r="C12" s="103"/>
-      <c r="D12" s="110" t="s">
+      <c r="B12" s="76"/>
+      <c r="C12" s="74"/>
+      <c r="D12" s="77" t="s">
         <v>111</v>
       </c>
-      <c r="E12" s="102"/>
-      <c r="F12" s="102"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="102"/>
-      <c r="I12" s="102"/>
-      <c r="J12" s="111"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76"/>
+      <c r="J12" s="78"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="127" t="s">
+      <c r="A13" s="109" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="118"/>
-      <c r="C13" s="128"/>
-      <c r="D13" s="117"/>
-      <c r="E13" s="118"/>
-      <c r="F13" s="118"/>
-      <c r="G13" s="118"/>
-      <c r="H13" s="118"/>
-      <c r="I13" s="118"/>
-      <c r="J13" s="119"/>
+      <c r="B13" s="107"/>
+      <c r="C13" s="110"/>
+      <c r="D13" s="106"/>
+      <c r="E13" s="107"/>
+      <c r="F13" s="107"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="107"/>
+      <c r="I13" s="107"/>
+      <c r="J13" s="108"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5719,6 +5719,17 @@
     <row r="1000" s="64" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
@@ -5735,17 +5746,6 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="A13:C13"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5764,19 +5764,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="154" t="s">
+      <c r="A1" s="123" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="163" t="s">
+      <c r="B1" s="124"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="164"/>
-      <c r="F1" s="163" t="s">
+      <c r="E1" s="133"/>
+      <c r="F1" s="132" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="164"/>
+      <c r="G1" s="133"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -5788,40 +5788,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="157"/>
-      <c r="B2" s="158"/>
-      <c r="C2" s="159"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="166"/>
-      <c r="F2" s="165"/>
-      <c r="G2" s="166"/>
-      <c r="H2" s="148"/>
-      <c r="I2" s="148"/>
-      <c r="J2" s="151"/>
+      <c r="A2" s="126"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="120"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="157"/>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="167"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="167"/>
-      <c r="G3" s="159"/>
-      <c r="H3" s="149"/>
-      <c r="I3" s="149"/>
-      <c r="J3" s="152"/>
+      <c r="A3" s="126"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="118"/>
+      <c r="I3" s="118"/>
+      <c r="J3" s="121"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="160"/>
-      <c r="B4" s="161"/>
-      <c r="C4" s="162"/>
-      <c r="D4" s="168"/>
-      <c r="E4" s="162"/>
-      <c r="F4" s="168"/>
-      <c r="G4" s="162"/>
-      <c r="H4" s="150"/>
-      <c r="I4" s="150"/>
-      <c r="J4" s="153"/>
+      <c r="A4" s="129"/>
+      <c r="B4" s="130"/>
+      <c r="C4" s="131"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="131"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="131"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="122"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="5"/>
@@ -7177,19 +7177,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="154" t="s">
+      <c r="A1" s="123" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="163" t="s">
+      <c r="B1" s="124"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="164"/>
-      <c r="F1" s="163" t="s">
+      <c r="E1" s="133"/>
+      <c r="F1" s="132" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="164"/>
+      <c r="G1" s="133"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -7201,48 +7201,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="157"/>
-      <c r="B2" s="158"/>
-      <c r="C2" s="159"/>
-      <c r="D2" s="165" t="s">
+      <c r="A2" s="126"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="166"/>
-      <c r="F2" s="165" t="s">
+      <c r="E2" s="135"/>
+      <c r="F2" s="134" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="166"/>
-      <c r="H2" s="169">
+      <c r="G2" s="135"/>
+      <c r="H2" s="138">
         <v>46182</v>
       </c>
-      <c r="I2" s="148" t="s">
+      <c r="I2" s="117" t="s">
         <v>52</v>
       </c>
-      <c r="J2" s="151"/>
+      <c r="J2" s="120"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="157"/>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="167"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="167"/>
-      <c r="G3" s="159"/>
-      <c r="H3" s="149"/>
-      <c r="I3" s="149"/>
-      <c r="J3" s="152"/>
+      <c r="A3" s="126"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="118"/>
+      <c r="I3" s="118"/>
+      <c r="J3" s="121"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="160"/>
-      <c r="B4" s="161"/>
-      <c r="C4" s="162"/>
-      <c r="D4" s="168"/>
-      <c r="E4" s="162"/>
-      <c r="F4" s="168"/>
-      <c r="G4" s="162"/>
-      <c r="H4" s="150"/>
-      <c r="I4" s="150"/>
-      <c r="J4" s="153"/>
+      <c r="A4" s="129"/>
+      <c r="B4" s="130"/>
+      <c r="C4" s="131"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="131"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="131"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="122"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="5"/>
@@ -8593,19 +8593,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="154" t="s">
+      <c r="A1" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="163" t="s">
+      <c r="B1" s="124"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="164"/>
-      <c r="F1" s="163" t="s">
+      <c r="E1" s="133"/>
+      <c r="F1" s="132" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="164"/>
+      <c r="G1" s="133"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -8617,192 +8617,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="157"/>
-      <c r="B2" s="158"/>
-      <c r="C2" s="159"/>
-      <c r="D2" s="165" t="s">
+      <c r="A2" s="126"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="134" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="166"/>
-      <c r="F2" s="165" t="s">
+      <c r="E2" s="135"/>
+      <c r="F2" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="G2" s="166"/>
-      <c r="H2" s="190">
+      <c r="G2" s="135"/>
+      <c r="H2" s="139">
         <v>46175</v>
       </c>
-      <c r="I2" s="148" t="s">
+      <c r="I2" s="117" t="s">
         <v>52</v>
       </c>
-      <c r="J2" s="151"/>
+      <c r="J2" s="120"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="157"/>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="167"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="167"/>
-      <c r="G3" s="159"/>
-      <c r="H3" s="149"/>
-      <c r="I3" s="149"/>
-      <c r="J3" s="152"/>
+      <c r="A3" s="126"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="118"/>
+      <c r="I3" s="118"/>
+      <c r="J3" s="121"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="157"/>
-      <c r="B4" s="158"/>
-      <c r="C4" s="159"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="159"/>
-      <c r="F4" s="167"/>
-      <c r="G4" s="159"/>
-      <c r="H4" s="149"/>
-      <c r="I4" s="149"/>
-      <c r="J4" s="152"/>
+      <c r="A4" s="126"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="128"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="128"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="121"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="178" t="s">
+      <c r="A5" s="140" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="179"/>
-      <c r="C5" s="164"/>
-      <c r="D5" s="183" t="s">
+      <c r="B5" s="141"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="149" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="179"/>
-      <c r="F5" s="179"/>
-      <c r="G5" s="179"/>
-      <c r="H5" s="179"/>
-      <c r="I5" s="179"/>
-      <c r="J5" s="184"/>
+      <c r="E5" s="141"/>
+      <c r="F5" s="141"/>
+      <c r="G5" s="141"/>
+      <c r="H5" s="141"/>
+      <c r="I5" s="141"/>
+      <c r="J5" s="150"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="182" t="s">
+      <c r="A6" s="145" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="174"/>
-      <c r="C6" s="174"/>
-      <c r="D6" s="174"/>
-      <c r="E6" s="174"/>
-      <c r="F6" s="174"/>
-      <c r="G6" s="174"/>
-      <c r="H6" s="174"/>
-      <c r="I6" s="174"/>
-      <c r="J6" s="177"/>
+      <c r="B6" s="146"/>
+      <c r="C6" s="146"/>
+      <c r="D6" s="146"/>
+      <c r="E6" s="146"/>
+      <c r="F6" s="146"/>
+      <c r="G6" s="146"/>
+      <c r="H6" s="146"/>
+      <c r="I6" s="146"/>
+      <c r="J6" s="151"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="185" t="e" vm="1">
+      <c r="A7" s="152" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B7" s="186"/>
-      <c r="C7" s="186"/>
-      <c r="D7" s="186"/>
-      <c r="E7" s="186"/>
-      <c r="F7" s="186"/>
-      <c r="G7" s="186"/>
-      <c r="H7" s="186"/>
-      <c r="I7" s="186"/>
-      <c r="J7" s="187"/>
+      <c r="B7" s="153"/>
+      <c r="C7" s="153"/>
+      <c r="D7" s="153"/>
+      <c r="E7" s="153"/>
+      <c r="F7" s="153"/>
+      <c r="G7" s="153"/>
+      <c r="H7" s="153"/>
+      <c r="I7" s="153"/>
+      <c r="J7" s="154"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="157"/>
-      <c r="B8" s="158"/>
-      <c r="C8" s="158"/>
-      <c r="D8" s="158"/>
-      <c r="E8" s="158"/>
-      <c r="F8" s="158"/>
-      <c r="G8" s="158"/>
-      <c r="H8" s="158"/>
-      <c r="I8" s="158"/>
-      <c r="J8" s="188"/>
+      <c r="A8" s="126"/>
+      <c r="B8" s="127"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+      <c r="F8" s="127"/>
+      <c r="G8" s="127"/>
+      <c r="H8" s="127"/>
+      <c r="I8" s="127"/>
+      <c r="J8" s="155"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="157"/>
-      <c r="B9" s="158"/>
-      <c r="C9" s="158"/>
-      <c r="D9" s="158"/>
-      <c r="E9" s="158"/>
-      <c r="F9" s="158"/>
-      <c r="G9" s="158"/>
-      <c r="H9" s="158"/>
-      <c r="I9" s="158"/>
-      <c r="J9" s="188"/>
+      <c r="A9" s="126"/>
+      <c r="B9" s="127"/>
+      <c r="C9" s="127"/>
+      <c r="D9" s="127"/>
+      <c r="E9" s="127"/>
+      <c r="F9" s="127"/>
+      <c r="G9" s="127"/>
+      <c r="H9" s="127"/>
+      <c r="I9" s="127"/>
+      <c r="J9" s="155"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="157"/>
-      <c r="B10" s="158"/>
-      <c r="C10" s="158"/>
-      <c r="D10" s="158"/>
-      <c r="E10" s="158"/>
-      <c r="F10" s="158"/>
-      <c r="G10" s="158"/>
-      <c r="H10" s="158"/>
-      <c r="I10" s="158"/>
-      <c r="J10" s="188"/>
+      <c r="A10" s="126"/>
+      <c r="B10" s="127"/>
+      <c r="C10" s="127"/>
+      <c r="D10" s="127"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="127"/>
+      <c r="G10" s="127"/>
+      <c r="H10" s="127"/>
+      <c r="I10" s="127"/>
+      <c r="J10" s="155"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="157"/>
-      <c r="B11" s="158"/>
-      <c r="C11" s="158"/>
-      <c r="D11" s="158"/>
-      <c r="E11" s="158"/>
-      <c r="F11" s="158"/>
-      <c r="G11" s="158"/>
-      <c r="H11" s="158"/>
-      <c r="I11" s="158"/>
-      <c r="J11" s="188"/>
+      <c r="A11" s="126"/>
+      <c r="B11" s="127"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="127"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="127"/>
+      <c r="G11" s="127"/>
+      <c r="H11" s="127"/>
+      <c r="I11" s="127"/>
+      <c r="J11" s="155"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="157"/>
-      <c r="B12" s="158"/>
-      <c r="C12" s="158"/>
-      <c r="D12" s="158"/>
-      <c r="E12" s="158"/>
-      <c r="F12" s="158"/>
-      <c r="G12" s="158"/>
-      <c r="H12" s="158"/>
-      <c r="I12" s="158"/>
-      <c r="J12" s="188"/>
+      <c r="A12" s="126"/>
+      <c r="B12" s="127"/>
+      <c r="C12" s="127"/>
+      <c r="D12" s="127"/>
+      <c r="E12" s="127"/>
+      <c r="F12" s="127"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="155"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="157"/>
-      <c r="B13" s="158"/>
-      <c r="C13" s="158"/>
-      <c r="D13" s="158"/>
-      <c r="E13" s="158"/>
-      <c r="F13" s="158"/>
-      <c r="G13" s="158"/>
-      <c r="H13" s="158"/>
-      <c r="I13" s="158"/>
-      <c r="J13" s="188"/>
+      <c r="A13" s="126"/>
+      <c r="B13" s="127"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="127"/>
+      <c r="E13" s="127"/>
+      <c r="F13" s="127"/>
+      <c r="G13" s="127"/>
+      <c r="H13" s="127"/>
+      <c r="I13" s="127"/>
+      <c r="J13" s="155"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="182" t="s">
+      <c r="A14" s="145" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="174"/>
-      <c r="C14" s="174"/>
-      <c r="D14" s="174"/>
-      <c r="E14" s="174"/>
-      <c r="F14" s="174"/>
-      <c r="G14" s="174"/>
-      <c r="H14" s="174"/>
-      <c r="I14" s="174"/>
-      <c r="J14" s="177"/>
+      <c r="B14" s="146"/>
+      <c r="C14" s="146"/>
+      <c r="D14" s="146"/>
+      <c r="E14" s="146"/>
+      <c r="F14" s="146"/>
+      <c r="G14" s="146"/>
+      <c r="H14" s="146"/>
+      <c r="I14" s="146"/>
+      <c r="J14" s="151"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="182" t="s">
+      <c r="A15" s="145" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="174"/>
-      <c r="C15" s="175"/>
-      <c r="D15" s="176" t="s">
+      <c r="B15" s="146"/>
+      <c r="C15" s="147"/>
+      <c r="D15" s="156" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="174"/>
-      <c r="F15" s="174"/>
-      <c r="G15" s="174"/>
-      <c r="H15" s="175"/>
+      <c r="E15" s="146"/>
+      <c r="F15" s="146"/>
+      <c r="G15" s="146"/>
+      <c r="H15" s="147"/>
       <c r="I15" s="12" t="s">
         <v>25</v>
       </c>
@@ -8811,11 +8811,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="182" t="s">
+      <c r="A16" s="145" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="174"/>
-      <c r="C16" s="175"/>
+      <c r="B16" s="146"/>
+      <c r="C16" s="147"/>
       <c r="D16" s="12" t="s">
         <v>27</v>
       </c>
@@ -8828,18 +8828,18 @@
       <c r="G16" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="189" t="s">
+      <c r="H16" s="157" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="174"/>
-      <c r="J16" s="177"/>
+      <c r="I16" s="146"/>
+      <c r="J16" s="151"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="173">
+      <c r="A17" s="148">
         <v>1</v>
       </c>
-      <c r="B17" s="174"/>
-      <c r="C17" s="175"/>
+      <c r="B17" s="146"/>
+      <c r="C17" s="147"/>
       <c r="D17" s="14" t="s">
         <v>58</v>
       </c>
@@ -8850,16 +8850,16 @@
         <v>60</v>
       </c>
       <c r="G17" s="15"/>
-      <c r="H17" s="176"/>
-      <c r="I17" s="174"/>
-      <c r="J17" s="177"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="146"/>
+      <c r="J17" s="151"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="173">
+      <c r="A18" s="148">
         <v>2</v>
       </c>
-      <c r="B18" s="174"/>
-      <c r="C18" s="175"/>
+      <c r="B18" s="146"/>
+      <c r="C18" s="147"/>
       <c r="D18" s="14" t="s">
         <v>61</v>
       </c>
@@ -8870,16 +8870,16 @@
         <v>62</v>
       </c>
       <c r="G18" s="15"/>
-      <c r="H18" s="176"/>
-      <c r="I18" s="174"/>
-      <c r="J18" s="177"/>
+      <c r="H18" s="156"/>
+      <c r="I18" s="146"/>
+      <c r="J18" s="151"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="173">
+      <c r="A19" s="148">
         <v>3</v>
       </c>
-      <c r="B19" s="174"/>
-      <c r="C19" s="175"/>
+      <c r="B19" s="146"/>
+      <c r="C19" s="147"/>
       <c r="D19" s="14" t="s">
         <v>55</v>
       </c>
@@ -8890,16 +8890,16 @@
       <c r="G19" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="H19" s="176"/>
-      <c r="I19" s="174"/>
-      <c r="J19" s="177"/>
+      <c r="H19" s="156"/>
+      <c r="I19" s="146"/>
+      <c r="J19" s="151"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="173">
+      <c r="A20" s="148">
         <v>4</v>
       </c>
-      <c r="B20" s="174"/>
-      <c r="C20" s="175"/>
+      <c r="B20" s="146"/>
+      <c r="C20" s="147"/>
       <c r="D20" s="14" t="s">
         <v>64</v>
       </c>
@@ -8910,45 +8910,45 @@
       <c r="G20" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="H20" s="176"/>
-      <c r="I20" s="174"/>
-      <c r="J20" s="177"/>
+      <c r="H20" s="156"/>
+      <c r="I20" s="146"/>
+      <c r="J20" s="151"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="173"/>
-      <c r="B21" s="174"/>
-      <c r="C21" s="175"/>
+      <c r="A21" s="148"/>
+      <c r="B21" s="146"/>
+      <c r="C21" s="147"/>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
-      <c r="H21" s="176"/>
-      <c r="I21" s="174"/>
-      <c r="J21" s="177"/>
+      <c r="H21" s="156"/>
+      <c r="I21" s="146"/>
+      <c r="J21" s="151"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="173"/>
-      <c r="B22" s="174"/>
-      <c r="C22" s="175"/>
+      <c r="A22" s="148"/>
+      <c r="B22" s="146"/>
+      <c r="C22" s="147"/>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
-      <c r="H22" s="176"/>
-      <c r="I22" s="174"/>
-      <c r="J22" s="177"/>
+      <c r="H22" s="156"/>
+      <c r="I22" s="146"/>
+      <c r="J22" s="151"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="180"/>
-      <c r="B23" s="171"/>
-      <c r="C23" s="181"/>
+      <c r="A23" s="142"/>
+      <c r="B23" s="143"/>
+      <c r="C23" s="144"/>
       <c r="D23" s="16"/>
       <c r="E23" s="16"/>
       <c r="F23" s="17"/>
       <c r="G23" s="17"/>
-      <c r="H23" s="170"/>
-      <c r="I23" s="171"/>
-      <c r="J23" s="172"/>
+      <c r="H23" s="158"/>
+      <c r="I23" s="143"/>
+      <c r="J23" s="159"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9929,11 +9929,16 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -9950,16 +9955,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9979,184 +9979,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="166" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="163" t="s">
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="179"/>
-      <c r="I1" s="179"/>
-      <c r="J1" s="164"/>
-      <c r="K1" s="163" t="s">
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="132" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="179"/>
-      <c r="M1" s="179"/>
-      <c r="N1" s="164"/>
-      <c r="O1" s="163" t="s">
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="133"/>
+      <c r="O1" s="132" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="164"/>
-      <c r="Q1" s="163" t="s">
+      <c r="P1" s="133"/>
+      <c r="Q1" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="164"/>
-      <c r="S1" s="163" t="s">
+      <c r="R1" s="133"/>
+      <c r="S1" s="132" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="184"/>
+      <c r="T1" s="150"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="157"/>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="165" t="s">
+      <c r="A2" s="126"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="186"/>
-      <c r="I2" s="186"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="165" t="s">
+      <c r="H2" s="153"/>
+      <c r="I2" s="153"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="134" t="s">
         <v>66</v>
       </c>
-      <c r="L2" s="186"/>
-      <c r="M2" s="186"/>
-      <c r="N2" s="166"/>
-      <c r="O2" s="200">
+      <c r="L2" s="153"/>
+      <c r="M2" s="153"/>
+      <c r="N2" s="135"/>
+      <c r="O2" s="164">
         <v>46182</v>
       </c>
-      <c r="P2" s="166"/>
-      <c r="Q2" s="165" t="s">
+      <c r="P2" s="135"/>
+      <c r="Q2" s="134" t="s">
         <v>67</v>
       </c>
-      <c r="R2" s="166"/>
-      <c r="S2" s="165"/>
-      <c r="T2" s="187"/>
+      <c r="R2" s="135"/>
+      <c r="S2" s="134"/>
+      <c r="T2" s="154"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="157"/>
-      <c r="B3" s="158"/>
-      <c r="C3" s="158"/>
-      <c r="D3" s="158"/>
-      <c r="E3" s="158"/>
-      <c r="F3" s="159"/>
-      <c r="G3" s="167"/>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="159"/>
-      <c r="K3" s="167"/>
-      <c r="L3" s="158"/>
-      <c r="M3" s="158"/>
-      <c r="N3" s="159"/>
-      <c r="O3" s="167"/>
-      <c r="P3" s="159"/>
-      <c r="Q3" s="167"/>
-      <c r="R3" s="159"/>
-      <c r="S3" s="167"/>
-      <c r="T3" s="188"/>
+      <c r="A3" s="126"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="136"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="128"/>
+      <c r="Q3" s="136"/>
+      <c r="R3" s="128"/>
+      <c r="S3" s="136"/>
+      <c r="T3" s="155"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="160"/>
-      <c r="B4" s="161"/>
-      <c r="C4" s="161"/>
-      <c r="D4" s="161"/>
-      <c r="E4" s="161"/>
-      <c r="F4" s="162"/>
-      <c r="G4" s="168"/>
-      <c r="H4" s="161"/>
-      <c r="I4" s="161"/>
-      <c r="J4" s="162"/>
-      <c r="K4" s="168"/>
-      <c r="L4" s="161"/>
-      <c r="M4" s="161"/>
-      <c r="N4" s="162"/>
-      <c r="O4" s="168"/>
-      <c r="P4" s="162"/>
-      <c r="Q4" s="168"/>
-      <c r="R4" s="162"/>
-      <c r="S4" s="168"/>
-      <c r="T4" s="201"/>
+      <c r="A4" s="129"/>
+      <c r="B4" s="130"/>
+      <c r="C4" s="130"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="131"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="130"/>
+      <c r="I4" s="130"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="130"/>
+      <c r="M4" s="130"/>
+      <c r="N4" s="131"/>
+      <c r="O4" s="137"/>
+      <c r="P4" s="131"/>
+      <c r="Q4" s="137"/>
+      <c r="R4" s="131"/>
+      <c r="S4" s="137"/>
+      <c r="T4" s="165"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="178" t="s">
+      <c r="A5" s="140" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="179"/>
-      <c r="C5" s="179"/>
-      <c r="D5" s="179"/>
-      <c r="E5" s="179"/>
-      <c r="F5" s="164"/>
-      <c r="G5" s="197"/>
-      <c r="H5" s="179"/>
-      <c r="I5" s="179"/>
-      <c r="J5" s="179"/>
-      <c r="K5" s="179"/>
-      <c r="L5" s="179"/>
-      <c r="M5" s="179"/>
-      <c r="N5" s="179"/>
-      <c r="O5" s="179"/>
-      <c r="P5" s="179"/>
-      <c r="Q5" s="179"/>
-      <c r="R5" s="179"/>
-      <c r="S5" s="179"/>
-      <c r="T5" s="184"/>
+      <c r="B5" s="141"/>
+      <c r="C5" s="141"/>
+      <c r="D5" s="141"/>
+      <c r="E5" s="141"/>
+      <c r="F5" s="133"/>
+      <c r="G5" s="167"/>
+      <c r="H5" s="141"/>
+      <c r="I5" s="141"/>
+      <c r="J5" s="141"/>
+      <c r="K5" s="141"/>
+      <c r="L5" s="141"/>
+      <c r="M5" s="141"/>
+      <c r="N5" s="141"/>
+      <c r="O5" s="141"/>
+      <c r="P5" s="141"/>
+      <c r="Q5" s="141"/>
+      <c r="R5" s="141"/>
+      <c r="S5" s="141"/>
+      <c r="T5" s="150"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="182" t="s">
+      <c r="A6" s="145" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="174"/>
-      <c r="C6" s="174"/>
-      <c r="D6" s="174"/>
-      <c r="E6" s="174"/>
-      <c r="F6" s="175"/>
-      <c r="G6" s="176"/>
-      <c r="H6" s="174"/>
-      <c r="I6" s="174"/>
-      <c r="J6" s="174"/>
-      <c r="K6" s="174"/>
-      <c r="L6" s="174"/>
-      <c r="M6" s="174"/>
-      <c r="N6" s="174"/>
-      <c r="O6" s="174"/>
-      <c r="P6" s="174"/>
-      <c r="Q6" s="174"/>
-      <c r="R6" s="174"/>
-      <c r="S6" s="174"/>
-      <c r="T6" s="177"/>
+      <c r="B6" s="146"/>
+      <c r="C6" s="146"/>
+      <c r="D6" s="146"/>
+      <c r="E6" s="146"/>
+      <c r="F6" s="147"/>
+      <c r="G6" s="156"/>
+      <c r="H6" s="146"/>
+      <c r="I6" s="146"/>
+      <c r="J6" s="146"/>
+      <c r="K6" s="146"/>
+      <c r="L6" s="146"/>
+      <c r="M6" s="146"/>
+      <c r="N6" s="146"/>
+      <c r="O6" s="146"/>
+      <c r="P6" s="146"/>
+      <c r="Q6" s="146"/>
+      <c r="R6" s="146"/>
+      <c r="S6" s="146"/>
+      <c r="T6" s="151"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="182" t="s">
+      <c r="A7" s="145" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="174"/>
-      <c r="C7" s="174"/>
-      <c r="D7" s="174"/>
-      <c r="E7" s="174"/>
-      <c r="F7" s="175"/>
-      <c r="G7" s="176"/>
-      <c r="H7" s="174"/>
-      <c r="I7" s="174"/>
-      <c r="J7" s="174"/>
-      <c r="K7" s="174"/>
-      <c r="L7" s="174"/>
-      <c r="M7" s="174"/>
-      <c r="N7" s="174"/>
-      <c r="O7" s="174"/>
-      <c r="P7" s="174"/>
-      <c r="Q7" s="174"/>
-      <c r="R7" s="174"/>
-      <c r="S7" s="174"/>
-      <c r="T7" s="177"/>
+      <c r="B7" s="146"/>
+      <c r="C7" s="146"/>
+      <c r="D7" s="146"/>
+      <c r="E7" s="146"/>
+      <c r="F7" s="147"/>
+      <c r="G7" s="156"/>
+      <c r="H7" s="146"/>
+      <c r="I7" s="146"/>
+      <c r="J7" s="146"/>
+      <c r="K7" s="146"/>
+      <c r="L7" s="146"/>
+      <c r="M7" s="146"/>
+      <c r="N7" s="146"/>
+      <c r="O7" s="146"/>
+      <c r="P7" s="146"/>
+      <c r="Q7" s="146"/>
+      <c r="R7" s="146"/>
+      <c r="S7" s="146"/>
+      <c r="T7" s="151"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="5"/>
@@ -10355,37 +10355,37 @@
       <c r="T14" s="7"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="182" t="s">
+      <c r="A15" s="145" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="175"/>
-      <c r="C15" s="199" t="s">
+      <c r="B15" s="147"/>
+      <c r="C15" s="170" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="175"/>
-      <c r="E15" s="189" t="s">
+      <c r="D15" s="147"/>
+      <c r="E15" s="157" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="175"/>
-      <c r="G15" s="189" t="s">
+      <c r="F15" s="147"/>
+      <c r="G15" s="157" t="s">
         <v>43</v>
       </c>
-      <c r="H15" s="174"/>
-      <c r="I15" s="175"/>
-      <c r="J15" s="189" t="s">
+      <c r="H15" s="146"/>
+      <c r="I15" s="147"/>
+      <c r="J15" s="157" t="s">
         <v>44</v>
       </c>
-      <c r="K15" s="175"/>
-      <c r="L15" s="189" t="s">
+      <c r="K15" s="147"/>
+      <c r="L15" s="157" t="s">
         <v>45</v>
       </c>
-      <c r="M15" s="174"/>
-      <c r="N15" s="175"/>
-      <c r="O15" s="189" t="s">
+      <c r="M15" s="146"/>
+      <c r="N15" s="147"/>
+      <c r="O15" s="157" t="s">
         <v>46</v>
       </c>
-      <c r="P15" s="174"/>
-      <c r="Q15" s="175"/>
+      <c r="P15" s="146"/>
+      <c r="Q15" s="147"/>
       <c r="R15" s="12" t="s">
         <v>47</v>
       </c>
@@ -10397,25 +10397,25 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="191">
+      <c r="A16" s="168">
         <v>1</v>
       </c>
-      <c r="B16" s="175"/>
-      <c r="C16" s="192"/>
-      <c r="D16" s="175"/>
-      <c r="E16" s="192"/>
-      <c r="F16" s="175"/>
-      <c r="G16" s="198"/>
-      <c r="H16" s="174"/>
-      <c r="I16" s="175"/>
-      <c r="J16" s="198"/>
-      <c r="K16" s="175"/>
-      <c r="L16" s="195"/>
-      <c r="M16" s="174"/>
-      <c r="N16" s="175"/>
-      <c r="O16" s="195"/>
-      <c r="P16" s="174"/>
-      <c r="Q16" s="175"/>
+      <c r="B16" s="147"/>
+      <c r="C16" s="169"/>
+      <c r="D16" s="147"/>
+      <c r="E16" s="169"/>
+      <c r="F16" s="147"/>
+      <c r="G16" s="160"/>
+      <c r="H16" s="146"/>
+      <c r="I16" s="147"/>
+      <c r="J16" s="160"/>
+      <c r="K16" s="147"/>
+      <c r="L16" s="162"/>
+      <c r="M16" s="146"/>
+      <c r="N16" s="147"/>
+      <c r="O16" s="162"/>
+      <c r="P16" s="146"/>
+      <c r="Q16" s="147"/>
       <c r="R16" s="30"/>
       <c r="S16" s="30"/>
       <c r="T16" s="31"/>
@@ -10427,25 +10427,25 @@
       <c r="Z16" s="32"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="191">
+      <c r="A17" s="168">
         <v>2</v>
       </c>
-      <c r="B17" s="175"/>
-      <c r="C17" s="192"/>
-      <c r="D17" s="175"/>
-      <c r="E17" s="192"/>
-      <c r="F17" s="175"/>
-      <c r="G17" s="198"/>
-      <c r="H17" s="174"/>
-      <c r="I17" s="175"/>
-      <c r="J17" s="198"/>
-      <c r="K17" s="175"/>
-      <c r="L17" s="195"/>
-      <c r="M17" s="174"/>
-      <c r="N17" s="175"/>
-      <c r="O17" s="195"/>
-      <c r="P17" s="174"/>
-      <c r="Q17" s="175"/>
+      <c r="B17" s="147"/>
+      <c r="C17" s="169"/>
+      <c r="D17" s="147"/>
+      <c r="E17" s="169"/>
+      <c r="F17" s="147"/>
+      <c r="G17" s="160"/>
+      <c r="H17" s="146"/>
+      <c r="I17" s="147"/>
+      <c r="J17" s="160"/>
+      <c r="K17" s="147"/>
+      <c r="L17" s="162"/>
+      <c r="M17" s="146"/>
+      <c r="N17" s="147"/>
+      <c r="O17" s="162"/>
+      <c r="P17" s="146"/>
+      <c r="Q17" s="147"/>
       <c r="R17" s="30"/>
       <c r="S17" s="30"/>
       <c r="T17" s="31"/>
@@ -10457,23 +10457,23 @@
       <c r="Z17" s="32"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="191"/>
-      <c r="B18" s="175"/>
-      <c r="C18" s="192"/>
-      <c r="D18" s="175"/>
-      <c r="E18" s="192"/>
-      <c r="F18" s="175"/>
-      <c r="G18" s="198"/>
-      <c r="H18" s="174"/>
-      <c r="I18" s="175"/>
-      <c r="J18" s="198"/>
-      <c r="K18" s="175"/>
-      <c r="L18" s="195"/>
-      <c r="M18" s="174"/>
-      <c r="N18" s="175"/>
-      <c r="O18" s="195"/>
-      <c r="P18" s="174"/>
-      <c r="Q18" s="175"/>
+      <c r="A18" s="168"/>
+      <c r="B18" s="147"/>
+      <c r="C18" s="169"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="169"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="160"/>
+      <c r="H18" s="146"/>
+      <c r="I18" s="147"/>
+      <c r="J18" s="160"/>
+      <c r="K18" s="147"/>
+      <c r="L18" s="162"/>
+      <c r="M18" s="146"/>
+      <c r="N18" s="147"/>
+      <c r="O18" s="162"/>
+      <c r="P18" s="146"/>
+      <c r="Q18" s="147"/>
       <c r="R18" s="30"/>
       <c r="S18" s="30"/>
       <c r="T18" s="31"/>
@@ -10485,23 +10485,23 @@
       <c r="Z18" s="32"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="191"/>
-      <c r="B19" s="175"/>
-      <c r="C19" s="192"/>
-      <c r="D19" s="175"/>
-      <c r="E19" s="192"/>
-      <c r="F19" s="175"/>
-      <c r="G19" s="198"/>
-      <c r="H19" s="174"/>
-      <c r="I19" s="175"/>
-      <c r="J19" s="198"/>
-      <c r="K19" s="175"/>
-      <c r="L19" s="195"/>
-      <c r="M19" s="174"/>
-      <c r="N19" s="175"/>
-      <c r="O19" s="195"/>
-      <c r="P19" s="174"/>
-      <c r="Q19" s="175"/>
+      <c r="A19" s="168"/>
+      <c r="B19" s="147"/>
+      <c r="C19" s="169"/>
+      <c r="D19" s="147"/>
+      <c r="E19" s="169"/>
+      <c r="F19" s="147"/>
+      <c r="G19" s="160"/>
+      <c r="H19" s="146"/>
+      <c r="I19" s="147"/>
+      <c r="J19" s="160"/>
+      <c r="K19" s="147"/>
+      <c r="L19" s="162"/>
+      <c r="M19" s="146"/>
+      <c r="N19" s="147"/>
+      <c r="O19" s="162"/>
+      <c r="P19" s="146"/>
+      <c r="Q19" s="147"/>
       <c r="R19" s="30"/>
       <c r="S19" s="30"/>
       <c r="T19" s="31"/>
@@ -10513,23 +10513,23 @@
       <c r="Z19" s="32"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="191"/>
-      <c r="B20" s="175"/>
-      <c r="C20" s="192"/>
-      <c r="D20" s="175"/>
-      <c r="E20" s="192"/>
-      <c r="F20" s="175"/>
-      <c r="G20" s="198"/>
-      <c r="H20" s="174"/>
-      <c r="I20" s="175"/>
-      <c r="J20" s="198"/>
-      <c r="K20" s="175"/>
-      <c r="L20" s="195"/>
-      <c r="M20" s="174"/>
-      <c r="N20" s="175"/>
-      <c r="O20" s="195"/>
-      <c r="P20" s="174"/>
-      <c r="Q20" s="175"/>
+      <c r="A20" s="168"/>
+      <c r="B20" s="147"/>
+      <c r="C20" s="169"/>
+      <c r="D20" s="147"/>
+      <c r="E20" s="169"/>
+      <c r="F20" s="147"/>
+      <c r="G20" s="160"/>
+      <c r="H20" s="146"/>
+      <c r="I20" s="147"/>
+      <c r="J20" s="160"/>
+      <c r="K20" s="147"/>
+      <c r="L20" s="162"/>
+      <c r="M20" s="146"/>
+      <c r="N20" s="147"/>
+      <c r="O20" s="162"/>
+      <c r="P20" s="146"/>
+      <c r="Q20" s="147"/>
       <c r="R20" s="30"/>
       <c r="S20" s="30"/>
       <c r="T20" s="31"/>
@@ -10541,23 +10541,23 @@
       <c r="Z20" s="32"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="191"/>
-      <c r="B21" s="175"/>
-      <c r="C21" s="192"/>
-      <c r="D21" s="175"/>
-      <c r="E21" s="192"/>
-      <c r="F21" s="175"/>
-      <c r="G21" s="198"/>
-      <c r="H21" s="174"/>
-      <c r="I21" s="175"/>
-      <c r="J21" s="198"/>
-      <c r="K21" s="175"/>
-      <c r="L21" s="195"/>
-      <c r="M21" s="174"/>
-      <c r="N21" s="175"/>
-      <c r="O21" s="195"/>
-      <c r="P21" s="174"/>
-      <c r="Q21" s="175"/>
+      <c r="A21" s="168"/>
+      <c r="B21" s="147"/>
+      <c r="C21" s="169"/>
+      <c r="D21" s="147"/>
+      <c r="E21" s="169"/>
+      <c r="F21" s="147"/>
+      <c r="G21" s="160"/>
+      <c r="H21" s="146"/>
+      <c r="I21" s="147"/>
+      <c r="J21" s="160"/>
+      <c r="K21" s="147"/>
+      <c r="L21" s="162"/>
+      <c r="M21" s="146"/>
+      <c r="N21" s="147"/>
+      <c r="O21" s="162"/>
+      <c r="P21" s="146"/>
+      <c r="Q21" s="147"/>
       <c r="R21" s="30"/>
       <c r="S21" s="30"/>
       <c r="T21" s="31"/>
@@ -10569,23 +10569,23 @@
       <c r="Z21" s="32"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="191"/>
-      <c r="B22" s="175"/>
-      <c r="C22" s="192"/>
-      <c r="D22" s="175"/>
-      <c r="E22" s="192"/>
-      <c r="F22" s="175"/>
-      <c r="G22" s="198"/>
-      <c r="H22" s="174"/>
-      <c r="I22" s="175"/>
-      <c r="J22" s="198"/>
-      <c r="K22" s="175"/>
-      <c r="L22" s="195"/>
-      <c r="M22" s="174"/>
-      <c r="N22" s="175"/>
-      <c r="O22" s="195"/>
-      <c r="P22" s="174"/>
-      <c r="Q22" s="175"/>
+      <c r="A22" s="168"/>
+      <c r="B22" s="147"/>
+      <c r="C22" s="169"/>
+      <c r="D22" s="147"/>
+      <c r="E22" s="169"/>
+      <c r="F22" s="147"/>
+      <c r="G22" s="160"/>
+      <c r="H22" s="146"/>
+      <c r="I22" s="147"/>
+      <c r="J22" s="160"/>
+      <c r="K22" s="147"/>
+      <c r="L22" s="162"/>
+      <c r="M22" s="146"/>
+      <c r="N22" s="147"/>
+      <c r="O22" s="162"/>
+      <c r="P22" s="146"/>
+      <c r="Q22" s="147"/>
       <c r="R22" s="30"/>
       <c r="S22" s="30"/>
       <c r="T22" s="31"/>
@@ -10597,23 +10597,23 @@
       <c r="Z22" s="32"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="191"/>
-      <c r="B23" s="175"/>
-      <c r="C23" s="192"/>
-      <c r="D23" s="175"/>
-      <c r="E23" s="192"/>
-      <c r="F23" s="175"/>
-      <c r="G23" s="198"/>
-      <c r="H23" s="174"/>
-      <c r="I23" s="175"/>
-      <c r="J23" s="198"/>
-      <c r="K23" s="175"/>
-      <c r="L23" s="195"/>
-      <c r="M23" s="174"/>
-      <c r="N23" s="175"/>
-      <c r="O23" s="195"/>
-      <c r="P23" s="174"/>
-      <c r="Q23" s="175"/>
+      <c r="A23" s="168"/>
+      <c r="B23" s="147"/>
+      <c r="C23" s="169"/>
+      <c r="D23" s="147"/>
+      <c r="E23" s="169"/>
+      <c r="F23" s="147"/>
+      <c r="G23" s="160"/>
+      <c r="H23" s="146"/>
+      <c r="I23" s="147"/>
+      <c r="J23" s="160"/>
+      <c r="K23" s="147"/>
+      <c r="L23" s="162"/>
+      <c r="M23" s="146"/>
+      <c r="N23" s="147"/>
+      <c r="O23" s="162"/>
+      <c r="P23" s="146"/>
+      <c r="Q23" s="147"/>
       <c r="R23" s="30"/>
       <c r="S23" s="30"/>
       <c r="T23" s="31"/>
@@ -10625,23 +10625,23 @@
       <c r="Z23" s="32"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="191"/>
-      <c r="B24" s="175"/>
-      <c r="C24" s="192"/>
-      <c r="D24" s="175"/>
-      <c r="E24" s="192"/>
-      <c r="F24" s="175"/>
-      <c r="G24" s="198"/>
-      <c r="H24" s="174"/>
-      <c r="I24" s="175"/>
-      <c r="J24" s="198"/>
-      <c r="K24" s="175"/>
-      <c r="L24" s="195"/>
-      <c r="M24" s="174"/>
-      <c r="N24" s="175"/>
-      <c r="O24" s="195"/>
-      <c r="P24" s="174"/>
-      <c r="Q24" s="175"/>
+      <c r="A24" s="168"/>
+      <c r="B24" s="147"/>
+      <c r="C24" s="169"/>
+      <c r="D24" s="147"/>
+      <c r="E24" s="169"/>
+      <c r="F24" s="147"/>
+      <c r="G24" s="160"/>
+      <c r="H24" s="146"/>
+      <c r="I24" s="147"/>
+      <c r="J24" s="160"/>
+      <c r="K24" s="147"/>
+      <c r="L24" s="162"/>
+      <c r="M24" s="146"/>
+      <c r="N24" s="147"/>
+      <c r="O24" s="162"/>
+      <c r="P24" s="146"/>
+      <c r="Q24" s="147"/>
       <c r="R24" s="30"/>
       <c r="S24" s="30"/>
       <c r="T24" s="31"/>
@@ -10653,23 +10653,23 @@
       <c r="Z24" s="32"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="191"/>
-      <c r="B25" s="175"/>
-      <c r="C25" s="192"/>
-      <c r="D25" s="175"/>
-      <c r="E25" s="192"/>
-      <c r="F25" s="175"/>
-      <c r="G25" s="198"/>
-      <c r="H25" s="174"/>
-      <c r="I25" s="175"/>
-      <c r="J25" s="198"/>
-      <c r="K25" s="175"/>
-      <c r="L25" s="195"/>
-      <c r="M25" s="174"/>
-      <c r="N25" s="175"/>
-      <c r="O25" s="195"/>
-      <c r="P25" s="174"/>
-      <c r="Q25" s="175"/>
+      <c r="A25" s="168"/>
+      <c r="B25" s="147"/>
+      <c r="C25" s="169"/>
+      <c r="D25" s="147"/>
+      <c r="E25" s="169"/>
+      <c r="F25" s="147"/>
+      <c r="G25" s="160"/>
+      <c r="H25" s="146"/>
+      <c r="I25" s="147"/>
+      <c r="J25" s="160"/>
+      <c r="K25" s="147"/>
+      <c r="L25" s="162"/>
+      <c r="M25" s="146"/>
+      <c r="N25" s="147"/>
+      <c r="O25" s="162"/>
+      <c r="P25" s="146"/>
+      <c r="Q25" s="147"/>
       <c r="R25" s="30"/>
       <c r="S25" s="30"/>
       <c r="T25" s="31"/>
@@ -10681,23 +10681,23 @@
       <c r="Z25" s="32"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="191"/>
-      <c r="B26" s="175"/>
-      <c r="C26" s="192"/>
-      <c r="D26" s="175"/>
-      <c r="E26" s="192"/>
-      <c r="F26" s="175"/>
-      <c r="G26" s="198"/>
-      <c r="H26" s="174"/>
-      <c r="I26" s="175"/>
-      <c r="J26" s="198"/>
-      <c r="K26" s="175"/>
-      <c r="L26" s="195"/>
-      <c r="M26" s="174"/>
-      <c r="N26" s="175"/>
-      <c r="O26" s="195"/>
-      <c r="P26" s="174"/>
-      <c r="Q26" s="175"/>
+      <c r="A26" s="168"/>
+      <c r="B26" s="147"/>
+      <c r="C26" s="169"/>
+      <c r="D26" s="147"/>
+      <c r="E26" s="169"/>
+      <c r="F26" s="147"/>
+      <c r="G26" s="160"/>
+      <c r="H26" s="146"/>
+      <c r="I26" s="147"/>
+      <c r="J26" s="160"/>
+      <c r="K26" s="147"/>
+      <c r="L26" s="162"/>
+      <c r="M26" s="146"/>
+      <c r="N26" s="147"/>
+      <c r="O26" s="162"/>
+      <c r="P26" s="146"/>
+      <c r="Q26" s="147"/>
       <c r="R26" s="30"/>
       <c r="S26" s="30"/>
       <c r="T26" s="31"/>
@@ -10709,23 +10709,23 @@
       <c r="Z26" s="32"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="191"/>
-      <c r="B27" s="175"/>
-      <c r="C27" s="192"/>
-      <c r="D27" s="175"/>
-      <c r="E27" s="192"/>
-      <c r="F27" s="175"/>
-      <c r="G27" s="198"/>
-      <c r="H27" s="174"/>
-      <c r="I27" s="175"/>
-      <c r="J27" s="198"/>
-      <c r="K27" s="175"/>
-      <c r="L27" s="195"/>
-      <c r="M27" s="174"/>
-      <c r="N27" s="175"/>
-      <c r="O27" s="195"/>
-      <c r="P27" s="174"/>
-      <c r="Q27" s="175"/>
+      <c r="A27" s="168"/>
+      <c r="B27" s="147"/>
+      <c r="C27" s="169"/>
+      <c r="D27" s="147"/>
+      <c r="E27" s="169"/>
+      <c r="F27" s="147"/>
+      <c r="G27" s="160"/>
+      <c r="H27" s="146"/>
+      <c r="I27" s="147"/>
+      <c r="J27" s="160"/>
+      <c r="K27" s="147"/>
+      <c r="L27" s="162"/>
+      <c r="M27" s="146"/>
+      <c r="N27" s="147"/>
+      <c r="O27" s="162"/>
+      <c r="P27" s="146"/>
+      <c r="Q27" s="147"/>
       <c r="R27" s="30"/>
       <c r="S27" s="30"/>
       <c r="T27" s="31"/>
@@ -10737,23 +10737,23 @@
       <c r="Z27" s="32"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="191"/>
-      <c r="B28" s="175"/>
-      <c r="C28" s="192"/>
-      <c r="D28" s="175"/>
-      <c r="E28" s="192"/>
-      <c r="F28" s="175"/>
-      <c r="G28" s="198"/>
-      <c r="H28" s="174"/>
-      <c r="I28" s="175"/>
-      <c r="J28" s="198"/>
-      <c r="K28" s="175"/>
-      <c r="L28" s="195"/>
-      <c r="M28" s="174"/>
-      <c r="N28" s="175"/>
-      <c r="O28" s="195"/>
-      <c r="P28" s="174"/>
-      <c r="Q28" s="175"/>
+      <c r="A28" s="168"/>
+      <c r="B28" s="147"/>
+      <c r="C28" s="169"/>
+      <c r="D28" s="147"/>
+      <c r="E28" s="169"/>
+      <c r="F28" s="147"/>
+      <c r="G28" s="160"/>
+      <c r="H28" s="146"/>
+      <c r="I28" s="147"/>
+      <c r="J28" s="160"/>
+      <c r="K28" s="147"/>
+      <c r="L28" s="162"/>
+      <c r="M28" s="146"/>
+      <c r="N28" s="147"/>
+      <c r="O28" s="162"/>
+      <c r="P28" s="146"/>
+      <c r="Q28" s="147"/>
       <c r="R28" s="30"/>
       <c r="S28" s="30"/>
       <c r="T28" s="31"/>
@@ -10765,23 +10765,23 @@
       <c r="Z28" s="32"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="191"/>
-      <c r="B29" s="175"/>
-      <c r="C29" s="192"/>
-      <c r="D29" s="175"/>
-      <c r="E29" s="192"/>
-      <c r="F29" s="175"/>
-      <c r="G29" s="198"/>
-      <c r="H29" s="174"/>
-      <c r="I29" s="175"/>
-      <c r="J29" s="198"/>
-      <c r="K29" s="175"/>
-      <c r="L29" s="195"/>
-      <c r="M29" s="174"/>
-      <c r="N29" s="175"/>
-      <c r="O29" s="195"/>
-      <c r="P29" s="174"/>
-      <c r="Q29" s="175"/>
+      <c r="A29" s="168"/>
+      <c r="B29" s="147"/>
+      <c r="C29" s="169"/>
+      <c r="D29" s="147"/>
+      <c r="E29" s="169"/>
+      <c r="F29" s="147"/>
+      <c r="G29" s="160"/>
+      <c r="H29" s="146"/>
+      <c r="I29" s="147"/>
+      <c r="J29" s="160"/>
+      <c r="K29" s="147"/>
+      <c r="L29" s="162"/>
+      <c r="M29" s="146"/>
+      <c r="N29" s="147"/>
+      <c r="O29" s="162"/>
+      <c r="P29" s="146"/>
+      <c r="Q29" s="147"/>
       <c r="R29" s="30"/>
       <c r="S29" s="30"/>
       <c r="T29" s="31"/>
@@ -10793,23 +10793,23 @@
       <c r="Z29" s="32"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="191"/>
-      <c r="B30" s="175"/>
-      <c r="C30" s="192"/>
-      <c r="D30" s="175"/>
-      <c r="E30" s="192"/>
-      <c r="F30" s="175"/>
-      <c r="G30" s="198"/>
-      <c r="H30" s="174"/>
-      <c r="I30" s="175"/>
-      <c r="J30" s="198"/>
-      <c r="K30" s="175"/>
-      <c r="L30" s="195"/>
-      <c r="M30" s="174"/>
-      <c r="N30" s="175"/>
-      <c r="O30" s="195"/>
-      <c r="P30" s="174"/>
-      <c r="Q30" s="175"/>
+      <c r="A30" s="168"/>
+      <c r="B30" s="147"/>
+      <c r="C30" s="169"/>
+      <c r="D30" s="147"/>
+      <c r="E30" s="169"/>
+      <c r="F30" s="147"/>
+      <c r="G30" s="160"/>
+      <c r="H30" s="146"/>
+      <c r="I30" s="147"/>
+      <c r="J30" s="160"/>
+      <c r="K30" s="147"/>
+      <c r="L30" s="162"/>
+      <c r="M30" s="146"/>
+      <c r="N30" s="147"/>
+      <c r="O30" s="162"/>
+      <c r="P30" s="146"/>
+      <c r="Q30" s="147"/>
       <c r="R30" s="30"/>
       <c r="S30" s="30"/>
       <c r="T30" s="31"/>
@@ -10821,23 +10821,23 @@
       <c r="Z30" s="32"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="193"/>
-      <c r="B31" s="181"/>
-      <c r="C31" s="194"/>
-      <c r="D31" s="181"/>
-      <c r="E31" s="194"/>
-      <c r="F31" s="181"/>
-      <c r="G31" s="203"/>
-      <c r="H31" s="171"/>
-      <c r="I31" s="181"/>
-      <c r="J31" s="203"/>
-      <c r="K31" s="181"/>
-      <c r="L31" s="196"/>
-      <c r="M31" s="171"/>
-      <c r="N31" s="181"/>
-      <c r="O31" s="196"/>
-      <c r="P31" s="171"/>
-      <c r="Q31" s="181"/>
+      <c r="A31" s="171"/>
+      <c r="B31" s="144"/>
+      <c r="C31" s="172"/>
+      <c r="D31" s="144"/>
+      <c r="E31" s="172"/>
+      <c r="F31" s="144"/>
+      <c r="G31" s="161"/>
+      <c r="H31" s="143"/>
+      <c r="I31" s="144"/>
+      <c r="J31" s="161"/>
+      <c r="K31" s="144"/>
+      <c r="L31" s="163"/>
+      <c r="M31" s="143"/>
+      <c r="N31" s="144"/>
+      <c r="O31" s="163"/>
+      <c r="P31" s="143"/>
+      <c r="Q31" s="144"/>
       <c r="R31" s="33"/>
       <c r="S31" s="33"/>
       <c r="T31" s="34"/>
@@ -11835,62 +11835,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -11915,62 +11915,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11993,72 +11993,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="181" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="97" t="s">
+      <c r="B1" s="181"/>
+      <c r="C1" s="182" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="98"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="70" t="s">
+      <c r="D1" s="183"/>
+      <c r="E1" s="184"/>
+      <c r="F1" s="185" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="71"/>
+      <c r="G1" s="186"/>
+      <c r="H1" s="186"/>
+      <c r="I1" s="186"/>
+      <c r="J1" s="186"/>
+      <c r="K1" s="186"/>
+      <c r="L1" s="186"/>
+      <c r="M1" s="187"/>
       <c r="N1" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="O1" s="70" t="s">
+      <c r="O1" s="185" t="s">
         <v>72</v>
       </c>
-      <c r="P1" s="71"/>
+      <c r="P1" s="187"/>
       <c r="Q1" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="R1" s="70" t="s">
+      <c r="R1" s="185" t="s">
         <v>74</v>
       </c>
-      <c r="S1" s="71"/>
+      <c r="S1" s="187"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="97" t="s">
+      <c r="A2" s="181"/>
+      <c r="B2" s="181"/>
+      <c r="C2" s="182" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="70" t="s">
+      <c r="D2" s="183"/>
+      <c r="E2" s="184"/>
+      <c r="F2" s="185" t="s">
         <v>76</v>
       </c>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="71"/>
+      <c r="G2" s="186"/>
+      <c r="H2" s="186"/>
+      <c r="I2" s="186"/>
+      <c r="J2" s="186"/>
+      <c r="K2" s="186"/>
+      <c r="L2" s="186"/>
+      <c r="M2" s="187"/>
       <c r="N2" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="O2" s="80">
+      <c r="O2" s="194">
         <v>46182</v>
       </c>
-      <c r="P2" s="81"/>
+      <c r="P2" s="195"/>
       <c r="Q2" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="R2" s="72" t="s">
+      <c r="R2" s="202" t="s">
         <v>72</v>
       </c>
-      <c r="S2" s="73"/>
+      <c r="S2" s="203"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="37"/>
@@ -12088,33 +12088,33 @@
       <c r="B4" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="83" t="s">
+      <c r="C4" s="177" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="83" t="s">
+      <c r="D4" s="178"/>
+      <c r="E4" s="178"/>
+      <c r="F4" s="178"/>
+      <c r="G4" s="179"/>
+      <c r="H4" s="177" t="s">
         <v>82</v>
       </c>
-      <c r="I4" s="84"/>
-      <c r="J4" s="84"/>
-      <c r="K4" s="84"/>
-      <c r="L4" s="84"/>
-      <c r="M4" s="85"/>
-      <c r="N4" s="83" t="s">
+      <c r="I4" s="178"/>
+      <c r="J4" s="178"/>
+      <c r="K4" s="178"/>
+      <c r="L4" s="178"/>
+      <c r="M4" s="179"/>
+      <c r="N4" s="177" t="s">
         <v>83</v>
       </c>
-      <c r="O4" s="84"/>
-      <c r="P4" s="85"/>
+      <c r="O4" s="178"/>
+      <c r="P4" s="179"/>
       <c r="Q4" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="R4" s="83" t="s">
+      <c r="R4" s="177" t="s">
         <v>85</v>
       </c>
-      <c r="S4" s="85"/>
+      <c r="S4" s="179"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="41">
@@ -12123,31 +12123,31 @@
       <c r="B5" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="92" t="s">
+      <c r="C5" s="180" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="92"/>
-      <c r="E5" s="92"/>
-      <c r="F5" s="92"/>
-      <c r="G5" s="92"/>
-      <c r="H5" s="92" t="s">
+      <c r="D5" s="180"/>
+      <c r="E5" s="180"/>
+      <c r="F5" s="180"/>
+      <c r="G5" s="180"/>
+      <c r="H5" s="180" t="s">
         <v>101</v>
       </c>
-      <c r="I5" s="92"/>
-      <c r="J5" s="92"/>
-      <c r="K5" s="92"/>
-      <c r="L5" s="92"/>
-      <c r="M5" s="92"/>
-      <c r="N5" s="86" t="s">
+      <c r="I5" s="180"/>
+      <c r="J5" s="180"/>
+      <c r="K5" s="180"/>
+      <c r="L5" s="180"/>
+      <c r="M5" s="180"/>
+      <c r="N5" s="196" t="s">
         <v>88</v>
       </c>
-      <c r="O5" s="87"/>
-      <c r="P5" s="88"/>
+      <c r="O5" s="197"/>
+      <c r="P5" s="198"/>
       <c r="Q5" s="42">
         <v>46182</v>
       </c>
-      <c r="R5" s="94"/>
-      <c r="S5" s="95"/>
+      <c r="R5" s="192"/>
+      <c r="S5" s="193"/>
     </row>
     <row r="6" spans="1:19" ht="46.5" customHeight="1">
       <c r="A6" s="43">
@@ -12156,31 +12156,31 @@
       <c r="B6" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="92" t="s">
+      <c r="C6" s="180" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="92"/>
-      <c r="E6" s="92"/>
-      <c r="F6" s="92"/>
-      <c r="G6" s="92"/>
-      <c r="H6" s="92" t="s">
+      <c r="D6" s="180"/>
+      <c r="E6" s="180"/>
+      <c r="F6" s="180"/>
+      <c r="G6" s="180"/>
+      <c r="H6" s="180" t="s">
         <v>101</v>
       </c>
-      <c r="I6" s="92"/>
-      <c r="J6" s="92"/>
-      <c r="K6" s="92"/>
-      <c r="L6" s="92"/>
-      <c r="M6" s="92"/>
-      <c r="N6" s="89" t="s">
+      <c r="I6" s="180"/>
+      <c r="J6" s="180"/>
+      <c r="K6" s="180"/>
+      <c r="L6" s="180"/>
+      <c r="M6" s="180"/>
+      <c r="N6" s="199" t="s">
         <v>102</v>
       </c>
-      <c r="O6" s="90"/>
-      <c r="P6" s="91"/>
+      <c r="O6" s="200"/>
+      <c r="P6" s="201"/>
       <c r="Q6" s="42">
         <v>46182</v>
       </c>
-      <c r="R6" s="82"/>
-      <c r="S6" s="82"/>
+      <c r="R6" s="188"/>
+      <c r="S6" s="188"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="43">
@@ -12189,979 +12189,1160 @@
       <c r="B7" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="92" t="s">
+      <c r="C7" s="180" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="93" t="s">
+      <c r="D7" s="180"/>
+      <c r="E7" s="180"/>
+      <c r="F7" s="180"/>
+      <c r="G7" s="180"/>
+      <c r="H7" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="I7" s="93"/>
-      <c r="J7" s="93"/>
-      <c r="K7" s="93"/>
-      <c r="L7" s="93"/>
-      <c r="M7" s="93"/>
-      <c r="N7" s="89" t="s">
+      <c r="I7" s="176"/>
+      <c r="J7" s="176"/>
+      <c r="K7" s="176"/>
+      <c r="L7" s="176"/>
+      <c r="M7" s="176"/>
+      <c r="N7" s="199" t="s">
         <v>103</v>
       </c>
-      <c r="O7" s="75"/>
-      <c r="P7" s="76"/>
+      <c r="O7" s="190"/>
+      <c r="P7" s="191"/>
       <c r="Q7" s="42">
         <v>46182</v>
       </c>
-      <c r="R7" s="82"/>
-      <c r="S7" s="82"/>
+      <c r="R7" s="188"/>
+      <c r="S7" s="188"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="43"/>
       <c r="B8" s="43"/>
-      <c r="C8" s="93"/>
-      <c r="D8" s="93"/>
-      <c r="E8" s="93"/>
-      <c r="F8" s="93"/>
-      <c r="G8" s="93"/>
-      <c r="H8" s="93"/>
-      <c r="I8" s="93"/>
-      <c r="J8" s="93"/>
-      <c r="K8" s="93"/>
-      <c r="L8" s="93"/>
-      <c r="M8" s="93"/>
-      <c r="N8" s="74"/>
-      <c r="O8" s="75"/>
-      <c r="P8" s="76"/>
+      <c r="C8" s="176"/>
+      <c r="D8" s="176"/>
+      <c r="E8" s="176"/>
+      <c r="F8" s="176"/>
+      <c r="G8" s="176"/>
+      <c r="H8" s="176"/>
+      <c r="I8" s="176"/>
+      <c r="J8" s="176"/>
+      <c r="K8" s="176"/>
+      <c r="L8" s="176"/>
+      <c r="M8" s="176"/>
+      <c r="N8" s="189"/>
+      <c r="O8" s="190"/>
+      <c r="P8" s="191"/>
       <c r="Q8" s="44"/>
-      <c r="R8" s="82"/>
-      <c r="S8" s="82"/>
+      <c r="R8" s="188"/>
+      <c r="S8" s="188"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="43"/>
       <c r="B9" s="43"/>
-      <c r="C9" s="93"/>
-      <c r="D9" s="93"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="93"/>
-      <c r="G9" s="93"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="93"/>
-      <c r="J9" s="93"/>
-      <c r="K9" s="93"/>
-      <c r="L9" s="93"/>
-      <c r="M9" s="93"/>
-      <c r="N9" s="74"/>
-      <c r="O9" s="75"/>
-      <c r="P9" s="76"/>
+      <c r="C9" s="176"/>
+      <c r="D9" s="176"/>
+      <c r="E9" s="176"/>
+      <c r="F9" s="176"/>
+      <c r="G9" s="176"/>
+      <c r="H9" s="176"/>
+      <c r="I9" s="176"/>
+      <c r="J9" s="176"/>
+      <c r="K9" s="176"/>
+      <c r="L9" s="176"/>
+      <c r="M9" s="176"/>
+      <c r="N9" s="189"/>
+      <c r="O9" s="190"/>
+      <c r="P9" s="191"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="82"/>
-      <c r="S9" s="82"/>
+      <c r="R9" s="188"/>
+      <c r="S9" s="188"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="43"/>
       <c r="B10" s="43"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="93"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="78"/>
-      <c r="J10" s="78"/>
-      <c r="K10" s="78"/>
-      <c r="L10" s="78"/>
-      <c r="M10" s="79"/>
-      <c r="N10" s="74"/>
-      <c r="O10" s="75"/>
-      <c r="P10" s="76"/>
+      <c r="C10" s="176"/>
+      <c r="D10" s="176"/>
+      <c r="E10" s="176"/>
+      <c r="F10" s="176"/>
+      <c r="G10" s="176"/>
+      <c r="H10" s="173"/>
+      <c r="I10" s="174"/>
+      <c r="J10" s="174"/>
+      <c r="K10" s="174"/>
+      <c r="L10" s="174"/>
+      <c r="M10" s="175"/>
+      <c r="N10" s="189"/>
+      <c r="O10" s="190"/>
+      <c r="P10" s="191"/>
       <c r="Q10" s="44"/>
-      <c r="R10" s="82"/>
-      <c r="S10" s="82"/>
+      <c r="R10" s="188"/>
+      <c r="S10" s="188"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="43"/>
       <c r="B11" s="43"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="78"/>
-      <c r="J11" s="78"/>
-      <c r="K11" s="78"/>
-      <c r="L11" s="78"/>
-      <c r="M11" s="79"/>
-      <c r="N11" s="74"/>
-      <c r="O11" s="75"/>
-      <c r="P11" s="76"/>
+      <c r="C11" s="176"/>
+      <c r="D11" s="176"/>
+      <c r="E11" s="176"/>
+      <c r="F11" s="176"/>
+      <c r="G11" s="176"/>
+      <c r="H11" s="173"/>
+      <c r="I11" s="174"/>
+      <c r="J11" s="174"/>
+      <c r="K11" s="174"/>
+      <c r="L11" s="174"/>
+      <c r="M11" s="175"/>
+      <c r="N11" s="189"/>
+      <c r="O11" s="190"/>
+      <c r="P11" s="191"/>
       <c r="Q11" s="43"/>
-      <c r="R11" s="82"/>
-      <c r="S11" s="82"/>
+      <c r="R11" s="188"/>
+      <c r="S11" s="188"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="43"/>
       <c r="B12" s="43"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="93"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="78"/>
-      <c r="L12" s="78"/>
-      <c r="M12" s="79"/>
-      <c r="N12" s="74"/>
-      <c r="O12" s="75"/>
-      <c r="P12" s="76"/>
+      <c r="C12" s="176"/>
+      <c r="D12" s="176"/>
+      <c r="E12" s="176"/>
+      <c r="F12" s="176"/>
+      <c r="G12" s="176"/>
+      <c r="H12" s="173"/>
+      <c r="I12" s="174"/>
+      <c r="J12" s="174"/>
+      <c r="K12" s="174"/>
+      <c r="L12" s="174"/>
+      <c r="M12" s="175"/>
+      <c r="N12" s="189"/>
+      <c r="O12" s="190"/>
+      <c r="P12" s="191"/>
       <c r="Q12" s="43"/>
-      <c r="R12" s="82"/>
-      <c r="S12" s="82"/>
+      <c r="R12" s="188"/>
+      <c r="S12" s="188"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="43"/>
       <c r="B13" s="43"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="93"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="93"/>
-      <c r="G13" s="93"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="78"/>
-      <c r="J13" s="78"/>
-      <c r="K13" s="78"/>
-      <c r="L13" s="78"/>
-      <c r="M13" s="79"/>
-      <c r="N13" s="74"/>
-      <c r="O13" s="75"/>
-      <c r="P13" s="76"/>
+      <c r="C13" s="176"/>
+      <c r="D13" s="176"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="176"/>
+      <c r="G13" s="176"/>
+      <c r="H13" s="173"/>
+      <c r="I13" s="174"/>
+      <c r="J13" s="174"/>
+      <c r="K13" s="174"/>
+      <c r="L13" s="174"/>
+      <c r="M13" s="175"/>
+      <c r="N13" s="189"/>
+      <c r="O13" s="190"/>
+      <c r="P13" s="191"/>
       <c r="Q13" s="43"/>
-      <c r="R13" s="82"/>
-      <c r="S13" s="82"/>
+      <c r="R13" s="188"/>
+      <c r="S13" s="188"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="43"/>
       <c r="B14" s="43"/>
-      <c r="C14" s="93"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="93"/>
-      <c r="F14" s="93"/>
-      <c r="G14" s="93"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="78"/>
-      <c r="K14" s="78"/>
-      <c r="L14" s="78"/>
-      <c r="M14" s="79"/>
-      <c r="N14" s="74"/>
-      <c r="O14" s="75"/>
-      <c r="P14" s="76"/>
+      <c r="C14" s="176"/>
+      <c r="D14" s="176"/>
+      <c r="E14" s="176"/>
+      <c r="F14" s="176"/>
+      <c r="G14" s="176"/>
+      <c r="H14" s="173"/>
+      <c r="I14" s="174"/>
+      <c r="J14" s="174"/>
+      <c r="K14" s="174"/>
+      <c r="L14" s="174"/>
+      <c r="M14" s="175"/>
+      <c r="N14" s="189"/>
+      <c r="O14" s="190"/>
+      <c r="P14" s="191"/>
       <c r="Q14" s="43"/>
-      <c r="R14" s="82"/>
-      <c r="S14" s="82"/>
+      <c r="R14" s="188"/>
+      <c r="S14" s="188"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="43"/>
       <c r="B15" s="43"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="93"/>
-      <c r="E15" s="93"/>
-      <c r="F15" s="93"/>
-      <c r="G15" s="93"/>
-      <c r="H15" s="77"/>
-      <c r="I15" s="78"/>
-      <c r="J15" s="78"/>
-      <c r="K15" s="78"/>
-      <c r="L15" s="78"/>
-      <c r="M15" s="79"/>
-      <c r="N15" s="74"/>
-      <c r="O15" s="75"/>
-      <c r="P15" s="76"/>
+      <c r="C15" s="176"/>
+      <c r="D15" s="176"/>
+      <c r="E15" s="176"/>
+      <c r="F15" s="176"/>
+      <c r="G15" s="176"/>
+      <c r="H15" s="173"/>
+      <c r="I15" s="174"/>
+      <c r="J15" s="174"/>
+      <c r="K15" s="174"/>
+      <c r="L15" s="174"/>
+      <c r="M15" s="175"/>
+      <c r="N15" s="189"/>
+      <c r="O15" s="190"/>
+      <c r="P15" s="191"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="82"/>
-      <c r="S15" s="82"/>
+      <c r="R15" s="188"/>
+      <c r="S15" s="188"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="43"/>
       <c r="B16" s="43"/>
-      <c r="C16" s="93"/>
-      <c r="D16" s="93"/>
-      <c r="E16" s="93"/>
-      <c r="F16" s="93"/>
-      <c r="G16" s="93"/>
-      <c r="H16" s="77"/>
-      <c r="I16" s="78"/>
-      <c r="J16" s="78"/>
-      <c r="K16" s="78"/>
-      <c r="L16" s="78"/>
-      <c r="M16" s="79"/>
-      <c r="N16" s="74"/>
-      <c r="O16" s="75"/>
-      <c r="P16" s="76"/>
+      <c r="C16" s="176"/>
+      <c r="D16" s="176"/>
+      <c r="E16" s="176"/>
+      <c r="F16" s="176"/>
+      <c r="G16" s="176"/>
+      <c r="H16" s="173"/>
+      <c r="I16" s="174"/>
+      <c r="J16" s="174"/>
+      <c r="K16" s="174"/>
+      <c r="L16" s="174"/>
+      <c r="M16" s="175"/>
+      <c r="N16" s="189"/>
+      <c r="O16" s="190"/>
+      <c r="P16" s="191"/>
       <c r="Q16" s="43"/>
-      <c r="R16" s="82"/>
-      <c r="S16" s="82"/>
+      <c r="R16" s="188"/>
+      <c r="S16" s="188"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="43"/>
       <c r="B17" s="43"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="93"/>
-      <c r="F17" s="93"/>
-      <c r="G17" s="93"/>
-      <c r="H17" s="77"/>
-      <c r="I17" s="78"/>
-      <c r="J17" s="78"/>
-      <c r="K17" s="78"/>
-      <c r="L17" s="78"/>
-      <c r="M17" s="79"/>
-      <c r="N17" s="74"/>
-      <c r="O17" s="75"/>
-      <c r="P17" s="76"/>
+      <c r="C17" s="176"/>
+      <c r="D17" s="176"/>
+      <c r="E17" s="176"/>
+      <c r="F17" s="176"/>
+      <c r="G17" s="176"/>
+      <c r="H17" s="173"/>
+      <c r="I17" s="174"/>
+      <c r="J17" s="174"/>
+      <c r="K17" s="174"/>
+      <c r="L17" s="174"/>
+      <c r="M17" s="175"/>
+      <c r="N17" s="189"/>
+      <c r="O17" s="190"/>
+      <c r="P17" s="191"/>
       <c r="Q17" s="43"/>
-      <c r="R17" s="82"/>
-      <c r="S17" s="82"/>
+      <c r="R17" s="188"/>
+      <c r="S17" s="188"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="43"/>
       <c r="B18" s="43"/>
-      <c r="C18" s="93"/>
-      <c r="D18" s="93"/>
-      <c r="E18" s="93"/>
-      <c r="F18" s="93"/>
-      <c r="G18" s="93"/>
-      <c r="H18" s="77"/>
-      <c r="I18" s="78"/>
-      <c r="J18" s="78"/>
-      <c r="K18" s="78"/>
-      <c r="L18" s="78"/>
-      <c r="M18" s="79"/>
-      <c r="N18" s="74"/>
-      <c r="O18" s="75"/>
-      <c r="P18" s="76"/>
+      <c r="C18" s="176"/>
+      <c r="D18" s="176"/>
+      <c r="E18" s="176"/>
+      <c r="F18" s="176"/>
+      <c r="G18" s="176"/>
+      <c r="H18" s="173"/>
+      <c r="I18" s="174"/>
+      <c r="J18" s="174"/>
+      <c r="K18" s="174"/>
+      <c r="L18" s="174"/>
+      <c r="M18" s="175"/>
+      <c r="N18" s="189"/>
+      <c r="O18" s="190"/>
+      <c r="P18" s="191"/>
       <c r="Q18" s="43"/>
-      <c r="R18" s="82"/>
-      <c r="S18" s="82"/>
+      <c r="R18" s="188"/>
+      <c r="S18" s="188"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="43"/>
       <c r="B19" s="43"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="93"/>
-      <c r="F19" s="93"/>
-      <c r="G19" s="93"/>
-      <c r="H19" s="77"/>
-      <c r="I19" s="78"/>
-      <c r="J19" s="78"/>
-      <c r="K19" s="78"/>
-      <c r="L19" s="78"/>
-      <c r="M19" s="79"/>
-      <c r="N19" s="74"/>
-      <c r="O19" s="75"/>
-      <c r="P19" s="76"/>
+      <c r="C19" s="176"/>
+      <c r="D19" s="176"/>
+      <c r="E19" s="176"/>
+      <c r="F19" s="176"/>
+      <c r="G19" s="176"/>
+      <c r="H19" s="173"/>
+      <c r="I19" s="174"/>
+      <c r="J19" s="174"/>
+      <c r="K19" s="174"/>
+      <c r="L19" s="174"/>
+      <c r="M19" s="175"/>
+      <c r="N19" s="189"/>
+      <c r="O19" s="190"/>
+      <c r="P19" s="191"/>
       <c r="Q19" s="43"/>
-      <c r="R19" s="82"/>
-      <c r="S19" s="82"/>
+      <c r="R19" s="188"/>
+      <c r="S19" s="188"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="43"/>
       <c r="B20" s="43"/>
-      <c r="C20" s="93"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="93"/>
-      <c r="F20" s="93"/>
-      <c r="G20" s="93"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="78"/>
-      <c r="J20" s="78"/>
-      <c r="K20" s="78"/>
-      <c r="L20" s="78"/>
-      <c r="M20" s="79"/>
-      <c r="N20" s="74"/>
-      <c r="O20" s="75"/>
-      <c r="P20" s="76"/>
+      <c r="C20" s="176"/>
+      <c r="D20" s="176"/>
+      <c r="E20" s="176"/>
+      <c r="F20" s="176"/>
+      <c r="G20" s="176"/>
+      <c r="H20" s="173"/>
+      <c r="I20" s="174"/>
+      <c r="J20" s="174"/>
+      <c r="K20" s="174"/>
+      <c r="L20" s="174"/>
+      <c r="M20" s="175"/>
+      <c r="N20" s="189"/>
+      <c r="O20" s="190"/>
+      <c r="P20" s="191"/>
       <c r="Q20" s="43"/>
-      <c r="R20" s="82"/>
-      <c r="S20" s="82"/>
+      <c r="R20" s="188"/>
+      <c r="S20" s="188"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="43"/>
       <c r="B21" s="43"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="93"/>
-      <c r="E21" s="93"/>
-      <c r="F21" s="93"/>
-      <c r="G21" s="93"/>
-      <c r="H21" s="77"/>
-      <c r="I21" s="78"/>
-      <c r="J21" s="78"/>
-      <c r="K21" s="78"/>
-      <c r="L21" s="78"/>
-      <c r="M21" s="79"/>
-      <c r="N21" s="74"/>
-      <c r="O21" s="75"/>
-      <c r="P21" s="76"/>
+      <c r="C21" s="176"/>
+      <c r="D21" s="176"/>
+      <c r="E21" s="176"/>
+      <c r="F21" s="176"/>
+      <c r="G21" s="176"/>
+      <c r="H21" s="173"/>
+      <c r="I21" s="174"/>
+      <c r="J21" s="174"/>
+      <c r="K21" s="174"/>
+      <c r="L21" s="174"/>
+      <c r="M21" s="175"/>
+      <c r="N21" s="189"/>
+      <c r="O21" s="190"/>
+      <c r="P21" s="191"/>
       <c r="Q21" s="43"/>
-      <c r="R21" s="82"/>
-      <c r="S21" s="82"/>
+      <c r="R21" s="188"/>
+      <c r="S21" s="188"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="43"/>
       <c r="B22" s="43"/>
-      <c r="C22" s="93"/>
-      <c r="D22" s="93"/>
-      <c r="E22" s="93"/>
-      <c r="F22" s="93"/>
-      <c r="G22" s="93"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="78"/>
-      <c r="J22" s="78"/>
-      <c r="K22" s="78"/>
-      <c r="L22" s="78"/>
-      <c r="M22" s="79"/>
-      <c r="N22" s="74"/>
-      <c r="O22" s="75"/>
-      <c r="P22" s="76"/>
+      <c r="C22" s="176"/>
+      <c r="D22" s="176"/>
+      <c r="E22" s="176"/>
+      <c r="F22" s="176"/>
+      <c r="G22" s="176"/>
+      <c r="H22" s="173"/>
+      <c r="I22" s="174"/>
+      <c r="J22" s="174"/>
+      <c r="K22" s="174"/>
+      <c r="L22" s="174"/>
+      <c r="M22" s="175"/>
+      <c r="N22" s="189"/>
+      <c r="O22" s="190"/>
+      <c r="P22" s="191"/>
       <c r="Q22" s="43"/>
-      <c r="R22" s="82"/>
-      <c r="S22" s="82"/>
+      <c r="R22" s="188"/>
+      <c r="S22" s="188"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="43"/>
       <c r="B23" s="43"/>
-      <c r="C23" s="93"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="93"/>
-      <c r="F23" s="93"/>
-      <c r="G23" s="93"/>
-      <c r="H23" s="77"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="78"/>
-      <c r="K23" s="78"/>
-      <c r="L23" s="78"/>
-      <c r="M23" s="79"/>
-      <c r="N23" s="74"/>
-      <c r="O23" s="75"/>
-      <c r="P23" s="76"/>
+      <c r="C23" s="176"/>
+      <c r="D23" s="176"/>
+      <c r="E23" s="176"/>
+      <c r="F23" s="176"/>
+      <c r="G23" s="176"/>
+      <c r="H23" s="173"/>
+      <c r="I23" s="174"/>
+      <c r="J23" s="174"/>
+      <c r="K23" s="174"/>
+      <c r="L23" s="174"/>
+      <c r="M23" s="175"/>
+      <c r="N23" s="189"/>
+      <c r="O23" s="190"/>
+      <c r="P23" s="191"/>
       <c r="Q23" s="43"/>
-      <c r="R23" s="82"/>
-      <c r="S23" s="82"/>
+      <c r="R23" s="188"/>
+      <c r="S23" s="188"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="43"/>
       <c r="B24" s="43"/>
-      <c r="C24" s="93"/>
-      <c r="D24" s="93"/>
-      <c r="E24" s="93"/>
-      <c r="F24" s="93"/>
-      <c r="G24" s="93"/>
-      <c r="H24" s="77"/>
-      <c r="I24" s="78"/>
-      <c r="J24" s="78"/>
-      <c r="K24" s="78"/>
-      <c r="L24" s="78"/>
-      <c r="M24" s="79"/>
-      <c r="N24" s="74"/>
-      <c r="O24" s="75"/>
-      <c r="P24" s="76"/>
+      <c r="C24" s="176"/>
+      <c r="D24" s="176"/>
+      <c r="E24" s="176"/>
+      <c r="F24" s="176"/>
+      <c r="G24" s="176"/>
+      <c r="H24" s="173"/>
+      <c r="I24" s="174"/>
+      <c r="J24" s="174"/>
+      <c r="K24" s="174"/>
+      <c r="L24" s="174"/>
+      <c r="M24" s="175"/>
+      <c r="N24" s="189"/>
+      <c r="O24" s="190"/>
+      <c r="P24" s="191"/>
       <c r="Q24" s="43"/>
-      <c r="R24" s="82"/>
-      <c r="S24" s="82"/>
+      <c r="R24" s="188"/>
+      <c r="S24" s="188"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="43"/>
       <c r="B25" s="43"/>
-      <c r="C25" s="93"/>
-      <c r="D25" s="93"/>
-      <c r="E25" s="93"/>
-      <c r="F25" s="93"/>
-      <c r="G25" s="93"/>
-      <c r="H25" s="77"/>
-      <c r="I25" s="78"/>
-      <c r="J25" s="78"/>
-      <c r="K25" s="78"/>
-      <c r="L25" s="78"/>
-      <c r="M25" s="79"/>
-      <c r="N25" s="74"/>
-      <c r="O25" s="75"/>
-      <c r="P25" s="76"/>
+      <c r="C25" s="176"/>
+      <c r="D25" s="176"/>
+      <c r="E25" s="176"/>
+      <c r="F25" s="176"/>
+      <c r="G25" s="176"/>
+      <c r="H25" s="173"/>
+      <c r="I25" s="174"/>
+      <c r="J25" s="174"/>
+      <c r="K25" s="174"/>
+      <c r="L25" s="174"/>
+      <c r="M25" s="175"/>
+      <c r="N25" s="189"/>
+      <c r="O25" s="190"/>
+      <c r="P25" s="191"/>
       <c r="Q25" s="43"/>
-      <c r="R25" s="82"/>
-      <c r="S25" s="82"/>
+      <c r="R25" s="188"/>
+      <c r="S25" s="188"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="43"/>
       <c r="B26" s="43"/>
-      <c r="C26" s="93"/>
-      <c r="D26" s="93"/>
-      <c r="E26" s="93"/>
-      <c r="F26" s="93"/>
-      <c r="G26" s="93"/>
-      <c r="H26" s="77"/>
-      <c r="I26" s="78"/>
-      <c r="J26" s="78"/>
-      <c r="K26" s="78"/>
-      <c r="L26" s="78"/>
-      <c r="M26" s="79"/>
-      <c r="N26" s="74"/>
-      <c r="O26" s="75"/>
-      <c r="P26" s="76"/>
+      <c r="C26" s="176"/>
+      <c r="D26" s="176"/>
+      <c r="E26" s="176"/>
+      <c r="F26" s="176"/>
+      <c r="G26" s="176"/>
+      <c r="H26" s="173"/>
+      <c r="I26" s="174"/>
+      <c r="J26" s="174"/>
+      <c r="K26" s="174"/>
+      <c r="L26" s="174"/>
+      <c r="M26" s="175"/>
+      <c r="N26" s="189"/>
+      <c r="O26" s="190"/>
+      <c r="P26" s="191"/>
       <c r="Q26" s="43"/>
-      <c r="R26" s="82"/>
-      <c r="S26" s="82"/>
+      <c r="R26" s="188"/>
+      <c r="S26" s="188"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="43"/>
       <c r="B27" s="43"/>
-      <c r="C27" s="93"/>
-      <c r="D27" s="93"/>
-      <c r="E27" s="93"/>
-      <c r="F27" s="93"/>
-      <c r="G27" s="93"/>
-      <c r="H27" s="77"/>
-      <c r="I27" s="78"/>
-      <c r="J27" s="78"/>
-      <c r="K27" s="78"/>
-      <c r="L27" s="78"/>
-      <c r="M27" s="79"/>
-      <c r="N27" s="74"/>
-      <c r="O27" s="75"/>
-      <c r="P27" s="76"/>
+      <c r="C27" s="176"/>
+      <c r="D27" s="176"/>
+      <c r="E27" s="176"/>
+      <c r="F27" s="176"/>
+      <c r="G27" s="176"/>
+      <c r="H27" s="173"/>
+      <c r="I27" s="174"/>
+      <c r="J27" s="174"/>
+      <c r="K27" s="174"/>
+      <c r="L27" s="174"/>
+      <c r="M27" s="175"/>
+      <c r="N27" s="189"/>
+      <c r="O27" s="190"/>
+      <c r="P27" s="191"/>
       <c r="Q27" s="43"/>
-      <c r="R27" s="82"/>
-      <c r="S27" s="82"/>
+      <c r="R27" s="188"/>
+      <c r="S27" s="188"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="43"/>
       <c r="B28" s="43"/>
-      <c r="C28" s="93"/>
-      <c r="D28" s="93"/>
-      <c r="E28" s="93"/>
-      <c r="F28" s="93"/>
-      <c r="G28" s="93"/>
-      <c r="H28" s="77"/>
-      <c r="I28" s="78"/>
-      <c r="J28" s="78"/>
-      <c r="K28" s="78"/>
-      <c r="L28" s="78"/>
-      <c r="M28" s="79"/>
-      <c r="N28" s="74"/>
-      <c r="O28" s="75"/>
-      <c r="P28" s="76"/>
+      <c r="C28" s="176"/>
+      <c r="D28" s="176"/>
+      <c r="E28" s="176"/>
+      <c r="F28" s="176"/>
+      <c r="G28" s="176"/>
+      <c r="H28" s="173"/>
+      <c r="I28" s="174"/>
+      <c r="J28" s="174"/>
+      <c r="K28" s="174"/>
+      <c r="L28" s="174"/>
+      <c r="M28" s="175"/>
+      <c r="N28" s="189"/>
+      <c r="O28" s="190"/>
+      <c r="P28" s="191"/>
       <c r="Q28" s="43"/>
-      <c r="R28" s="82"/>
-      <c r="S28" s="82"/>
+      <c r="R28" s="188"/>
+      <c r="S28" s="188"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="43"/>
       <c r="B29" s="43"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="93"/>
-      <c r="E29" s="93"/>
-      <c r="F29" s="93"/>
-      <c r="G29" s="93"/>
-      <c r="H29" s="77"/>
-      <c r="I29" s="78"/>
-      <c r="J29" s="78"/>
-      <c r="K29" s="78"/>
-      <c r="L29" s="78"/>
-      <c r="M29" s="79"/>
-      <c r="N29" s="74"/>
-      <c r="O29" s="75"/>
-      <c r="P29" s="76"/>
+      <c r="C29" s="176"/>
+      <c r="D29" s="176"/>
+      <c r="E29" s="176"/>
+      <c r="F29" s="176"/>
+      <c r="G29" s="176"/>
+      <c r="H29" s="173"/>
+      <c r="I29" s="174"/>
+      <c r="J29" s="174"/>
+      <c r="K29" s="174"/>
+      <c r="L29" s="174"/>
+      <c r="M29" s="175"/>
+      <c r="N29" s="189"/>
+      <c r="O29" s="190"/>
+      <c r="P29" s="191"/>
       <c r="Q29" s="43"/>
-      <c r="R29" s="82"/>
-      <c r="S29" s="82"/>
+      <c r="R29" s="188"/>
+      <c r="S29" s="188"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="43"/>
       <c r="B30" s="43"/>
-      <c r="C30" s="93"/>
-      <c r="D30" s="93"/>
-      <c r="E30" s="93"/>
-      <c r="F30" s="93"/>
-      <c r="G30" s="93"/>
-      <c r="H30" s="77"/>
-      <c r="I30" s="78"/>
-      <c r="J30" s="78"/>
-      <c r="K30" s="78"/>
-      <c r="L30" s="78"/>
-      <c r="M30" s="79"/>
-      <c r="N30" s="74"/>
-      <c r="O30" s="75"/>
-      <c r="P30" s="76"/>
+      <c r="C30" s="176"/>
+      <c r="D30" s="176"/>
+      <c r="E30" s="176"/>
+      <c r="F30" s="176"/>
+      <c r="G30" s="176"/>
+      <c r="H30" s="173"/>
+      <c r="I30" s="174"/>
+      <c r="J30" s="174"/>
+      <c r="K30" s="174"/>
+      <c r="L30" s="174"/>
+      <c r="M30" s="175"/>
+      <c r="N30" s="189"/>
+      <c r="O30" s="190"/>
+      <c r="P30" s="191"/>
       <c r="Q30" s="43"/>
-      <c r="R30" s="82"/>
-      <c r="S30" s="82"/>
+      <c r="R30" s="188"/>
+      <c r="S30" s="188"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="43"/>
       <c r="B31" s="43"/>
-      <c r="C31" s="93"/>
-      <c r="D31" s="93"/>
-      <c r="E31" s="93"/>
-      <c r="F31" s="93"/>
-      <c r="G31" s="93"/>
-      <c r="H31" s="77"/>
-      <c r="I31" s="78"/>
-      <c r="J31" s="78"/>
-      <c r="K31" s="78"/>
-      <c r="L31" s="78"/>
-      <c r="M31" s="79"/>
-      <c r="N31" s="74"/>
-      <c r="O31" s="75"/>
-      <c r="P31" s="76"/>
+      <c r="C31" s="176"/>
+      <c r="D31" s="176"/>
+      <c r="E31" s="176"/>
+      <c r="F31" s="176"/>
+      <c r="G31" s="176"/>
+      <c r="H31" s="173"/>
+      <c r="I31" s="174"/>
+      <c r="J31" s="174"/>
+      <c r="K31" s="174"/>
+      <c r="L31" s="174"/>
+      <c r="M31" s="175"/>
+      <c r="N31" s="189"/>
+      <c r="O31" s="190"/>
+      <c r="P31" s="191"/>
       <c r="Q31" s="43"/>
-      <c r="R31" s="82"/>
-      <c r="S31" s="82"/>
+      <c r="R31" s="188"/>
+      <c r="S31" s="188"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="43"/>
       <c r="B32" s="43"/>
-      <c r="C32" s="93"/>
-      <c r="D32" s="93"/>
-      <c r="E32" s="93"/>
-      <c r="F32" s="93"/>
-      <c r="G32" s="93"/>
-      <c r="H32" s="77"/>
-      <c r="I32" s="78"/>
-      <c r="J32" s="78"/>
-      <c r="K32" s="78"/>
-      <c r="L32" s="78"/>
-      <c r="M32" s="79"/>
-      <c r="N32" s="74"/>
-      <c r="O32" s="75"/>
-      <c r="P32" s="76"/>
+      <c r="C32" s="176"/>
+      <c r="D32" s="176"/>
+      <c r="E32" s="176"/>
+      <c r="F32" s="176"/>
+      <c r="G32" s="176"/>
+      <c r="H32" s="173"/>
+      <c r="I32" s="174"/>
+      <c r="J32" s="174"/>
+      <c r="K32" s="174"/>
+      <c r="L32" s="174"/>
+      <c r="M32" s="175"/>
+      <c r="N32" s="189"/>
+      <c r="O32" s="190"/>
+      <c r="P32" s="191"/>
       <c r="Q32" s="43"/>
-      <c r="R32" s="82"/>
-      <c r="S32" s="82"/>
+      <c r="R32" s="188"/>
+      <c r="S32" s="188"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="43"/>
       <c r="B33" s="43"/>
-      <c r="C33" s="93"/>
-      <c r="D33" s="93"/>
-      <c r="E33" s="93"/>
-      <c r="F33" s="93"/>
-      <c r="G33" s="93"/>
-      <c r="H33" s="77"/>
-      <c r="I33" s="78"/>
-      <c r="J33" s="78"/>
-      <c r="K33" s="78"/>
-      <c r="L33" s="78"/>
-      <c r="M33" s="79"/>
-      <c r="N33" s="74"/>
-      <c r="O33" s="75"/>
-      <c r="P33" s="76"/>
+      <c r="C33" s="176"/>
+      <c r="D33" s="176"/>
+      <c r="E33" s="176"/>
+      <c r="F33" s="176"/>
+      <c r="G33" s="176"/>
+      <c r="H33" s="173"/>
+      <c r="I33" s="174"/>
+      <c r="J33" s="174"/>
+      <c r="K33" s="174"/>
+      <c r="L33" s="174"/>
+      <c r="M33" s="175"/>
+      <c r="N33" s="189"/>
+      <c r="O33" s="190"/>
+      <c r="P33" s="191"/>
       <c r="Q33" s="43"/>
-      <c r="R33" s="82"/>
-      <c r="S33" s="82"/>
+      <c r="R33" s="188"/>
+      <c r="S33" s="188"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="43"/>
       <c r="B34" s="43"/>
-      <c r="C34" s="93"/>
-      <c r="D34" s="93"/>
-      <c r="E34" s="93"/>
-      <c r="F34" s="93"/>
-      <c r="G34" s="93"/>
-      <c r="H34" s="77"/>
-      <c r="I34" s="78"/>
-      <c r="J34" s="78"/>
-      <c r="K34" s="78"/>
-      <c r="L34" s="78"/>
-      <c r="M34" s="79"/>
-      <c r="N34" s="74"/>
-      <c r="O34" s="75"/>
-      <c r="P34" s="76"/>
+      <c r="C34" s="176"/>
+      <c r="D34" s="176"/>
+      <c r="E34" s="176"/>
+      <c r="F34" s="176"/>
+      <c r="G34" s="176"/>
+      <c r="H34" s="173"/>
+      <c r="I34" s="174"/>
+      <c r="J34" s="174"/>
+      <c r="K34" s="174"/>
+      <c r="L34" s="174"/>
+      <c r="M34" s="175"/>
+      <c r="N34" s="189"/>
+      <c r="O34" s="190"/>
+      <c r="P34" s="191"/>
       <c r="Q34" s="43"/>
-      <c r="R34" s="82"/>
-      <c r="S34" s="82"/>
+      <c r="R34" s="188"/>
+      <c r="S34" s="188"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="43"/>
       <c r="B35" s="43"/>
-      <c r="C35" s="93"/>
-      <c r="D35" s="93"/>
-      <c r="E35" s="93"/>
-      <c r="F35" s="93"/>
-      <c r="G35" s="93"/>
-      <c r="H35" s="77"/>
-      <c r="I35" s="78"/>
-      <c r="J35" s="78"/>
-      <c r="K35" s="78"/>
-      <c r="L35" s="78"/>
-      <c r="M35" s="79"/>
-      <c r="N35" s="74"/>
-      <c r="O35" s="75"/>
-      <c r="P35" s="76"/>
+      <c r="C35" s="176"/>
+      <c r="D35" s="176"/>
+      <c r="E35" s="176"/>
+      <c r="F35" s="176"/>
+      <c r="G35" s="176"/>
+      <c r="H35" s="173"/>
+      <c r="I35" s="174"/>
+      <c r="J35" s="174"/>
+      <c r="K35" s="174"/>
+      <c r="L35" s="174"/>
+      <c r="M35" s="175"/>
+      <c r="N35" s="189"/>
+      <c r="O35" s="190"/>
+      <c r="P35" s="191"/>
       <c r="Q35" s="43"/>
-      <c r="R35" s="82"/>
-      <c r="S35" s="82"/>
+      <c r="R35" s="188"/>
+      <c r="S35" s="188"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="43"/>
       <c r="B36" s="43"/>
-      <c r="C36" s="93"/>
-      <c r="D36" s="93"/>
-      <c r="E36" s="93"/>
-      <c r="F36" s="93"/>
-      <c r="G36" s="93"/>
-      <c r="H36" s="77"/>
-      <c r="I36" s="78"/>
-      <c r="J36" s="78"/>
-      <c r="K36" s="78"/>
-      <c r="L36" s="78"/>
-      <c r="M36" s="79"/>
-      <c r="N36" s="74"/>
-      <c r="O36" s="75"/>
-      <c r="P36" s="76"/>
+      <c r="C36" s="176"/>
+      <c r="D36" s="176"/>
+      <c r="E36" s="176"/>
+      <c r="F36" s="176"/>
+      <c r="G36" s="176"/>
+      <c r="H36" s="173"/>
+      <c r="I36" s="174"/>
+      <c r="J36" s="174"/>
+      <c r="K36" s="174"/>
+      <c r="L36" s="174"/>
+      <c r="M36" s="175"/>
+      <c r="N36" s="189"/>
+      <c r="O36" s="190"/>
+      <c r="P36" s="191"/>
       <c r="Q36" s="43"/>
-      <c r="R36" s="82"/>
-      <c r="S36" s="82"/>
+      <c r="R36" s="188"/>
+      <c r="S36" s="188"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="43"/>
       <c r="B37" s="43"/>
-      <c r="C37" s="93"/>
-      <c r="D37" s="93"/>
-      <c r="E37" s="93"/>
-      <c r="F37" s="93"/>
-      <c r="G37" s="93"/>
-      <c r="H37" s="77"/>
-      <c r="I37" s="78"/>
-      <c r="J37" s="78"/>
-      <c r="K37" s="78"/>
-      <c r="L37" s="78"/>
-      <c r="M37" s="79"/>
-      <c r="N37" s="74"/>
-      <c r="O37" s="75"/>
-      <c r="P37" s="76"/>
+      <c r="C37" s="176"/>
+      <c r="D37" s="176"/>
+      <c r="E37" s="176"/>
+      <c r="F37" s="176"/>
+      <c r="G37" s="176"/>
+      <c r="H37" s="173"/>
+      <c r="I37" s="174"/>
+      <c r="J37" s="174"/>
+      <c r="K37" s="174"/>
+      <c r="L37" s="174"/>
+      <c r="M37" s="175"/>
+      <c r="N37" s="189"/>
+      <c r="O37" s="190"/>
+      <c r="P37" s="191"/>
       <c r="Q37" s="43"/>
-      <c r="R37" s="82"/>
-      <c r="S37" s="82"/>
+      <c r="R37" s="188"/>
+      <c r="S37" s="188"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="43"/>
       <c r="B38" s="43"/>
-      <c r="C38" s="93"/>
-      <c r="D38" s="93"/>
-      <c r="E38" s="93"/>
-      <c r="F38" s="93"/>
-      <c r="G38" s="93"/>
-      <c r="H38" s="77"/>
-      <c r="I38" s="78"/>
-      <c r="J38" s="78"/>
-      <c r="K38" s="78"/>
-      <c r="L38" s="78"/>
-      <c r="M38" s="79"/>
-      <c r="N38" s="74"/>
-      <c r="O38" s="75"/>
-      <c r="P38" s="76"/>
+      <c r="C38" s="176"/>
+      <c r="D38" s="176"/>
+      <c r="E38" s="176"/>
+      <c r="F38" s="176"/>
+      <c r="G38" s="176"/>
+      <c r="H38" s="173"/>
+      <c r="I38" s="174"/>
+      <c r="J38" s="174"/>
+      <c r="K38" s="174"/>
+      <c r="L38" s="174"/>
+      <c r="M38" s="175"/>
+      <c r="N38" s="189"/>
+      <c r="O38" s="190"/>
+      <c r="P38" s="191"/>
       <c r="Q38" s="43"/>
-      <c r="R38" s="82"/>
-      <c r="S38" s="82"/>
+      <c r="R38" s="188"/>
+      <c r="S38" s="188"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="43"/>
       <c r="B39" s="43"/>
-      <c r="C39" s="93"/>
-      <c r="D39" s="93"/>
-      <c r="E39" s="93"/>
-      <c r="F39" s="93"/>
-      <c r="G39" s="93"/>
-      <c r="H39" s="77"/>
-      <c r="I39" s="78"/>
-      <c r="J39" s="78"/>
-      <c r="K39" s="78"/>
-      <c r="L39" s="78"/>
-      <c r="M39" s="79"/>
-      <c r="N39" s="74"/>
-      <c r="O39" s="75"/>
-      <c r="P39" s="76"/>
+      <c r="C39" s="176"/>
+      <c r="D39" s="176"/>
+      <c r="E39" s="176"/>
+      <c r="F39" s="176"/>
+      <c r="G39" s="176"/>
+      <c r="H39" s="173"/>
+      <c r="I39" s="174"/>
+      <c r="J39" s="174"/>
+      <c r="K39" s="174"/>
+      <c r="L39" s="174"/>
+      <c r="M39" s="175"/>
+      <c r="N39" s="189"/>
+      <c r="O39" s="190"/>
+      <c r="P39" s="191"/>
       <c r="Q39" s="43"/>
-      <c r="R39" s="82"/>
-      <c r="S39" s="82"/>
+      <c r="R39" s="188"/>
+      <c r="S39" s="188"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="43"/>
       <c r="B40" s="43"/>
-      <c r="C40" s="93"/>
-      <c r="D40" s="93"/>
-      <c r="E40" s="93"/>
-      <c r="F40" s="93"/>
-      <c r="G40" s="93"/>
-      <c r="H40" s="77"/>
-      <c r="I40" s="78"/>
-      <c r="J40" s="78"/>
-      <c r="K40" s="78"/>
-      <c r="L40" s="78"/>
-      <c r="M40" s="79"/>
-      <c r="N40" s="74"/>
-      <c r="O40" s="75"/>
-      <c r="P40" s="76"/>
+      <c r="C40" s="176"/>
+      <c r="D40" s="176"/>
+      <c r="E40" s="176"/>
+      <c r="F40" s="176"/>
+      <c r="G40" s="176"/>
+      <c r="H40" s="173"/>
+      <c r="I40" s="174"/>
+      <c r="J40" s="174"/>
+      <c r="K40" s="174"/>
+      <c r="L40" s="174"/>
+      <c r="M40" s="175"/>
+      <c r="N40" s="189"/>
+      <c r="O40" s="190"/>
+      <c r="P40" s="191"/>
       <c r="Q40" s="43"/>
-      <c r="R40" s="82"/>
-      <c r="S40" s="82"/>
+      <c r="R40" s="188"/>
+      <c r="S40" s="188"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="43"/>
       <c r="B41" s="43"/>
-      <c r="C41" s="93"/>
-      <c r="D41" s="93"/>
-      <c r="E41" s="93"/>
-      <c r="F41" s="93"/>
-      <c r="G41" s="93"/>
-      <c r="H41" s="77"/>
-      <c r="I41" s="78"/>
-      <c r="J41" s="78"/>
-      <c r="K41" s="78"/>
-      <c r="L41" s="78"/>
-      <c r="M41" s="79"/>
-      <c r="N41" s="74"/>
-      <c r="O41" s="75"/>
-      <c r="P41" s="76"/>
+      <c r="C41" s="176"/>
+      <c r="D41" s="176"/>
+      <c r="E41" s="176"/>
+      <c r="F41" s="176"/>
+      <c r="G41" s="176"/>
+      <c r="H41" s="173"/>
+      <c r="I41" s="174"/>
+      <c r="J41" s="174"/>
+      <c r="K41" s="174"/>
+      <c r="L41" s="174"/>
+      <c r="M41" s="175"/>
+      <c r="N41" s="189"/>
+      <c r="O41" s="190"/>
+      <c r="P41" s="191"/>
       <c r="Q41" s="43"/>
-      <c r="R41" s="82"/>
-      <c r="S41" s="82"/>
+      <c r="R41" s="188"/>
+      <c r="S41" s="188"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="43"/>
       <c r="B42" s="43"/>
-      <c r="C42" s="93"/>
-      <c r="D42" s="93"/>
-      <c r="E42" s="93"/>
-      <c r="F42" s="93"/>
-      <c r="G42" s="93"/>
-      <c r="H42" s="77"/>
-      <c r="I42" s="78"/>
-      <c r="J42" s="78"/>
-      <c r="K42" s="78"/>
-      <c r="L42" s="78"/>
-      <c r="M42" s="79"/>
-      <c r="N42" s="74"/>
-      <c r="O42" s="75"/>
-      <c r="P42" s="76"/>
+      <c r="C42" s="176"/>
+      <c r="D42" s="176"/>
+      <c r="E42" s="176"/>
+      <c r="F42" s="176"/>
+      <c r="G42" s="176"/>
+      <c r="H42" s="173"/>
+      <c r="I42" s="174"/>
+      <c r="J42" s="174"/>
+      <c r="K42" s="174"/>
+      <c r="L42" s="174"/>
+      <c r="M42" s="175"/>
+      <c r="N42" s="189"/>
+      <c r="O42" s="190"/>
+      <c r="P42" s="191"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="82"/>
-      <c r="S42" s="82"/>
+      <c r="R42" s="188"/>
+      <c r="S42" s="188"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="43"/>
       <c r="B43" s="43"/>
-      <c r="C43" s="93"/>
-      <c r="D43" s="93"/>
-      <c r="E43" s="93"/>
-      <c r="F43" s="93"/>
-      <c r="G43" s="93"/>
-      <c r="H43" s="77"/>
-      <c r="I43" s="78"/>
-      <c r="J43" s="78"/>
-      <c r="K43" s="78"/>
-      <c r="L43" s="78"/>
-      <c r="M43" s="79"/>
-      <c r="N43" s="74"/>
-      <c r="O43" s="75"/>
-      <c r="P43" s="76"/>
+      <c r="C43" s="176"/>
+      <c r="D43" s="176"/>
+      <c r="E43" s="176"/>
+      <c r="F43" s="176"/>
+      <c r="G43" s="176"/>
+      <c r="H43" s="173"/>
+      <c r="I43" s="174"/>
+      <c r="J43" s="174"/>
+      <c r="K43" s="174"/>
+      <c r="L43" s="174"/>
+      <c r="M43" s="175"/>
+      <c r="N43" s="189"/>
+      <c r="O43" s="190"/>
+      <c r="P43" s="191"/>
       <c r="Q43" s="43"/>
-      <c r="R43" s="82"/>
-      <c r="S43" s="82"/>
+      <c r="R43" s="188"/>
+      <c r="S43" s="188"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="43"/>
       <c r="B44" s="43"/>
-      <c r="C44" s="93"/>
-      <c r="D44" s="93"/>
-      <c r="E44" s="93"/>
-      <c r="F44" s="93"/>
-      <c r="G44" s="93"/>
-      <c r="H44" s="77"/>
-      <c r="I44" s="78"/>
-      <c r="J44" s="78"/>
-      <c r="K44" s="78"/>
-      <c r="L44" s="78"/>
-      <c r="M44" s="79"/>
-      <c r="N44" s="74"/>
-      <c r="O44" s="75"/>
-      <c r="P44" s="76"/>
+      <c r="C44" s="176"/>
+      <c r="D44" s="176"/>
+      <c r="E44" s="176"/>
+      <c r="F44" s="176"/>
+      <c r="G44" s="176"/>
+      <c r="H44" s="173"/>
+      <c r="I44" s="174"/>
+      <c r="J44" s="174"/>
+      <c r="K44" s="174"/>
+      <c r="L44" s="174"/>
+      <c r="M44" s="175"/>
+      <c r="N44" s="189"/>
+      <c r="O44" s="190"/>
+      <c r="P44" s="191"/>
       <c r="Q44" s="43"/>
-      <c r="R44" s="82"/>
-      <c r="S44" s="82"/>
+      <c r="R44" s="188"/>
+      <c r="S44" s="188"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="43"/>
       <c r="B45" s="43"/>
-      <c r="C45" s="93"/>
-      <c r="D45" s="93"/>
-      <c r="E45" s="93"/>
-      <c r="F45" s="93"/>
-      <c r="G45" s="93"/>
-      <c r="H45" s="77"/>
-      <c r="I45" s="78"/>
-      <c r="J45" s="78"/>
-      <c r="K45" s="78"/>
-      <c r="L45" s="78"/>
-      <c r="M45" s="79"/>
-      <c r="N45" s="74"/>
-      <c r="O45" s="75"/>
-      <c r="P45" s="76"/>
+      <c r="C45" s="176"/>
+      <c r="D45" s="176"/>
+      <c r="E45" s="176"/>
+      <c r="F45" s="176"/>
+      <c r="G45" s="176"/>
+      <c r="H45" s="173"/>
+      <c r="I45" s="174"/>
+      <c r="J45" s="174"/>
+      <c r="K45" s="174"/>
+      <c r="L45" s="174"/>
+      <c r="M45" s="175"/>
+      <c r="N45" s="189"/>
+      <c r="O45" s="190"/>
+      <c r="P45" s="191"/>
       <c r="Q45" s="43"/>
-      <c r="R45" s="82"/>
-      <c r="S45" s="82"/>
+      <c r="R45" s="188"/>
+      <c r="S45" s="188"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="43"/>
       <c r="B46" s="43"/>
-      <c r="C46" s="93"/>
-      <c r="D46" s="93"/>
-      <c r="E46" s="93"/>
-      <c r="F46" s="93"/>
-      <c r="G46" s="93"/>
-      <c r="H46" s="77"/>
-      <c r="I46" s="78"/>
-      <c r="J46" s="78"/>
-      <c r="K46" s="78"/>
-      <c r="L46" s="78"/>
-      <c r="M46" s="79"/>
-      <c r="N46" s="74"/>
-      <c r="O46" s="75"/>
-      <c r="P46" s="76"/>
+      <c r="C46" s="176"/>
+      <c r="D46" s="176"/>
+      <c r="E46" s="176"/>
+      <c r="F46" s="176"/>
+      <c r="G46" s="176"/>
+      <c r="H46" s="173"/>
+      <c r="I46" s="174"/>
+      <c r="J46" s="174"/>
+      <c r="K46" s="174"/>
+      <c r="L46" s="174"/>
+      <c r="M46" s="175"/>
+      <c r="N46" s="189"/>
+      <c r="O46" s="190"/>
+      <c r="P46" s="191"/>
       <c r="Q46" s="43"/>
-      <c r="R46" s="82"/>
-      <c r="S46" s="82"/>
+      <c r="R46" s="188"/>
+      <c r="S46" s="188"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="43"/>
       <c r="B47" s="43"/>
-      <c r="C47" s="93"/>
-      <c r="D47" s="93"/>
-      <c r="E47" s="93"/>
-      <c r="F47" s="93"/>
-      <c r="G47" s="93"/>
-      <c r="H47" s="77"/>
-      <c r="I47" s="78"/>
-      <c r="J47" s="78"/>
-      <c r="K47" s="78"/>
-      <c r="L47" s="78"/>
-      <c r="M47" s="79"/>
-      <c r="N47" s="74"/>
-      <c r="O47" s="75"/>
-      <c r="P47" s="76"/>
+      <c r="C47" s="176"/>
+      <c r="D47" s="176"/>
+      <c r="E47" s="176"/>
+      <c r="F47" s="176"/>
+      <c r="G47" s="176"/>
+      <c r="H47" s="173"/>
+      <c r="I47" s="174"/>
+      <c r="J47" s="174"/>
+      <c r="K47" s="174"/>
+      <c r="L47" s="174"/>
+      <c r="M47" s="175"/>
+      <c r="N47" s="189"/>
+      <c r="O47" s="190"/>
+      <c r="P47" s="191"/>
       <c r="Q47" s="43"/>
-      <c r="R47" s="82"/>
-      <c r="S47" s="82"/>
+      <c r="R47" s="188"/>
+      <c r="S47" s="188"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="43"/>
       <c r="B48" s="43"/>
-      <c r="C48" s="93"/>
-      <c r="D48" s="93"/>
-      <c r="E48" s="93"/>
-      <c r="F48" s="93"/>
-      <c r="G48" s="93"/>
-      <c r="H48" s="77"/>
-      <c r="I48" s="78"/>
-      <c r="J48" s="78"/>
-      <c r="K48" s="78"/>
-      <c r="L48" s="78"/>
-      <c r="M48" s="79"/>
-      <c r="N48" s="74"/>
-      <c r="O48" s="75"/>
-      <c r="P48" s="76"/>
+      <c r="C48" s="176"/>
+      <c r="D48" s="176"/>
+      <c r="E48" s="176"/>
+      <c r="F48" s="176"/>
+      <c r="G48" s="176"/>
+      <c r="H48" s="173"/>
+      <c r="I48" s="174"/>
+      <c r="J48" s="174"/>
+      <c r="K48" s="174"/>
+      <c r="L48" s="174"/>
+      <c r="M48" s="175"/>
+      <c r="N48" s="189"/>
+      <c r="O48" s="190"/>
+      <c r="P48" s="191"/>
       <c r="Q48" s="43"/>
-      <c r="R48" s="82"/>
-      <c r="S48" s="82"/>
+      <c r="R48" s="188"/>
+      <c r="S48" s="188"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="43"/>
       <c r="B49" s="43"/>
-      <c r="C49" s="93"/>
-      <c r="D49" s="93"/>
-      <c r="E49" s="93"/>
-      <c r="F49" s="93"/>
-      <c r="G49" s="93"/>
-      <c r="H49" s="77"/>
-      <c r="I49" s="78"/>
-      <c r="J49" s="78"/>
-      <c r="K49" s="78"/>
-      <c r="L49" s="78"/>
-      <c r="M49" s="79"/>
-      <c r="N49" s="74"/>
-      <c r="O49" s="75"/>
-      <c r="P49" s="76"/>
+      <c r="C49" s="176"/>
+      <c r="D49" s="176"/>
+      <c r="E49" s="176"/>
+      <c r="F49" s="176"/>
+      <c r="G49" s="176"/>
+      <c r="H49" s="173"/>
+      <c r="I49" s="174"/>
+      <c r="J49" s="174"/>
+      <c r="K49" s="174"/>
+      <c r="L49" s="174"/>
+      <c r="M49" s="175"/>
+      <c r="N49" s="189"/>
+      <c r="O49" s="190"/>
+      <c r="P49" s="191"/>
       <c r="Q49" s="43"/>
-      <c r="R49" s="82"/>
-      <c r="S49" s="82"/>
+      <c r="R49" s="188"/>
+      <c r="S49" s="188"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="43"/>
       <c r="B50" s="43"/>
-      <c r="C50" s="93"/>
-      <c r="D50" s="93"/>
-      <c r="E50" s="93"/>
-      <c r="F50" s="93"/>
-      <c r="G50" s="93"/>
-      <c r="H50" s="77"/>
-      <c r="I50" s="78"/>
-      <c r="J50" s="78"/>
-      <c r="K50" s="78"/>
-      <c r="L50" s="78"/>
-      <c r="M50" s="79"/>
-      <c r="N50" s="74"/>
-      <c r="O50" s="75"/>
-      <c r="P50" s="76"/>
+      <c r="C50" s="176"/>
+      <c r="D50" s="176"/>
+      <c r="E50" s="176"/>
+      <c r="F50" s="176"/>
+      <c r="G50" s="176"/>
+      <c r="H50" s="173"/>
+      <c r="I50" s="174"/>
+      <c r="J50" s="174"/>
+      <c r="K50" s="174"/>
+      <c r="L50" s="174"/>
+      <c r="M50" s="175"/>
+      <c r="N50" s="189"/>
+      <c r="O50" s="190"/>
+      <c r="P50" s="191"/>
       <c r="Q50" s="43"/>
-      <c r="R50" s="82"/>
-      <c r="S50" s="82"/>
+      <c r="R50" s="188"/>
+      <c r="S50" s="188"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="43"/>
       <c r="B51" s="43"/>
-      <c r="C51" s="93"/>
-      <c r="D51" s="93"/>
-      <c r="E51" s="93"/>
-      <c r="F51" s="93"/>
-      <c r="G51" s="93"/>
-      <c r="H51" s="77"/>
-      <c r="I51" s="78"/>
-      <c r="J51" s="78"/>
-      <c r="K51" s="78"/>
-      <c r="L51" s="78"/>
-      <c r="M51" s="79"/>
-      <c r="N51" s="74"/>
-      <c r="O51" s="75"/>
-      <c r="P51" s="76"/>
+      <c r="C51" s="176"/>
+      <c r="D51" s="176"/>
+      <c r="E51" s="176"/>
+      <c r="F51" s="176"/>
+      <c r="G51" s="176"/>
+      <c r="H51" s="173"/>
+      <c r="I51" s="174"/>
+      <c r="J51" s="174"/>
+      <c r="K51" s="174"/>
+      <c r="L51" s="174"/>
+      <c r="M51" s="175"/>
+      <c r="N51" s="189"/>
+      <c r="O51" s="190"/>
+      <c r="P51" s="191"/>
       <c r="Q51" s="43"/>
-      <c r="R51" s="82"/>
-      <c r="S51" s="82"/>
+      <c r="R51" s="188"/>
+      <c r="S51" s="188"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="43"/>
       <c r="B52" s="43"/>
-      <c r="C52" s="93"/>
-      <c r="D52" s="93"/>
-      <c r="E52" s="93"/>
-      <c r="F52" s="93"/>
-      <c r="G52" s="93"/>
-      <c r="H52" s="77"/>
-      <c r="I52" s="78"/>
-      <c r="J52" s="78"/>
-      <c r="K52" s="78"/>
-      <c r="L52" s="78"/>
-      <c r="M52" s="79"/>
-      <c r="N52" s="74"/>
-      <c r="O52" s="75"/>
-      <c r="P52" s="76"/>
+      <c r="C52" s="176"/>
+      <c r="D52" s="176"/>
+      <c r="E52" s="176"/>
+      <c r="F52" s="176"/>
+      <c r="G52" s="176"/>
+      <c r="H52" s="173"/>
+      <c r="I52" s="174"/>
+      <c r="J52" s="174"/>
+      <c r="K52" s="174"/>
+      <c r="L52" s="174"/>
+      <c r="M52" s="175"/>
+      <c r="N52" s="189"/>
+      <c r="O52" s="190"/>
+      <c r="P52" s="191"/>
       <c r="Q52" s="43"/>
-      <c r="R52" s="82"/>
-      <c r="S52" s="82"/>
+      <c r="R52" s="188"/>
+      <c r="S52" s="188"/>
     </row>
   </sheetData>
   <mergeCells count="205">
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F1:M1"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="H4:M4"/>
+    <mergeCell ref="H5:M5"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H38:M38"/>
     <mergeCell ref="H45:M45"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="C45:G45"/>
@@ -13186,187 +13367,6 @@
     <mergeCell ref="H34:M34"/>
     <mergeCell ref="H35:M35"/>
     <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F1:M1"/>
-    <mergeCell ref="F2:M2"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="H4:M4"/>
-    <mergeCell ref="H5:M5"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="N29:P29"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>

--- a/プロジェクト型演習_成果物_TasBo_ログイン.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_ログイン.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER110\Desktop\プロジェクト演習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68AED1EF-2936-4620-A850-C7929BFDE03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFB1A43-EFDE-493B-A9B7-1CBAA35F9465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙 " sheetId="11" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="115">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -516,10 +516,6 @@
     <phoneticPr fontId="20"/>
   </si>
   <si>
-    <t>selectAll()</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>login()</t>
     <phoneticPr fontId="12"/>
   </si>
@@ -532,26 +528,6 @@
       <t>カエ</t>
     </rPh>
     <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>メソッドを使用すると、List&lt;UserBean&gt;型の
-戻り値が返ってくること</t>
-    <rPh sb="5" eb="7">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>ガタ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>モド</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>チ</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>カエ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>チーム名「チームTasBo」</t>
@@ -1980,6 +1956,126 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="58" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="59" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="60" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="60" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1992,15 +2088,9 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2019,9 +2109,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2103,24 +2190,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2288,99 +2357,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="58" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="59" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="60" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="60" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2991,23 +2967,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>109482</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>153275</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>240862</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>49</xdr:col>
-      <xdr:colOff>135412</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>28277</xdr:rowOff>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>87585</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>146288</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A82D598-DE60-37AA-E09B-07A4213A64F5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCACCA4E-2373-5BEC-EA7D-BFA0565EA1E1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3023,8 +2999,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="503620" y="10937327"/>
-          <a:ext cx="9288171" cy="1790950"/>
+          <a:off x="0" y="2310086"/>
+          <a:ext cx="7970344" cy="8390340"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3035,23 +3011,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>153274</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>229914</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>186119</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>69504</xdr:rowOff>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>108683</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>212836</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D8E5256-7736-96F8-8483-017CBBF30962}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFF82781-ADF2-BB52-9C98-FD6EF0A439D0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3067,8 +3043,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="153274" y="2299138"/>
-          <a:ext cx="7324397" cy="9693038"/>
+          <a:off x="394138" y="11605172"/>
+          <a:ext cx="9173855" cy="1581371"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3352,85 +3328,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1" thickBot="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1" thickTop="1">
-      <c r="C2" s="113" t="s">
+      <c r="C2" s="106" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
-      <c r="J2" s="114"/>
-      <c r="K2" s="114"/>
-      <c r="L2" s="114"/>
-      <c r="M2" s="114"/>
-      <c r="N2" s="114"/>
-      <c r="O2" s="114"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="107"/>
+      <c r="J2" s="107"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="107"/>
+      <c r="M2" s="107"/>
+      <c r="N2" s="107"/>
+      <c r="O2" s="107"/>
       <c r="P2" s="66"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
-      <c r="K3" s="83"/>
-      <c r="L3" s="83"/>
-      <c r="M3" s="83"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="105"/>
+      <c r="I3" s="105"/>
+      <c r="J3" s="105"/>
+      <c r="K3" s="105"/>
+      <c r="L3" s="105"/>
+      <c r="M3" s="105"/>
+      <c r="N3" s="105"/>
+      <c r="O3" s="105"/>
       <c r="P3" s="66"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="83"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="105"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="105"/>
+      <c r="L4" s="105"/>
+      <c r="M4" s="105"/>
+      <c r="N4" s="105"/>
+      <c r="O4" s="105"/>
       <c r="P4" s="66"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-      <c r="J5" s="83"/>
-      <c r="K5" s="83"/>
-      <c r="L5" s="83"/>
-      <c r="M5" s="83"/>
-      <c r="N5" s="83"/>
-      <c r="O5" s="83"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="105"/>
+      <c r="K5" s="105"/>
+      <c r="L5" s="105"/>
+      <c r="M5" s="105"/>
+      <c r="N5" s="105"/>
+      <c r="O5" s="105"/>
       <c r="P5" s="66"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1" thickBot="1">
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="83"/>
-      <c r="L6" s="83"/>
-      <c r="M6" s="83"/>
-      <c r="N6" s="83"/>
-      <c r="O6" s="83"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="105"/>
+      <c r="I6" s="105"/>
+      <c r="J6" s="105"/>
+      <c r="K6" s="105"/>
+      <c r="L6" s="105"/>
+      <c r="M6" s="105"/>
+      <c r="N6" s="105"/>
+      <c r="O6" s="105"/>
       <c r="P6" s="66"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1" thickTop="1">
@@ -3450,46 +3426,46 @@
       <c r="P7" s="66"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="115" t="s">
-        <v>105</v>
-      </c>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="83"/>
-      <c r="K8" s="83"/>
-      <c r="L8" s="83"/>
-      <c r="M8" s="83"/>
+      <c r="E8" s="108" t="s">
+        <v>103</v>
+      </c>
+      <c r="F8" s="105"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="105"/>
+      <c r="I8" s="105"/>
+      <c r="J8" s="105"/>
+      <c r="K8" s="105"/>
+      <c r="L8" s="105"/>
+      <c r="M8" s="105"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="111" t="s">
+      <c r="G13" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="74"/>
-      <c r="I13" s="116">
+      <c r="H13" s="103"/>
+      <c r="I13" s="109">
         <v>46175</v>
       </c>
-      <c r="J13" s="76"/>
-      <c r="K13" s="74"/>
+      <c r="J13" s="102"/>
+      <c r="K13" s="103"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="111"/>
-      <c r="H14" s="74"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="76"/>
-      <c r="K14" s="74"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="103"/>
+      <c r="I14" s="101"/>
+      <c r="J14" s="102"/>
+      <c r="K14" s="103"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="111"/>
-      <c r="H15" s="74"/>
-      <c r="I15" s="111"/>
-      <c r="J15" s="76"/>
-      <c r="K15" s="74"/>
+      <c r="G15" s="101"/>
+      <c r="H15" s="103"/>
+      <c r="I15" s="101"/>
+      <c r="J15" s="102"/>
+      <c r="K15" s="103"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="65"/>
@@ -3498,13 +3474,13 @@
       <c r="J16" s="65"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="112" t="s">
-        <v>104</v>
-      </c>
-      <c r="H17" s="83"/>
-      <c r="I17" s="83"/>
-      <c r="J17" s="83"/>
-      <c r="K17" s="83"/>
+      <c r="G17" s="104" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" s="105"/>
+      <c r="I17" s="105"/>
+      <c r="J17" s="105"/>
+      <c r="K17" s="105"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4519,19 +4495,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="91" t="s">
+      <c r="B1" s="118"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="90"/>
-      <c r="F1" s="91" t="s">
+      <c r="E1" s="127"/>
+      <c r="F1" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="90"/>
+      <c r="G1" s="127"/>
       <c r="H1" s="69" t="s">
         <v>5</v>
       </c>
@@ -4543,192 +4519,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="92" t="s">
+      <c r="A2" s="120"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="121"/>
+      <c r="D2" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" s="130"/>
+      <c r="F2" s="129" t="s">
+        <v>107</v>
+      </c>
+      <c r="G2" s="130"/>
+      <c r="H2" s="133">
+        <v>46175</v>
+      </c>
+      <c r="I2" s="136" t="s">
+        <v>106</v>
+      </c>
+      <c r="J2" s="110"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="120"/>
+      <c r="B3" s="105"/>
+      <c r="C3" s="121"/>
+      <c r="D3" s="131"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="134"/>
+      <c r="I3" s="134"/>
+      <c r="J3" s="111"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="122"/>
+      <c r="B4" s="123"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="132"/>
+      <c r="E4" s="124"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="135"/>
+      <c r="I4" s="135"/>
+      <c r="J4" s="112"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="125" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="126"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="137" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="138"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="114" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="102"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="139" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="102"/>
+      <c r="I6" s="102"/>
+      <c r="J6" s="116"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="114" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="102"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="102"/>
+      <c r="J7" s="116"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="114" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="102"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="115" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="93"/>
-      <c r="F2" s="92" t="s">
+      <c r="E8" s="102"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="102"/>
+      <c r="H8" s="102"/>
+      <c r="I8" s="102"/>
+      <c r="J8" s="116"/>
+    </row>
+    <row r="9" spans="1:10" ht="106.5" customHeight="1">
+      <c r="A9" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="113" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="103"/>
+      <c r="D9" s="115" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="102"/>
+      <c r="F9" s="102"/>
+      <c r="G9" s="102"/>
+      <c r="H9" s="102"/>
+      <c r="I9" s="102"/>
+      <c r="J9" s="116"/>
+    </row>
+    <row r="10" spans="1:10" ht="126.75" customHeight="1">
+      <c r="A10" s="141"/>
+      <c r="B10" s="113" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="103"/>
+      <c r="D10" s="115" t="s">
+        <v>114</v>
+      </c>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="102"/>
+      <c r="J10" s="116"/>
+    </row>
+    <row r="11" spans="1:10" ht="51.75" customHeight="1">
+      <c r="A11" s="142"/>
+      <c r="B11" s="113" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="103"/>
+      <c r="D11" s="115" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="102"/>
+      <c r="I11" s="102"/>
+      <c r="J11" s="116"/>
+    </row>
+    <row r="12" spans="1:10" ht="48.75" customHeight="1">
+      <c r="A12" s="114" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="102"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="115" t="s">
         <v>109</v>
       </c>
-      <c r="G2" s="93"/>
-      <c r="H2" s="96">
-        <v>46175</v>
-      </c>
-      <c r="I2" s="99" t="s">
-        <v>108</v>
-      </c>
-      <c r="J2" s="70"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="82"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="71"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="85"/>
-      <c r="B4" s="86"/>
-      <c r="C4" s="87"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="72"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="88" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="89"/>
-      <c r="C5" s="90"/>
-      <c r="D5" s="100" t="s">
-        <v>107</v>
-      </c>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="101"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="76"/>
-      <c r="C6" s="74"/>
-      <c r="D6" s="102" t="s">
-        <v>114</v>
-      </c>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="78"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="75" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="76"/>
-      <c r="C7" s="74"/>
-      <c r="D7" s="102" t="s">
-        <v>113</v>
-      </c>
-      <c r="E7" s="76"/>
-      <c r="F7" s="76"/>
-      <c r="G7" s="76"/>
-      <c r="H7" s="76"/>
-      <c r="I7" s="76"/>
-      <c r="J7" s="78"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="75" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="76"/>
-      <c r="C8" s="74"/>
-      <c r="D8" s="77" t="s">
-        <v>112</v>
-      </c>
-      <c r="E8" s="76"/>
-      <c r="F8" s="76"/>
-      <c r="G8" s="76"/>
-      <c r="H8" s="76"/>
-      <c r="I8" s="76"/>
-      <c r="J8" s="78"/>
-    </row>
-    <row r="9" spans="1:10" ht="106.5" customHeight="1">
-      <c r="A9" s="103" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="73" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="74"/>
-      <c r="D9" s="77" t="s">
-        <v>115</v>
-      </c>
-      <c r="E9" s="76"/>
-      <c r="F9" s="76"/>
-      <c r="G9" s="76"/>
-      <c r="H9" s="76"/>
-      <c r="I9" s="76"/>
-      <c r="J9" s="78"/>
-    </row>
-    <row r="10" spans="1:10" ht="126.75" customHeight="1">
-      <c r="A10" s="104"/>
-      <c r="B10" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="74"/>
-      <c r="D10" s="77" t="s">
-        <v>116</v>
-      </c>
-      <c r="E10" s="76"/>
-      <c r="F10" s="76"/>
-      <c r="G10" s="76"/>
-      <c r="H10" s="76"/>
-      <c r="I10" s="76"/>
-      <c r="J10" s="78"/>
-    </row>
-    <row r="11" spans="1:10" ht="51.75" customHeight="1">
-      <c r="A11" s="105"/>
-      <c r="B11" s="73" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="74"/>
-      <c r="D11" s="77" t="s">
-        <v>106</v>
-      </c>
-      <c r="E11" s="76"/>
-      <c r="F11" s="76"/>
-      <c r="G11" s="76"/>
-      <c r="H11" s="76"/>
-      <c r="I11" s="76"/>
-      <c r="J11" s="78"/>
-    </row>
-    <row r="12" spans="1:10" ht="48.75" customHeight="1">
-      <c r="A12" s="75" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="76"/>
-      <c r="C12" s="74"/>
-      <c r="D12" s="77" t="s">
-        <v>111</v>
-      </c>
-      <c r="E12" s="76"/>
-      <c r="F12" s="76"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="76"/>
-      <c r="I12" s="76"/>
-      <c r="J12" s="78"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="102"/>
+      <c r="I12" s="102"/>
+      <c r="J12" s="116"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="109" t="s">
+      <c r="A13" s="146" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="107"/>
-      <c r="C13" s="110"/>
-      <c r="D13" s="106"/>
-      <c r="E13" s="107"/>
-      <c r="F13" s="107"/>
-      <c r="G13" s="107"/>
-      <c r="H13" s="107"/>
-      <c r="I13" s="107"/>
-      <c r="J13" s="108"/>
+      <c r="B13" s="144"/>
+      <c r="C13" s="147"/>
+      <c r="D13" s="143"/>
+      <c r="E13" s="144"/>
+      <c r="F13" s="144"/>
+      <c r="G13" s="144"/>
+      <c r="H13" s="144"/>
+      <c r="I13" s="144"/>
+      <c r="J13" s="145"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5764,19 +5740,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="154" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="132" t="s">
+      <c r="B1" s="155"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="163" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="133"/>
-      <c r="F1" s="132" t="s">
+      <c r="E1" s="164"/>
+      <c r="F1" s="163" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="133"/>
+      <c r="G1" s="164"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -5788,40 +5764,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="126"/>
-      <c r="B2" s="127"/>
-      <c r="C2" s="128"/>
-      <c r="D2" s="134"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="117"/>
-      <c r="I2" s="117"/>
-      <c r="J2" s="120"/>
+      <c r="A2" s="157"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="165"/>
+      <c r="E2" s="166"/>
+      <c r="F2" s="165"/>
+      <c r="G2" s="166"/>
+      <c r="H2" s="148"/>
+      <c r="I2" s="148"/>
+      <c r="J2" s="151"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="126"/>
-      <c r="B3" s="127"/>
-      <c r="C3" s="128"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="128"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="128"/>
-      <c r="H3" s="118"/>
-      <c r="I3" s="118"/>
-      <c r="J3" s="121"/>
+      <c r="A3" s="157"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="167"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="167"/>
+      <c r="G3" s="159"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="152"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="129"/>
-      <c r="B4" s="130"/>
-      <c r="C4" s="131"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="131"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="122"/>
+      <c r="A4" s="160"/>
+      <c r="B4" s="161"/>
+      <c r="C4" s="162"/>
+      <c r="D4" s="168"/>
+      <c r="E4" s="162"/>
+      <c r="F4" s="168"/>
+      <c r="G4" s="162"/>
+      <c r="H4" s="150"/>
+      <c r="I4" s="150"/>
+      <c r="J4" s="153"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="5"/>
@@ -7177,19 +7153,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="154" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="132" t="s">
+      <c r="B1" s="155"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="163" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="133"/>
-      <c r="F1" s="132" t="s">
+      <c r="E1" s="164"/>
+      <c r="F1" s="163" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="133"/>
+      <c r="G1" s="164"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -7201,48 +7177,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="126"/>
-      <c r="B2" s="127"/>
-      <c r="C2" s="128"/>
-      <c r="D2" s="134" t="s">
+      <c r="A2" s="157"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="165" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="135"/>
-      <c r="F2" s="134" t="s">
+      <c r="E2" s="166"/>
+      <c r="F2" s="165" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="135"/>
-      <c r="H2" s="138">
+      <c r="G2" s="166"/>
+      <c r="H2" s="169">
         <v>46182</v>
       </c>
-      <c r="I2" s="117" t="s">
+      <c r="I2" s="148" t="s">
         <v>52</v>
       </c>
-      <c r="J2" s="120"/>
+      <c r="J2" s="151"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="126"/>
-      <c r="B3" s="127"/>
-      <c r="C3" s="128"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="128"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="128"/>
-      <c r="H3" s="118"/>
-      <c r="I3" s="118"/>
-      <c r="J3" s="121"/>
+      <c r="A3" s="157"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="167"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="167"/>
+      <c r="G3" s="159"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="152"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="129"/>
-      <c r="B4" s="130"/>
-      <c r="C4" s="131"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="131"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="122"/>
+      <c r="A4" s="160"/>
+      <c r="B4" s="161"/>
+      <c r="C4" s="162"/>
+      <c r="D4" s="168"/>
+      <c r="E4" s="162"/>
+      <c r="F4" s="168"/>
+      <c r="G4" s="162"/>
+      <c r="H4" s="150"/>
+      <c r="I4" s="150"/>
+      <c r="J4" s="153"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="5"/>
@@ -8593,19 +8569,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="154" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="132" t="s">
+      <c r="B1" s="155"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="163" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="133"/>
-      <c r="F1" s="132" t="s">
+      <c r="E1" s="164"/>
+      <c r="F1" s="163" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="133"/>
+      <c r="G1" s="164"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -8617,192 +8593,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="126"/>
-      <c r="B2" s="127"/>
-      <c r="C2" s="128"/>
-      <c r="D2" s="134" t="s">
+      <c r="A2" s="157"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="165" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="135"/>
-      <c r="F2" s="134" t="s">
+      <c r="E2" s="166"/>
+      <c r="F2" s="165" t="s">
         <v>54</v>
       </c>
-      <c r="G2" s="135"/>
-      <c r="H2" s="139">
+      <c r="G2" s="166"/>
+      <c r="H2" s="170">
         <v>46175</v>
       </c>
-      <c r="I2" s="117" t="s">
+      <c r="I2" s="148" t="s">
         <v>52</v>
       </c>
-      <c r="J2" s="120"/>
+      <c r="J2" s="151"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="126"/>
-      <c r="B3" s="127"/>
-      <c r="C3" s="128"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="128"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="128"/>
-      <c r="H3" s="118"/>
-      <c r="I3" s="118"/>
-      <c r="J3" s="121"/>
+      <c r="A3" s="157"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="167"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="167"/>
+      <c r="G3" s="159"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="152"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="126"/>
-      <c r="B4" s="127"/>
-      <c r="C4" s="128"/>
-      <c r="D4" s="136"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="128"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="121"/>
+      <c r="A4" s="157"/>
+      <c r="B4" s="158"/>
+      <c r="C4" s="159"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="159"/>
+      <c r="F4" s="167"/>
+      <c r="G4" s="159"/>
+      <c r="H4" s="149"/>
+      <c r="I4" s="149"/>
+      <c r="J4" s="152"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="140" t="s">
+      <c r="A5" s="171" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="141"/>
-      <c r="C5" s="133"/>
-      <c r="D5" s="149" t="s">
+      <c r="B5" s="172"/>
+      <c r="C5" s="164"/>
+      <c r="D5" s="180" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="141"/>
-      <c r="F5" s="141"/>
-      <c r="G5" s="141"/>
-      <c r="H5" s="141"/>
-      <c r="I5" s="141"/>
-      <c r="J5" s="150"/>
+      <c r="E5" s="172"/>
+      <c r="F5" s="172"/>
+      <c r="G5" s="172"/>
+      <c r="H5" s="172"/>
+      <c r="I5" s="172"/>
+      <c r="J5" s="181"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="145" t="s">
+      <c r="A6" s="176" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="146"/>
-      <c r="C6" s="146"/>
-      <c r="D6" s="146"/>
-      <c r="E6" s="146"/>
-      <c r="F6" s="146"/>
-      <c r="G6" s="146"/>
-      <c r="H6" s="146"/>
-      <c r="I6" s="146"/>
-      <c r="J6" s="151"/>
+      <c r="B6" s="177"/>
+      <c r="C6" s="177"/>
+      <c r="D6" s="177"/>
+      <c r="E6" s="177"/>
+      <c r="F6" s="177"/>
+      <c r="G6" s="177"/>
+      <c r="H6" s="177"/>
+      <c r="I6" s="177"/>
+      <c r="J6" s="182"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="152" t="e" vm="1">
+      <c r="A7" s="183" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B7" s="153"/>
-      <c r="C7" s="153"/>
-      <c r="D7" s="153"/>
-      <c r="E7" s="153"/>
-      <c r="F7" s="153"/>
-      <c r="G7" s="153"/>
-      <c r="H7" s="153"/>
-      <c r="I7" s="153"/>
-      <c r="J7" s="154"/>
+      <c r="B7" s="184"/>
+      <c r="C7" s="184"/>
+      <c r="D7" s="184"/>
+      <c r="E7" s="184"/>
+      <c r="F7" s="184"/>
+      <c r="G7" s="184"/>
+      <c r="H7" s="184"/>
+      <c r="I7" s="184"/>
+      <c r="J7" s="185"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="126"/>
-      <c r="B8" s="127"/>
-      <c r="C8" s="127"/>
-      <c r="D8" s="127"/>
-      <c r="E8" s="127"/>
-      <c r="F8" s="127"/>
-      <c r="G8" s="127"/>
-      <c r="H8" s="127"/>
-      <c r="I8" s="127"/>
-      <c r="J8" s="155"/>
+      <c r="A8" s="157"/>
+      <c r="B8" s="158"/>
+      <c r="C8" s="158"/>
+      <c r="D8" s="158"/>
+      <c r="E8" s="158"/>
+      <c r="F8" s="158"/>
+      <c r="G8" s="158"/>
+      <c r="H8" s="158"/>
+      <c r="I8" s="158"/>
+      <c r="J8" s="186"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="126"/>
-      <c r="B9" s="127"/>
-      <c r="C9" s="127"/>
-      <c r="D9" s="127"/>
-      <c r="E9" s="127"/>
-      <c r="F9" s="127"/>
-      <c r="G9" s="127"/>
-      <c r="H9" s="127"/>
-      <c r="I9" s="127"/>
-      <c r="J9" s="155"/>
+      <c r="A9" s="157"/>
+      <c r="B9" s="158"/>
+      <c r="C9" s="158"/>
+      <c r="D9" s="158"/>
+      <c r="E9" s="158"/>
+      <c r="F9" s="158"/>
+      <c r="G9" s="158"/>
+      <c r="H9" s="158"/>
+      <c r="I9" s="158"/>
+      <c r="J9" s="186"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="126"/>
-      <c r="B10" s="127"/>
-      <c r="C10" s="127"/>
-      <c r="D10" s="127"/>
-      <c r="E10" s="127"/>
-      <c r="F10" s="127"/>
-      <c r="G10" s="127"/>
-      <c r="H10" s="127"/>
-      <c r="I10" s="127"/>
-      <c r="J10" s="155"/>
+      <c r="A10" s="157"/>
+      <c r="B10" s="158"/>
+      <c r="C10" s="158"/>
+      <c r="D10" s="158"/>
+      <c r="E10" s="158"/>
+      <c r="F10" s="158"/>
+      <c r="G10" s="158"/>
+      <c r="H10" s="158"/>
+      <c r="I10" s="158"/>
+      <c r="J10" s="186"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="126"/>
-      <c r="B11" s="127"/>
-      <c r="C11" s="127"/>
-      <c r="D11" s="127"/>
-      <c r="E11" s="127"/>
-      <c r="F11" s="127"/>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="127"/>
-      <c r="J11" s="155"/>
+      <c r="A11" s="157"/>
+      <c r="B11" s="158"/>
+      <c r="C11" s="158"/>
+      <c r="D11" s="158"/>
+      <c r="E11" s="158"/>
+      <c r="F11" s="158"/>
+      <c r="G11" s="158"/>
+      <c r="H11" s="158"/>
+      <c r="I11" s="158"/>
+      <c r="J11" s="186"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="126"/>
-      <c r="B12" s="127"/>
-      <c r="C12" s="127"/>
-      <c r="D12" s="127"/>
-      <c r="E12" s="127"/>
-      <c r="F12" s="127"/>
-      <c r="G12" s="127"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="127"/>
-      <c r="J12" s="155"/>
+      <c r="A12" s="157"/>
+      <c r="B12" s="158"/>
+      <c r="C12" s="158"/>
+      <c r="D12" s="158"/>
+      <c r="E12" s="158"/>
+      <c r="F12" s="158"/>
+      <c r="G12" s="158"/>
+      <c r="H12" s="158"/>
+      <c r="I12" s="158"/>
+      <c r="J12" s="186"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="126"/>
-      <c r="B13" s="127"/>
-      <c r="C13" s="127"/>
-      <c r="D13" s="127"/>
-      <c r="E13" s="127"/>
-      <c r="F13" s="127"/>
-      <c r="G13" s="127"/>
-      <c r="H13" s="127"/>
-      <c r="I13" s="127"/>
-      <c r="J13" s="155"/>
+      <c r="A13" s="157"/>
+      <c r="B13" s="158"/>
+      <c r="C13" s="158"/>
+      <c r="D13" s="158"/>
+      <c r="E13" s="158"/>
+      <c r="F13" s="158"/>
+      <c r="G13" s="158"/>
+      <c r="H13" s="158"/>
+      <c r="I13" s="158"/>
+      <c r="J13" s="186"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="145" t="s">
+      <c r="A14" s="176" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="146"/>
-      <c r="C14" s="146"/>
-      <c r="D14" s="146"/>
-      <c r="E14" s="146"/>
-      <c r="F14" s="146"/>
-      <c r="G14" s="146"/>
-      <c r="H14" s="146"/>
-      <c r="I14" s="146"/>
-      <c r="J14" s="151"/>
+      <c r="B14" s="177"/>
+      <c r="C14" s="177"/>
+      <c r="D14" s="177"/>
+      <c r="E14" s="177"/>
+      <c r="F14" s="177"/>
+      <c r="G14" s="177"/>
+      <c r="H14" s="177"/>
+      <c r="I14" s="177"/>
+      <c r="J14" s="182"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="145" t="s">
+      <c r="A15" s="176" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="146"/>
-      <c r="C15" s="147"/>
-      <c r="D15" s="156" t="s">
+      <c r="B15" s="177"/>
+      <c r="C15" s="178"/>
+      <c r="D15" s="187" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="146"/>
-      <c r="F15" s="146"/>
-      <c r="G15" s="146"/>
-      <c r="H15" s="147"/>
+      <c r="E15" s="177"/>
+      <c r="F15" s="177"/>
+      <c r="G15" s="177"/>
+      <c r="H15" s="178"/>
       <c r="I15" s="12" t="s">
         <v>25</v>
       </c>
@@ -8811,11 +8787,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="145" t="s">
+      <c r="A16" s="176" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="146"/>
-      <c r="C16" s="147"/>
+      <c r="B16" s="177"/>
+      <c r="C16" s="178"/>
       <c r="D16" s="12" t="s">
         <v>27</v>
       </c>
@@ -8828,18 +8804,18 @@
       <c r="G16" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="157" t="s">
+      <c r="H16" s="188" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="146"/>
-      <c r="J16" s="151"/>
+      <c r="I16" s="177"/>
+      <c r="J16" s="182"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="148">
+      <c r="A17" s="179">
         <v>1</v>
       </c>
-      <c r="B17" s="146"/>
-      <c r="C17" s="147"/>
+      <c r="B17" s="177"/>
+      <c r="C17" s="178"/>
       <c r="D17" s="14" t="s">
         <v>58</v>
       </c>
@@ -8850,16 +8826,16 @@
         <v>60</v>
       </c>
       <c r="G17" s="15"/>
-      <c r="H17" s="156"/>
-      <c r="I17" s="146"/>
-      <c r="J17" s="151"/>
+      <c r="H17" s="187"/>
+      <c r="I17" s="177"/>
+      <c r="J17" s="182"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="148">
+      <c r="A18" s="179">
         <v>2</v>
       </c>
-      <c r="B18" s="146"/>
-      <c r="C18" s="147"/>
+      <c r="B18" s="177"/>
+      <c r="C18" s="178"/>
       <c r="D18" s="14" t="s">
         <v>61</v>
       </c>
@@ -8870,16 +8846,16 @@
         <v>62</v>
       </c>
       <c r="G18" s="15"/>
-      <c r="H18" s="156"/>
-      <c r="I18" s="146"/>
-      <c r="J18" s="151"/>
+      <c r="H18" s="187"/>
+      <c r="I18" s="177"/>
+      <c r="J18" s="182"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="148">
+      <c r="A19" s="179">
         <v>3</v>
       </c>
-      <c r="B19" s="146"/>
-      <c r="C19" s="147"/>
+      <c r="B19" s="177"/>
+      <c r="C19" s="178"/>
       <c r="D19" s="14" t="s">
         <v>55</v>
       </c>
@@ -8890,16 +8866,16 @@
       <c r="G19" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="H19" s="156"/>
-      <c r="I19" s="146"/>
-      <c r="J19" s="151"/>
+      <c r="H19" s="187"/>
+      <c r="I19" s="177"/>
+      <c r="J19" s="182"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="148">
+      <c r="A20" s="179">
         <v>4</v>
       </c>
-      <c r="B20" s="146"/>
-      <c r="C20" s="147"/>
+      <c r="B20" s="177"/>
+      <c r="C20" s="178"/>
       <c r="D20" s="14" t="s">
         <v>64</v>
       </c>
@@ -8910,45 +8886,45 @@
       <c r="G20" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="H20" s="156"/>
-      <c r="I20" s="146"/>
-      <c r="J20" s="151"/>
+      <c r="H20" s="187"/>
+      <c r="I20" s="177"/>
+      <c r="J20" s="182"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="148"/>
-      <c r="B21" s="146"/>
-      <c r="C21" s="147"/>
+      <c r="A21" s="179"/>
+      <c r="B21" s="177"/>
+      <c r="C21" s="178"/>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
-      <c r="H21" s="156"/>
-      <c r="I21" s="146"/>
-      <c r="J21" s="151"/>
+      <c r="H21" s="187"/>
+      <c r="I21" s="177"/>
+      <c r="J21" s="182"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="148"/>
-      <c r="B22" s="146"/>
-      <c r="C22" s="147"/>
+      <c r="A22" s="179"/>
+      <c r="B22" s="177"/>
+      <c r="C22" s="178"/>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
-      <c r="H22" s="156"/>
-      <c r="I22" s="146"/>
-      <c r="J22" s="151"/>
+      <c r="H22" s="187"/>
+      <c r="I22" s="177"/>
+      <c r="J22" s="182"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="142"/>
-      <c r="B23" s="143"/>
-      <c r="C23" s="144"/>
+      <c r="A23" s="173"/>
+      <c r="B23" s="174"/>
+      <c r="C23" s="175"/>
       <c r="D23" s="16"/>
       <c r="E23" s="16"/>
       <c r="F23" s="17"/>
       <c r="G23" s="17"/>
-      <c r="H23" s="158"/>
-      <c r="I23" s="143"/>
-      <c r="J23" s="159"/>
+      <c r="H23" s="189"/>
+      <c r="I23" s="174"/>
+      <c r="J23" s="190"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9979,184 +9955,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="166" t="s">
+      <c r="A1" s="197" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="132" t="s">
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="163" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="132" t="s">
+      <c r="H1" s="172"/>
+      <c r="I1" s="172"/>
+      <c r="J1" s="164"/>
+      <c r="K1" s="163" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="133"/>
-      <c r="O1" s="132" t="s">
+      <c r="L1" s="172"/>
+      <c r="M1" s="172"/>
+      <c r="N1" s="164"/>
+      <c r="O1" s="163" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="133"/>
-      <c r="Q1" s="132" t="s">
+      <c r="P1" s="164"/>
+      <c r="Q1" s="163" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="133"/>
-      <c r="S1" s="132" t="s">
+      <c r="R1" s="164"/>
+      <c r="S1" s="163" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="150"/>
+      <c r="T1" s="181"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="126"/>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="134" t="s">
+      <c r="A2" s="157"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="165" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="153"/>
-      <c r="I2" s="153"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="134" t="s">
+      <c r="H2" s="184"/>
+      <c r="I2" s="184"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="165" t="s">
         <v>66</v>
       </c>
-      <c r="L2" s="153"/>
-      <c r="M2" s="153"/>
-      <c r="N2" s="135"/>
-      <c r="O2" s="164">
+      <c r="L2" s="184"/>
+      <c r="M2" s="184"/>
+      <c r="N2" s="166"/>
+      <c r="O2" s="195">
         <v>46182</v>
       </c>
-      <c r="P2" s="135"/>
-      <c r="Q2" s="134" t="s">
+      <c r="P2" s="166"/>
+      <c r="Q2" s="165" t="s">
         <v>67</v>
       </c>
-      <c r="R2" s="135"/>
-      <c r="S2" s="134"/>
-      <c r="T2" s="154"/>
+      <c r="R2" s="166"/>
+      <c r="S2" s="165"/>
+      <c r="T2" s="185"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="126"/>
-      <c r="B3" s="127"/>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="127"/>
-      <c r="F3" s="128"/>
-      <c r="G3" s="136"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="128"/>
-      <c r="K3" s="136"/>
-      <c r="L3" s="127"/>
-      <c r="M3" s="127"/>
-      <c r="N3" s="128"/>
-      <c r="O3" s="136"/>
-      <c r="P3" s="128"/>
-      <c r="Q3" s="136"/>
-      <c r="R3" s="128"/>
-      <c r="S3" s="136"/>
-      <c r="T3" s="155"/>
+      <c r="A3" s="157"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="167"/>
+      <c r="H3" s="158"/>
+      <c r="I3" s="158"/>
+      <c r="J3" s="159"/>
+      <c r="K3" s="167"/>
+      <c r="L3" s="158"/>
+      <c r="M3" s="158"/>
+      <c r="N3" s="159"/>
+      <c r="O3" s="167"/>
+      <c r="P3" s="159"/>
+      <c r="Q3" s="167"/>
+      <c r="R3" s="159"/>
+      <c r="S3" s="167"/>
+      <c r="T3" s="186"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="129"/>
-      <c r="B4" s="130"/>
-      <c r="C4" s="130"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="130"/>
-      <c r="F4" s="131"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="131"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="130"/>
-      <c r="M4" s="130"/>
-      <c r="N4" s="131"/>
-      <c r="O4" s="137"/>
-      <c r="P4" s="131"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="131"/>
-      <c r="S4" s="137"/>
-      <c r="T4" s="165"/>
+      <c r="A4" s="160"/>
+      <c r="B4" s="161"/>
+      <c r="C4" s="161"/>
+      <c r="D4" s="161"/>
+      <c r="E4" s="161"/>
+      <c r="F4" s="162"/>
+      <c r="G4" s="168"/>
+      <c r="H4" s="161"/>
+      <c r="I4" s="161"/>
+      <c r="J4" s="162"/>
+      <c r="K4" s="168"/>
+      <c r="L4" s="161"/>
+      <c r="M4" s="161"/>
+      <c r="N4" s="162"/>
+      <c r="O4" s="168"/>
+      <c r="P4" s="162"/>
+      <c r="Q4" s="168"/>
+      <c r="R4" s="162"/>
+      <c r="S4" s="168"/>
+      <c r="T4" s="196"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="140" t="s">
+      <c r="A5" s="171" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="141"/>
-      <c r="C5" s="141"/>
-      <c r="D5" s="141"/>
-      <c r="E5" s="141"/>
-      <c r="F5" s="133"/>
-      <c r="G5" s="167"/>
-      <c r="H5" s="141"/>
-      <c r="I5" s="141"/>
-      <c r="J5" s="141"/>
-      <c r="K5" s="141"/>
-      <c r="L5" s="141"/>
-      <c r="M5" s="141"/>
-      <c r="N5" s="141"/>
-      <c r="O5" s="141"/>
-      <c r="P5" s="141"/>
-      <c r="Q5" s="141"/>
-      <c r="R5" s="141"/>
-      <c r="S5" s="141"/>
-      <c r="T5" s="150"/>
+      <c r="B5" s="172"/>
+      <c r="C5" s="172"/>
+      <c r="D5" s="172"/>
+      <c r="E5" s="172"/>
+      <c r="F5" s="164"/>
+      <c r="G5" s="198"/>
+      <c r="H5" s="172"/>
+      <c r="I5" s="172"/>
+      <c r="J5" s="172"/>
+      <c r="K5" s="172"/>
+      <c r="L5" s="172"/>
+      <c r="M5" s="172"/>
+      <c r="N5" s="172"/>
+      <c r="O5" s="172"/>
+      <c r="P5" s="172"/>
+      <c r="Q5" s="172"/>
+      <c r="R5" s="172"/>
+      <c r="S5" s="172"/>
+      <c r="T5" s="181"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="145" t="s">
+      <c r="A6" s="176" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="146"/>
-      <c r="C6" s="146"/>
-      <c r="D6" s="146"/>
-      <c r="E6" s="146"/>
-      <c r="F6" s="147"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="146"/>
-      <c r="I6" s="146"/>
-      <c r="J6" s="146"/>
-      <c r="K6" s="146"/>
-      <c r="L6" s="146"/>
-      <c r="M6" s="146"/>
-      <c r="N6" s="146"/>
-      <c r="O6" s="146"/>
-      <c r="P6" s="146"/>
-      <c r="Q6" s="146"/>
-      <c r="R6" s="146"/>
-      <c r="S6" s="146"/>
-      <c r="T6" s="151"/>
+      <c r="B6" s="177"/>
+      <c r="C6" s="177"/>
+      <c r="D6" s="177"/>
+      <c r="E6" s="177"/>
+      <c r="F6" s="178"/>
+      <c r="G6" s="187"/>
+      <c r="H6" s="177"/>
+      <c r="I6" s="177"/>
+      <c r="J6" s="177"/>
+      <c r="K6" s="177"/>
+      <c r="L6" s="177"/>
+      <c r="M6" s="177"/>
+      <c r="N6" s="177"/>
+      <c r="O6" s="177"/>
+      <c r="P6" s="177"/>
+      <c r="Q6" s="177"/>
+      <c r="R6" s="177"/>
+      <c r="S6" s="177"/>
+      <c r="T6" s="182"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="145" t="s">
+      <c r="A7" s="176" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="146"/>
-      <c r="C7" s="146"/>
-      <c r="D7" s="146"/>
-      <c r="E7" s="146"/>
-      <c r="F7" s="147"/>
-      <c r="G7" s="156"/>
-      <c r="H7" s="146"/>
-      <c r="I7" s="146"/>
-      <c r="J7" s="146"/>
-      <c r="K7" s="146"/>
-      <c r="L7" s="146"/>
-      <c r="M7" s="146"/>
-      <c r="N7" s="146"/>
-      <c r="O7" s="146"/>
-      <c r="P7" s="146"/>
-      <c r="Q7" s="146"/>
-      <c r="R7" s="146"/>
-      <c r="S7" s="146"/>
-      <c r="T7" s="151"/>
+      <c r="B7" s="177"/>
+      <c r="C7" s="177"/>
+      <c r="D7" s="177"/>
+      <c r="E7" s="177"/>
+      <c r="F7" s="178"/>
+      <c r="G7" s="187"/>
+      <c r="H7" s="177"/>
+      <c r="I7" s="177"/>
+      <c r="J7" s="177"/>
+      <c r="K7" s="177"/>
+      <c r="L7" s="177"/>
+      <c r="M7" s="177"/>
+      <c r="N7" s="177"/>
+      <c r="O7" s="177"/>
+      <c r="P7" s="177"/>
+      <c r="Q7" s="177"/>
+      <c r="R7" s="177"/>
+      <c r="S7" s="177"/>
+      <c r="T7" s="182"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="5"/>
@@ -10355,37 +10331,37 @@
       <c r="T14" s="7"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="145" t="s">
+      <c r="A15" s="176" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="147"/>
-      <c r="C15" s="170" t="s">
+      <c r="B15" s="178"/>
+      <c r="C15" s="201" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="147"/>
-      <c r="E15" s="157" t="s">
+      <c r="D15" s="178"/>
+      <c r="E15" s="188" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="147"/>
-      <c r="G15" s="157" t="s">
+      <c r="F15" s="178"/>
+      <c r="G15" s="188" t="s">
         <v>43</v>
       </c>
-      <c r="H15" s="146"/>
-      <c r="I15" s="147"/>
-      <c r="J15" s="157" t="s">
+      <c r="H15" s="177"/>
+      <c r="I15" s="178"/>
+      <c r="J15" s="188" t="s">
         <v>44</v>
       </c>
-      <c r="K15" s="147"/>
-      <c r="L15" s="157" t="s">
+      <c r="K15" s="178"/>
+      <c r="L15" s="188" t="s">
         <v>45</v>
       </c>
-      <c r="M15" s="146"/>
-      <c r="N15" s="147"/>
-      <c r="O15" s="157" t="s">
+      <c r="M15" s="177"/>
+      <c r="N15" s="178"/>
+      <c r="O15" s="188" t="s">
         <v>46</v>
       </c>
-      <c r="P15" s="146"/>
-      <c r="Q15" s="147"/>
+      <c r="P15" s="177"/>
+      <c r="Q15" s="178"/>
       <c r="R15" s="12" t="s">
         <v>47</v>
       </c>
@@ -10397,25 +10373,25 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="168">
+      <c r="A16" s="199">
         <v>1</v>
       </c>
-      <c r="B16" s="147"/>
-      <c r="C16" s="169"/>
-      <c r="D16" s="147"/>
-      <c r="E16" s="169"/>
-      <c r="F16" s="147"/>
-      <c r="G16" s="160"/>
-      <c r="H16" s="146"/>
-      <c r="I16" s="147"/>
-      <c r="J16" s="160"/>
-      <c r="K16" s="147"/>
-      <c r="L16" s="162"/>
-      <c r="M16" s="146"/>
-      <c r="N16" s="147"/>
-      <c r="O16" s="162"/>
-      <c r="P16" s="146"/>
-      <c r="Q16" s="147"/>
+      <c r="B16" s="178"/>
+      <c r="C16" s="200"/>
+      <c r="D16" s="178"/>
+      <c r="E16" s="200"/>
+      <c r="F16" s="178"/>
+      <c r="G16" s="191"/>
+      <c r="H16" s="177"/>
+      <c r="I16" s="178"/>
+      <c r="J16" s="191"/>
+      <c r="K16" s="178"/>
+      <c r="L16" s="193"/>
+      <c r="M16" s="177"/>
+      <c r="N16" s="178"/>
+      <c r="O16" s="193"/>
+      <c r="P16" s="177"/>
+      <c r="Q16" s="178"/>
       <c r="R16" s="30"/>
       <c r="S16" s="30"/>
       <c r="T16" s="31"/>
@@ -10427,25 +10403,25 @@
       <c r="Z16" s="32"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="168">
+      <c r="A17" s="199">
         <v>2</v>
       </c>
-      <c r="B17" s="147"/>
-      <c r="C17" s="169"/>
-      <c r="D17" s="147"/>
-      <c r="E17" s="169"/>
-      <c r="F17" s="147"/>
-      <c r="G17" s="160"/>
-      <c r="H17" s="146"/>
-      <c r="I17" s="147"/>
-      <c r="J17" s="160"/>
-      <c r="K17" s="147"/>
-      <c r="L17" s="162"/>
-      <c r="M17" s="146"/>
-      <c r="N17" s="147"/>
-      <c r="O17" s="162"/>
-      <c r="P17" s="146"/>
-      <c r="Q17" s="147"/>
+      <c r="B17" s="178"/>
+      <c r="C17" s="200"/>
+      <c r="D17" s="178"/>
+      <c r="E17" s="200"/>
+      <c r="F17" s="178"/>
+      <c r="G17" s="191"/>
+      <c r="H17" s="177"/>
+      <c r="I17" s="178"/>
+      <c r="J17" s="191"/>
+      <c r="K17" s="178"/>
+      <c r="L17" s="193"/>
+      <c r="M17" s="177"/>
+      <c r="N17" s="178"/>
+      <c r="O17" s="193"/>
+      <c r="P17" s="177"/>
+      <c r="Q17" s="178"/>
       <c r="R17" s="30"/>
       <c r="S17" s="30"/>
       <c r="T17" s="31"/>
@@ -10457,23 +10433,23 @@
       <c r="Z17" s="32"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="168"/>
-      <c r="B18" s="147"/>
-      <c r="C18" s="169"/>
-      <c r="D18" s="147"/>
-      <c r="E18" s="169"/>
-      <c r="F18" s="147"/>
-      <c r="G18" s="160"/>
-      <c r="H18" s="146"/>
-      <c r="I18" s="147"/>
-      <c r="J18" s="160"/>
-      <c r="K18" s="147"/>
-      <c r="L18" s="162"/>
-      <c r="M18" s="146"/>
-      <c r="N18" s="147"/>
-      <c r="O18" s="162"/>
-      <c r="P18" s="146"/>
-      <c r="Q18" s="147"/>
+      <c r="A18" s="199"/>
+      <c r="B18" s="178"/>
+      <c r="C18" s="200"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="178"/>
+      <c r="G18" s="191"/>
+      <c r="H18" s="177"/>
+      <c r="I18" s="178"/>
+      <c r="J18" s="191"/>
+      <c r="K18" s="178"/>
+      <c r="L18" s="193"/>
+      <c r="M18" s="177"/>
+      <c r="N18" s="178"/>
+      <c r="O18" s="193"/>
+      <c r="P18" s="177"/>
+      <c r="Q18" s="178"/>
       <c r="R18" s="30"/>
       <c r="S18" s="30"/>
       <c r="T18" s="31"/>
@@ -10485,23 +10461,23 @@
       <c r="Z18" s="32"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="168"/>
-      <c r="B19" s="147"/>
-      <c r="C19" s="169"/>
-      <c r="D19" s="147"/>
-      <c r="E19" s="169"/>
-      <c r="F19" s="147"/>
-      <c r="G19" s="160"/>
-      <c r="H19" s="146"/>
-      <c r="I19" s="147"/>
-      <c r="J19" s="160"/>
-      <c r="K19" s="147"/>
-      <c r="L19" s="162"/>
-      <c r="M19" s="146"/>
-      <c r="N19" s="147"/>
-      <c r="O19" s="162"/>
-      <c r="P19" s="146"/>
-      <c r="Q19" s="147"/>
+      <c r="A19" s="199"/>
+      <c r="B19" s="178"/>
+      <c r="C19" s="200"/>
+      <c r="D19" s="178"/>
+      <c r="E19" s="200"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="191"/>
+      <c r="H19" s="177"/>
+      <c r="I19" s="178"/>
+      <c r="J19" s="191"/>
+      <c r="K19" s="178"/>
+      <c r="L19" s="193"/>
+      <c r="M19" s="177"/>
+      <c r="N19" s="178"/>
+      <c r="O19" s="193"/>
+      <c r="P19" s="177"/>
+      <c r="Q19" s="178"/>
       <c r="R19" s="30"/>
       <c r="S19" s="30"/>
       <c r="T19" s="31"/>
@@ -10513,23 +10489,23 @@
       <c r="Z19" s="32"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="168"/>
-      <c r="B20" s="147"/>
-      <c r="C20" s="169"/>
-      <c r="D20" s="147"/>
-      <c r="E20" s="169"/>
-      <c r="F20" s="147"/>
-      <c r="G20" s="160"/>
-      <c r="H20" s="146"/>
-      <c r="I20" s="147"/>
-      <c r="J20" s="160"/>
-      <c r="K20" s="147"/>
-      <c r="L20" s="162"/>
-      <c r="M20" s="146"/>
-      <c r="N20" s="147"/>
-      <c r="O20" s="162"/>
-      <c r="P20" s="146"/>
-      <c r="Q20" s="147"/>
+      <c r="A20" s="199"/>
+      <c r="B20" s="178"/>
+      <c r="C20" s="200"/>
+      <c r="D20" s="178"/>
+      <c r="E20" s="200"/>
+      <c r="F20" s="178"/>
+      <c r="G20" s="191"/>
+      <c r="H20" s="177"/>
+      <c r="I20" s="178"/>
+      <c r="J20" s="191"/>
+      <c r="K20" s="178"/>
+      <c r="L20" s="193"/>
+      <c r="M20" s="177"/>
+      <c r="N20" s="178"/>
+      <c r="O20" s="193"/>
+      <c r="P20" s="177"/>
+      <c r="Q20" s="178"/>
       <c r="R20" s="30"/>
       <c r="S20" s="30"/>
       <c r="T20" s="31"/>
@@ -10541,23 +10517,23 @@
       <c r="Z20" s="32"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="168"/>
-      <c r="B21" s="147"/>
-      <c r="C21" s="169"/>
-      <c r="D21" s="147"/>
-      <c r="E21" s="169"/>
-      <c r="F21" s="147"/>
-      <c r="G21" s="160"/>
-      <c r="H21" s="146"/>
-      <c r="I21" s="147"/>
-      <c r="J21" s="160"/>
-      <c r="K21" s="147"/>
-      <c r="L21" s="162"/>
-      <c r="M21" s="146"/>
-      <c r="N21" s="147"/>
-      <c r="O21" s="162"/>
-      <c r="P21" s="146"/>
-      <c r="Q21" s="147"/>
+      <c r="A21" s="199"/>
+      <c r="B21" s="178"/>
+      <c r="C21" s="200"/>
+      <c r="D21" s="178"/>
+      <c r="E21" s="200"/>
+      <c r="F21" s="178"/>
+      <c r="G21" s="191"/>
+      <c r="H21" s="177"/>
+      <c r="I21" s="178"/>
+      <c r="J21" s="191"/>
+      <c r="K21" s="178"/>
+      <c r="L21" s="193"/>
+      <c r="M21" s="177"/>
+      <c r="N21" s="178"/>
+      <c r="O21" s="193"/>
+      <c r="P21" s="177"/>
+      <c r="Q21" s="178"/>
       <c r="R21" s="30"/>
       <c r="S21" s="30"/>
       <c r="T21" s="31"/>
@@ -10569,23 +10545,23 @@
       <c r="Z21" s="32"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="168"/>
-      <c r="B22" s="147"/>
-      <c r="C22" s="169"/>
-      <c r="D22" s="147"/>
-      <c r="E22" s="169"/>
-      <c r="F22" s="147"/>
-      <c r="G22" s="160"/>
-      <c r="H22" s="146"/>
-      <c r="I22" s="147"/>
-      <c r="J22" s="160"/>
-      <c r="K22" s="147"/>
-      <c r="L22" s="162"/>
-      <c r="M22" s="146"/>
-      <c r="N22" s="147"/>
-      <c r="O22" s="162"/>
-      <c r="P22" s="146"/>
-      <c r="Q22" s="147"/>
+      <c r="A22" s="199"/>
+      <c r="B22" s="178"/>
+      <c r="C22" s="200"/>
+      <c r="D22" s="178"/>
+      <c r="E22" s="200"/>
+      <c r="F22" s="178"/>
+      <c r="G22" s="191"/>
+      <c r="H22" s="177"/>
+      <c r="I22" s="178"/>
+      <c r="J22" s="191"/>
+      <c r="K22" s="178"/>
+      <c r="L22" s="193"/>
+      <c r="M22" s="177"/>
+      <c r="N22" s="178"/>
+      <c r="O22" s="193"/>
+      <c r="P22" s="177"/>
+      <c r="Q22" s="178"/>
       <c r="R22" s="30"/>
       <c r="S22" s="30"/>
       <c r="T22" s="31"/>
@@ -10597,23 +10573,23 @@
       <c r="Z22" s="32"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="168"/>
-      <c r="B23" s="147"/>
-      <c r="C23" s="169"/>
-      <c r="D23" s="147"/>
-      <c r="E23" s="169"/>
-      <c r="F23" s="147"/>
-      <c r="G23" s="160"/>
-      <c r="H23" s="146"/>
-      <c r="I23" s="147"/>
-      <c r="J23" s="160"/>
-      <c r="K23" s="147"/>
-      <c r="L23" s="162"/>
-      <c r="M23" s="146"/>
-      <c r="N23" s="147"/>
-      <c r="O23" s="162"/>
-      <c r="P23" s="146"/>
-      <c r="Q23" s="147"/>
+      <c r="A23" s="199"/>
+      <c r="B23" s="178"/>
+      <c r="C23" s="200"/>
+      <c r="D23" s="178"/>
+      <c r="E23" s="200"/>
+      <c r="F23" s="178"/>
+      <c r="G23" s="191"/>
+      <c r="H23" s="177"/>
+      <c r="I23" s="178"/>
+      <c r="J23" s="191"/>
+      <c r="K23" s="178"/>
+      <c r="L23" s="193"/>
+      <c r="M23" s="177"/>
+      <c r="N23" s="178"/>
+      <c r="O23" s="193"/>
+      <c r="P23" s="177"/>
+      <c r="Q23" s="178"/>
       <c r="R23" s="30"/>
       <c r="S23" s="30"/>
       <c r="T23" s="31"/>
@@ -10625,23 +10601,23 @@
       <c r="Z23" s="32"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="168"/>
-      <c r="B24" s="147"/>
-      <c r="C24" s="169"/>
-      <c r="D24" s="147"/>
-      <c r="E24" s="169"/>
-      <c r="F24" s="147"/>
-      <c r="G24" s="160"/>
-      <c r="H24" s="146"/>
-      <c r="I24" s="147"/>
-      <c r="J24" s="160"/>
-      <c r="K24" s="147"/>
-      <c r="L24" s="162"/>
-      <c r="M24" s="146"/>
-      <c r="N24" s="147"/>
-      <c r="O24" s="162"/>
-      <c r="P24" s="146"/>
-      <c r="Q24" s="147"/>
+      <c r="A24" s="199"/>
+      <c r="B24" s="178"/>
+      <c r="C24" s="200"/>
+      <c r="D24" s="178"/>
+      <c r="E24" s="200"/>
+      <c r="F24" s="178"/>
+      <c r="G24" s="191"/>
+      <c r="H24" s="177"/>
+      <c r="I24" s="178"/>
+      <c r="J24" s="191"/>
+      <c r="K24" s="178"/>
+      <c r="L24" s="193"/>
+      <c r="M24" s="177"/>
+      <c r="N24" s="178"/>
+      <c r="O24" s="193"/>
+      <c r="P24" s="177"/>
+      <c r="Q24" s="178"/>
       <c r="R24" s="30"/>
       <c r="S24" s="30"/>
       <c r="T24" s="31"/>
@@ -10653,23 +10629,23 @@
       <c r="Z24" s="32"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="168"/>
-      <c r="B25" s="147"/>
-      <c r="C25" s="169"/>
-      <c r="D25" s="147"/>
-      <c r="E25" s="169"/>
-      <c r="F25" s="147"/>
-      <c r="G25" s="160"/>
-      <c r="H25" s="146"/>
-      <c r="I25" s="147"/>
-      <c r="J25" s="160"/>
-      <c r="K25" s="147"/>
-      <c r="L25" s="162"/>
-      <c r="M25" s="146"/>
-      <c r="N25" s="147"/>
-      <c r="O25" s="162"/>
-      <c r="P25" s="146"/>
-      <c r="Q25" s="147"/>
+      <c r="A25" s="199"/>
+      <c r="B25" s="178"/>
+      <c r="C25" s="200"/>
+      <c r="D25" s="178"/>
+      <c r="E25" s="200"/>
+      <c r="F25" s="178"/>
+      <c r="G25" s="191"/>
+      <c r="H25" s="177"/>
+      <c r="I25" s="178"/>
+      <c r="J25" s="191"/>
+      <c r="K25" s="178"/>
+      <c r="L25" s="193"/>
+      <c r="M25" s="177"/>
+      <c r="N25" s="178"/>
+      <c r="O25" s="193"/>
+      <c r="P25" s="177"/>
+      <c r="Q25" s="178"/>
       <c r="R25" s="30"/>
       <c r="S25" s="30"/>
       <c r="T25" s="31"/>
@@ -10681,23 +10657,23 @@
       <c r="Z25" s="32"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="168"/>
-      <c r="B26" s="147"/>
-      <c r="C26" s="169"/>
-      <c r="D26" s="147"/>
-      <c r="E26" s="169"/>
-      <c r="F26" s="147"/>
-      <c r="G26" s="160"/>
-      <c r="H26" s="146"/>
-      <c r="I26" s="147"/>
-      <c r="J26" s="160"/>
-      <c r="K26" s="147"/>
-      <c r="L26" s="162"/>
-      <c r="M26" s="146"/>
-      <c r="N26" s="147"/>
-      <c r="O26" s="162"/>
-      <c r="P26" s="146"/>
-      <c r="Q26" s="147"/>
+      <c r="A26" s="199"/>
+      <c r="B26" s="178"/>
+      <c r="C26" s="200"/>
+      <c r="D26" s="178"/>
+      <c r="E26" s="200"/>
+      <c r="F26" s="178"/>
+      <c r="G26" s="191"/>
+      <c r="H26" s="177"/>
+      <c r="I26" s="178"/>
+      <c r="J26" s="191"/>
+      <c r="K26" s="178"/>
+      <c r="L26" s="193"/>
+      <c r="M26" s="177"/>
+      <c r="N26" s="178"/>
+      <c r="O26" s="193"/>
+      <c r="P26" s="177"/>
+      <c r="Q26" s="178"/>
       <c r="R26" s="30"/>
       <c r="S26" s="30"/>
       <c r="T26" s="31"/>
@@ -10709,23 +10685,23 @@
       <c r="Z26" s="32"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="168"/>
-      <c r="B27" s="147"/>
-      <c r="C27" s="169"/>
-      <c r="D27" s="147"/>
-      <c r="E27" s="169"/>
-      <c r="F27" s="147"/>
-      <c r="G27" s="160"/>
-      <c r="H27" s="146"/>
-      <c r="I27" s="147"/>
-      <c r="J27" s="160"/>
-      <c r="K27" s="147"/>
-      <c r="L27" s="162"/>
-      <c r="M27" s="146"/>
-      <c r="N27" s="147"/>
-      <c r="O27" s="162"/>
-      <c r="P27" s="146"/>
-      <c r="Q27" s="147"/>
+      <c r="A27" s="199"/>
+      <c r="B27" s="178"/>
+      <c r="C27" s="200"/>
+      <c r="D27" s="178"/>
+      <c r="E27" s="200"/>
+      <c r="F27" s="178"/>
+      <c r="G27" s="191"/>
+      <c r="H27" s="177"/>
+      <c r="I27" s="178"/>
+      <c r="J27" s="191"/>
+      <c r="K27" s="178"/>
+      <c r="L27" s="193"/>
+      <c r="M27" s="177"/>
+      <c r="N27" s="178"/>
+      <c r="O27" s="193"/>
+      <c r="P27" s="177"/>
+      <c r="Q27" s="178"/>
       <c r="R27" s="30"/>
       <c r="S27" s="30"/>
       <c r="T27" s="31"/>
@@ -10737,23 +10713,23 @@
       <c r="Z27" s="32"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="168"/>
-      <c r="B28" s="147"/>
-      <c r="C28" s="169"/>
-      <c r="D28" s="147"/>
-      <c r="E28" s="169"/>
-      <c r="F28" s="147"/>
-      <c r="G28" s="160"/>
-      <c r="H28" s="146"/>
-      <c r="I28" s="147"/>
-      <c r="J28" s="160"/>
-      <c r="K28" s="147"/>
-      <c r="L28" s="162"/>
-      <c r="M28" s="146"/>
-      <c r="N28" s="147"/>
-      <c r="O28" s="162"/>
-      <c r="P28" s="146"/>
-      <c r="Q28" s="147"/>
+      <c r="A28" s="199"/>
+      <c r="B28" s="178"/>
+      <c r="C28" s="200"/>
+      <c r="D28" s="178"/>
+      <c r="E28" s="200"/>
+      <c r="F28" s="178"/>
+      <c r="G28" s="191"/>
+      <c r="H28" s="177"/>
+      <c r="I28" s="178"/>
+      <c r="J28" s="191"/>
+      <c r="K28" s="178"/>
+      <c r="L28" s="193"/>
+      <c r="M28" s="177"/>
+      <c r="N28" s="178"/>
+      <c r="O28" s="193"/>
+      <c r="P28" s="177"/>
+      <c r="Q28" s="178"/>
       <c r="R28" s="30"/>
       <c r="S28" s="30"/>
       <c r="T28" s="31"/>
@@ -10765,23 +10741,23 @@
       <c r="Z28" s="32"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="168"/>
-      <c r="B29" s="147"/>
-      <c r="C29" s="169"/>
-      <c r="D29" s="147"/>
-      <c r="E29" s="169"/>
-      <c r="F29" s="147"/>
-      <c r="G29" s="160"/>
-      <c r="H29" s="146"/>
-      <c r="I29" s="147"/>
-      <c r="J29" s="160"/>
-      <c r="K29" s="147"/>
-      <c r="L29" s="162"/>
-      <c r="M29" s="146"/>
-      <c r="N29" s="147"/>
-      <c r="O29" s="162"/>
-      <c r="P29" s="146"/>
-      <c r="Q29" s="147"/>
+      <c r="A29" s="199"/>
+      <c r="B29" s="178"/>
+      <c r="C29" s="200"/>
+      <c r="D29" s="178"/>
+      <c r="E29" s="200"/>
+      <c r="F29" s="178"/>
+      <c r="G29" s="191"/>
+      <c r="H29" s="177"/>
+      <c r="I29" s="178"/>
+      <c r="J29" s="191"/>
+      <c r="K29" s="178"/>
+      <c r="L29" s="193"/>
+      <c r="M29" s="177"/>
+      <c r="N29" s="178"/>
+      <c r="O29" s="193"/>
+      <c r="P29" s="177"/>
+      <c r="Q29" s="178"/>
       <c r="R29" s="30"/>
       <c r="S29" s="30"/>
       <c r="T29" s="31"/>
@@ -10793,23 +10769,23 @@
       <c r="Z29" s="32"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="168"/>
-      <c r="B30" s="147"/>
-      <c r="C30" s="169"/>
-      <c r="D30" s="147"/>
-      <c r="E30" s="169"/>
-      <c r="F30" s="147"/>
-      <c r="G30" s="160"/>
-      <c r="H30" s="146"/>
-      <c r="I30" s="147"/>
-      <c r="J30" s="160"/>
-      <c r="K30" s="147"/>
-      <c r="L30" s="162"/>
-      <c r="M30" s="146"/>
-      <c r="N30" s="147"/>
-      <c r="O30" s="162"/>
-      <c r="P30" s="146"/>
-      <c r="Q30" s="147"/>
+      <c r="A30" s="199"/>
+      <c r="B30" s="178"/>
+      <c r="C30" s="200"/>
+      <c r="D30" s="178"/>
+      <c r="E30" s="200"/>
+      <c r="F30" s="178"/>
+      <c r="G30" s="191"/>
+      <c r="H30" s="177"/>
+      <c r="I30" s="178"/>
+      <c r="J30" s="191"/>
+      <c r="K30" s="178"/>
+      <c r="L30" s="193"/>
+      <c r="M30" s="177"/>
+      <c r="N30" s="178"/>
+      <c r="O30" s="193"/>
+      <c r="P30" s="177"/>
+      <c r="Q30" s="178"/>
       <c r="R30" s="30"/>
       <c r="S30" s="30"/>
       <c r="T30" s="31"/>
@@ -10821,23 +10797,23 @@
       <c r="Z30" s="32"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="171"/>
-      <c r="B31" s="144"/>
-      <c r="C31" s="172"/>
-      <c r="D31" s="144"/>
-      <c r="E31" s="172"/>
-      <c r="F31" s="144"/>
-      <c r="G31" s="161"/>
-      <c r="H31" s="143"/>
-      <c r="I31" s="144"/>
-      <c r="J31" s="161"/>
-      <c r="K31" s="144"/>
-      <c r="L31" s="163"/>
-      <c r="M31" s="143"/>
-      <c r="N31" s="144"/>
-      <c r="O31" s="163"/>
-      <c r="P31" s="143"/>
-      <c r="Q31" s="144"/>
+      <c r="A31" s="202"/>
+      <c r="B31" s="175"/>
+      <c r="C31" s="203"/>
+      <c r="D31" s="175"/>
+      <c r="E31" s="203"/>
+      <c r="F31" s="175"/>
+      <c r="G31" s="192"/>
+      <c r="H31" s="174"/>
+      <c r="I31" s="175"/>
+      <c r="J31" s="192"/>
+      <c r="K31" s="175"/>
+      <c r="L31" s="194"/>
+      <c r="M31" s="174"/>
+      <c r="N31" s="175"/>
+      <c r="O31" s="194"/>
+      <c r="P31" s="174"/>
+      <c r="Q31" s="175"/>
       <c r="R31" s="33"/>
       <c r="S31" s="33"/>
       <c r="T31" s="34"/>
@@ -11993,72 +11969,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="181" t="s">
+      <c r="A1" s="78" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="182" t="s">
+      <c r="B1" s="78"/>
+      <c r="C1" s="79" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="183"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="185" t="s">
+      <c r="D1" s="80"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="82" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="186"/>
-      <c r="H1" s="186"/>
-      <c r="I1" s="186"/>
-      <c r="J1" s="186"/>
-      <c r="K1" s="186"/>
-      <c r="L1" s="186"/>
-      <c r="M1" s="187"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="84"/>
       <c r="N1" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="O1" s="185" t="s">
+      <c r="O1" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="P1" s="187"/>
+      <c r="P1" s="84"/>
       <c r="Q1" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="R1" s="185" t="s">
+      <c r="R1" s="82" t="s">
         <v>74</v>
       </c>
-      <c r="S1" s="187"/>
+      <c r="S1" s="84"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="181"/>
-      <c r="B2" s="181"/>
-      <c r="C2" s="182" t="s">
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="183"/>
-      <c r="E2" s="184"/>
-      <c r="F2" s="185" t="s">
+      <c r="D2" s="80"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="82" t="s">
         <v>76</v>
       </c>
-      <c r="G2" s="186"/>
-      <c r="H2" s="186"/>
-      <c r="I2" s="186"/>
-      <c r="J2" s="186"/>
-      <c r="K2" s="186"/>
-      <c r="L2" s="186"/>
-      <c r="M2" s="187"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="84"/>
       <c r="N2" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="O2" s="194">
-        <v>46182</v>
-      </c>
-      <c r="P2" s="195"/>
+      <c r="O2" s="91">
+        <v>46183</v>
+      </c>
+      <c r="P2" s="92"/>
       <c r="Q2" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="R2" s="202" t="s">
+      <c r="R2" s="99" t="s">
         <v>72</v>
       </c>
-      <c r="S2" s="203"/>
+      <c r="S2" s="100"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="37"/>
@@ -12088,33 +12064,33 @@
       <c r="B4" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="177" t="s">
+      <c r="C4" s="74" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="178"/>
-      <c r="E4" s="178"/>
-      <c r="F4" s="178"/>
-      <c r="G4" s="179"/>
-      <c r="H4" s="177" t="s">
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="74" t="s">
         <v>82</v>
       </c>
-      <c r="I4" s="178"/>
-      <c r="J4" s="178"/>
-      <c r="K4" s="178"/>
-      <c r="L4" s="178"/>
-      <c r="M4" s="179"/>
-      <c r="N4" s="177" t="s">
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
+      <c r="K4" s="75"/>
+      <c r="L4" s="75"/>
+      <c r="M4" s="76"/>
+      <c r="N4" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="O4" s="178"/>
-      <c r="P4" s="179"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="76"/>
       <c r="Q4" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="R4" s="177" t="s">
+      <c r="R4" s="74" t="s">
         <v>85</v>
       </c>
-      <c r="S4" s="179"/>
+      <c r="S4" s="76"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="41">
@@ -12123,31 +12099,31 @@
       <c r="B5" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="180" t="s">
+      <c r="C5" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="180"/>
-      <c r="E5" s="180"/>
-      <c r="F5" s="180"/>
-      <c r="G5" s="180"/>
-      <c r="H5" s="180" t="s">
-        <v>101</v>
-      </c>
-      <c r="I5" s="180"/>
-      <c r="J5" s="180"/>
-      <c r="K5" s="180"/>
-      <c r="L5" s="180"/>
-      <c r="M5" s="180"/>
-      <c r="N5" s="196" t="s">
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77" t="s">
+        <v>100</v>
+      </c>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="77"/>
+      <c r="M5" s="77"/>
+      <c r="N5" s="93" t="s">
         <v>88</v>
       </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="198"/>
+      <c r="O5" s="94"/>
+      <c r="P5" s="95"/>
       <c r="Q5" s="42">
-        <v>46182</v>
-      </c>
-      <c r="R5" s="192"/>
-      <c r="S5" s="193"/>
+        <v>46183</v>
+      </c>
+      <c r="R5" s="88"/>
+      <c r="S5" s="89"/>
     </row>
     <row r="6" spans="1:19" ht="46.5" customHeight="1">
       <c r="A6" s="43">
@@ -12156,1009 +12132,997 @@
       <c r="B6" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="180" t="s">
+      <c r="C6" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="180"/>
-      <c r="E6" s="180"/>
-      <c r="F6" s="180"/>
-      <c r="G6" s="180"/>
-      <c r="H6" s="180" t="s">
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77" t="s">
+        <v>100</v>
+      </c>
+      <c r="I6" s="77"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="77"/>
+      <c r="N6" s="96" t="s">
         <v>101</v>
       </c>
-      <c r="I6" s="180"/>
-      <c r="J6" s="180"/>
-      <c r="K6" s="180"/>
-      <c r="L6" s="180"/>
-      <c r="M6" s="180"/>
-      <c r="N6" s="199" t="s">
-        <v>102</v>
-      </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="201"/>
+      <c r="O6" s="97"/>
+      <c r="P6" s="98"/>
       <c r="Q6" s="42">
-        <v>46182</v>
-      </c>
-      <c r="R6" s="188"/>
-      <c r="S6" s="188"/>
+        <v>46183</v>
+      </c>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
-      <c r="A7" s="43">
-        <v>3</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="180" t="s">
-        <v>87</v>
-      </c>
-      <c r="D7" s="180"/>
-      <c r="E7" s="180"/>
-      <c r="F7" s="180"/>
-      <c r="G7" s="180"/>
-      <c r="H7" s="176" t="s">
-        <v>100</v>
-      </c>
-      <c r="I7" s="176"/>
-      <c r="J7" s="176"/>
-      <c r="K7" s="176"/>
-      <c r="L7" s="176"/>
-      <c r="M7" s="176"/>
-      <c r="N7" s="199" t="s">
-        <v>103</v>
-      </c>
-      <c r="O7" s="190"/>
-      <c r="P7" s="191"/>
-      <c r="Q7" s="42">
-        <v>46182</v>
-      </c>
-      <c r="R7" s="188"/>
-      <c r="S7" s="188"/>
+      <c r="A7" s="43"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="73"/>
+      <c r="I7" s="73"/>
+      <c r="J7" s="73"/>
+      <c r="K7" s="73"/>
+      <c r="L7" s="73"/>
+      <c r="M7" s="73"/>
+      <c r="N7" s="96"/>
+      <c r="O7" s="86"/>
+      <c r="P7" s="87"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="90"/>
+      <c r="S7" s="90"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="43"/>
       <c r="B8" s="43"/>
-      <c r="C8" s="176"/>
-      <c r="D8" s="176"/>
-      <c r="E8" s="176"/>
-      <c r="F8" s="176"/>
-      <c r="G8" s="176"/>
-      <c r="H8" s="176"/>
-      <c r="I8" s="176"/>
-      <c r="J8" s="176"/>
-      <c r="K8" s="176"/>
-      <c r="L8" s="176"/>
-      <c r="M8" s="176"/>
-      <c r="N8" s="189"/>
-      <c r="O8" s="190"/>
-      <c r="P8" s="191"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73"/>
+      <c r="J8" s="73"/>
+      <c r="K8" s="73"/>
+      <c r="L8" s="73"/>
+      <c r="M8" s="73"/>
+      <c r="N8" s="85"/>
+      <c r="O8" s="86"/>
+      <c r="P8" s="87"/>
       <c r="Q8" s="44"/>
-      <c r="R8" s="188"/>
-      <c r="S8" s="188"/>
+      <c r="R8" s="90"/>
+      <c r="S8" s="90"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="43"/>
       <c r="B9" s="43"/>
-      <c r="C9" s="176"/>
-      <c r="D9" s="176"/>
-      <c r="E9" s="176"/>
-      <c r="F9" s="176"/>
-      <c r="G9" s="176"/>
-      <c r="H9" s="176"/>
-      <c r="I9" s="176"/>
-      <c r="J9" s="176"/>
-      <c r="K9" s="176"/>
-      <c r="L9" s="176"/>
-      <c r="M9" s="176"/>
-      <c r="N9" s="189"/>
-      <c r="O9" s="190"/>
-      <c r="P9" s="191"/>
+      <c r="C9" s="73"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="73"/>
+      <c r="H9" s="73"/>
+      <c r="I9" s="73"/>
+      <c r="J9" s="73"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="73"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="85"/>
+      <c r="O9" s="86"/>
+      <c r="P9" s="87"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="188"/>
-      <c r="S9" s="188"/>
+      <c r="R9" s="90"/>
+      <c r="S9" s="90"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="43"/>
       <c r="B10" s="43"/>
-      <c r="C10" s="176"/>
-      <c r="D10" s="176"/>
-      <c r="E10" s="176"/>
-      <c r="F10" s="176"/>
-      <c r="G10" s="176"/>
-      <c r="H10" s="173"/>
-      <c r="I10" s="174"/>
-      <c r="J10" s="174"/>
-      <c r="K10" s="174"/>
-      <c r="L10" s="174"/>
-      <c r="M10" s="175"/>
-      <c r="N10" s="189"/>
-      <c r="O10" s="190"/>
-      <c r="P10" s="191"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="71"/>
+      <c r="L10" s="71"/>
+      <c r="M10" s="72"/>
+      <c r="N10" s="85"/>
+      <c r="O10" s="86"/>
+      <c r="P10" s="87"/>
       <c r="Q10" s="44"/>
-      <c r="R10" s="188"/>
-      <c r="S10" s="188"/>
+      <c r="R10" s="90"/>
+      <c r="S10" s="90"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="43"/>
       <c r="B11" s="43"/>
-      <c r="C11" s="176"/>
-      <c r="D11" s="176"/>
-      <c r="E11" s="176"/>
-      <c r="F11" s="176"/>
-      <c r="G11" s="176"/>
-      <c r="H11" s="173"/>
-      <c r="I11" s="174"/>
-      <c r="J11" s="174"/>
-      <c r="K11" s="174"/>
-      <c r="L11" s="174"/>
-      <c r="M11" s="175"/>
-      <c r="N11" s="189"/>
-      <c r="O11" s="190"/>
-      <c r="P11" s="191"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="71"/>
+      <c r="L11" s="71"/>
+      <c r="M11" s="72"/>
+      <c r="N11" s="85"/>
+      <c r="O11" s="86"/>
+      <c r="P11" s="87"/>
       <c r="Q11" s="43"/>
-      <c r="R11" s="188"/>
-      <c r="S11" s="188"/>
+      <c r="R11" s="90"/>
+      <c r="S11" s="90"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="43"/>
       <c r="B12" s="43"/>
-      <c r="C12" s="176"/>
-      <c r="D12" s="176"/>
-      <c r="E12" s="176"/>
-      <c r="F12" s="176"/>
-      <c r="G12" s="176"/>
-      <c r="H12" s="173"/>
-      <c r="I12" s="174"/>
-      <c r="J12" s="174"/>
-      <c r="K12" s="174"/>
-      <c r="L12" s="174"/>
-      <c r="M12" s="175"/>
-      <c r="N12" s="189"/>
-      <c r="O12" s="190"/>
-      <c r="P12" s="191"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="70"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="71"/>
+      <c r="K12" s="71"/>
+      <c r="L12" s="71"/>
+      <c r="M12" s="72"/>
+      <c r="N12" s="85"/>
+      <c r="O12" s="86"/>
+      <c r="P12" s="87"/>
       <c r="Q12" s="43"/>
-      <c r="R12" s="188"/>
-      <c r="S12" s="188"/>
+      <c r="R12" s="90"/>
+      <c r="S12" s="90"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="43"/>
       <c r="B13" s="43"/>
-      <c r="C13" s="176"/>
-      <c r="D13" s="176"/>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
-      <c r="G13" s="176"/>
-      <c r="H13" s="173"/>
-      <c r="I13" s="174"/>
-      <c r="J13" s="174"/>
-      <c r="K13" s="174"/>
-      <c r="L13" s="174"/>
-      <c r="M13" s="175"/>
-      <c r="N13" s="189"/>
-      <c r="O13" s="190"/>
-      <c r="P13" s="191"/>
+      <c r="C13" s="73"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="71"/>
+      <c r="L13" s="71"/>
+      <c r="M13" s="72"/>
+      <c r="N13" s="85"/>
+      <c r="O13" s="86"/>
+      <c r="P13" s="87"/>
       <c r="Q13" s="43"/>
-      <c r="R13" s="188"/>
-      <c r="S13" s="188"/>
+      <c r="R13" s="90"/>
+      <c r="S13" s="90"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="43"/>
       <c r="B14" s="43"/>
-      <c r="C14" s="176"/>
-      <c r="D14" s="176"/>
-      <c r="E14" s="176"/>
-      <c r="F14" s="176"/>
-      <c r="G14" s="176"/>
-      <c r="H14" s="173"/>
-      <c r="I14" s="174"/>
-      <c r="J14" s="174"/>
-      <c r="K14" s="174"/>
-      <c r="L14" s="174"/>
-      <c r="M14" s="175"/>
-      <c r="N14" s="189"/>
-      <c r="O14" s="190"/>
-      <c r="P14" s="191"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="71"/>
+      <c r="L14" s="71"/>
+      <c r="M14" s="72"/>
+      <c r="N14" s="85"/>
+      <c r="O14" s="86"/>
+      <c r="P14" s="87"/>
       <c r="Q14" s="43"/>
-      <c r="R14" s="188"/>
-      <c r="S14" s="188"/>
+      <c r="R14" s="90"/>
+      <c r="S14" s="90"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="43"/>
       <c r="B15" s="43"/>
-      <c r="C15" s="176"/>
-      <c r="D15" s="176"/>
-      <c r="E15" s="176"/>
-      <c r="F15" s="176"/>
-      <c r="G15" s="176"/>
-      <c r="H15" s="173"/>
-      <c r="I15" s="174"/>
-      <c r="J15" s="174"/>
-      <c r="K15" s="174"/>
-      <c r="L15" s="174"/>
-      <c r="M15" s="175"/>
-      <c r="N15" s="189"/>
-      <c r="O15" s="190"/>
-      <c r="P15" s="191"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="71"/>
+      <c r="L15" s="71"/>
+      <c r="M15" s="72"/>
+      <c r="N15" s="85"/>
+      <c r="O15" s="86"/>
+      <c r="P15" s="87"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="188"/>
-      <c r="S15" s="188"/>
+      <c r="R15" s="90"/>
+      <c r="S15" s="90"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="43"/>
       <c r="B16" s="43"/>
-      <c r="C16" s="176"/>
-      <c r="D16" s="176"/>
-      <c r="E16" s="176"/>
-      <c r="F16" s="176"/>
-      <c r="G16" s="176"/>
-      <c r="H16" s="173"/>
-      <c r="I16" s="174"/>
-      <c r="J16" s="174"/>
-      <c r="K16" s="174"/>
-      <c r="L16" s="174"/>
-      <c r="M16" s="175"/>
-      <c r="N16" s="189"/>
-      <c r="O16" s="190"/>
-      <c r="P16" s="191"/>
+      <c r="C16" s="73"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="73"/>
+      <c r="G16" s="73"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="71"/>
+      <c r="L16" s="71"/>
+      <c r="M16" s="72"/>
+      <c r="N16" s="85"/>
+      <c r="O16" s="86"/>
+      <c r="P16" s="87"/>
       <c r="Q16" s="43"/>
-      <c r="R16" s="188"/>
-      <c r="S16" s="188"/>
+      <c r="R16" s="90"/>
+      <c r="S16" s="90"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="43"/>
       <c r="B17" s="43"/>
-      <c r="C17" s="176"/>
-      <c r="D17" s="176"/>
-      <c r="E17" s="176"/>
-      <c r="F17" s="176"/>
-      <c r="G17" s="176"/>
-      <c r="H17" s="173"/>
-      <c r="I17" s="174"/>
-      <c r="J17" s="174"/>
-      <c r="K17" s="174"/>
-      <c r="L17" s="174"/>
-      <c r="M17" s="175"/>
-      <c r="N17" s="189"/>
-      <c r="O17" s="190"/>
-      <c r="P17" s="191"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="73"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="72"/>
+      <c r="N17" s="85"/>
+      <c r="O17" s="86"/>
+      <c r="P17" s="87"/>
       <c r="Q17" s="43"/>
-      <c r="R17" s="188"/>
-      <c r="S17" s="188"/>
+      <c r="R17" s="90"/>
+      <c r="S17" s="90"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="43"/>
       <c r="B18" s="43"/>
-      <c r="C18" s="176"/>
-      <c r="D18" s="176"/>
-      <c r="E18" s="176"/>
-      <c r="F18" s="176"/>
-      <c r="G18" s="176"/>
-      <c r="H18" s="173"/>
-      <c r="I18" s="174"/>
-      <c r="J18" s="174"/>
-      <c r="K18" s="174"/>
-      <c r="L18" s="174"/>
-      <c r="M18" s="175"/>
-      <c r="N18" s="189"/>
-      <c r="O18" s="190"/>
-      <c r="P18" s="191"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="73"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="71"/>
+      <c r="L18" s="71"/>
+      <c r="M18" s="72"/>
+      <c r="N18" s="85"/>
+      <c r="O18" s="86"/>
+      <c r="P18" s="87"/>
       <c r="Q18" s="43"/>
-      <c r="R18" s="188"/>
-      <c r="S18" s="188"/>
+      <c r="R18" s="90"/>
+      <c r="S18" s="90"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="43"/>
       <c r="B19" s="43"/>
-      <c r="C19" s="176"/>
-      <c r="D19" s="176"/>
-      <c r="E19" s="176"/>
-      <c r="F19" s="176"/>
-      <c r="G19" s="176"/>
-      <c r="H19" s="173"/>
-      <c r="I19" s="174"/>
-      <c r="J19" s="174"/>
-      <c r="K19" s="174"/>
-      <c r="L19" s="174"/>
-      <c r="M19" s="175"/>
-      <c r="N19" s="189"/>
-      <c r="O19" s="190"/>
-      <c r="P19" s="191"/>
+      <c r="C19" s="73"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="73"/>
+      <c r="G19" s="73"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="71"/>
+      <c r="L19" s="71"/>
+      <c r="M19" s="72"/>
+      <c r="N19" s="85"/>
+      <c r="O19" s="86"/>
+      <c r="P19" s="87"/>
       <c r="Q19" s="43"/>
-      <c r="R19" s="188"/>
-      <c r="S19" s="188"/>
+      <c r="R19" s="90"/>
+      <c r="S19" s="90"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="43"/>
       <c r="B20" s="43"/>
-      <c r="C20" s="176"/>
-      <c r="D20" s="176"/>
-      <c r="E20" s="176"/>
-      <c r="F20" s="176"/>
-      <c r="G20" s="176"/>
-      <c r="H20" s="173"/>
-      <c r="I20" s="174"/>
-      <c r="J20" s="174"/>
-      <c r="K20" s="174"/>
-      <c r="L20" s="174"/>
-      <c r="M20" s="175"/>
-      <c r="N20" s="189"/>
-      <c r="O20" s="190"/>
-      <c r="P20" s="191"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="71"/>
+      <c r="L20" s="71"/>
+      <c r="M20" s="72"/>
+      <c r="N20" s="85"/>
+      <c r="O20" s="86"/>
+      <c r="P20" s="87"/>
       <c r="Q20" s="43"/>
-      <c r="R20" s="188"/>
-      <c r="S20" s="188"/>
+      <c r="R20" s="90"/>
+      <c r="S20" s="90"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="43"/>
       <c r="B21" s="43"/>
-      <c r="C21" s="176"/>
-      <c r="D21" s="176"/>
-      <c r="E21" s="176"/>
-      <c r="F21" s="176"/>
-      <c r="G21" s="176"/>
-      <c r="H21" s="173"/>
-      <c r="I21" s="174"/>
-      <c r="J21" s="174"/>
-      <c r="K21" s="174"/>
-      <c r="L21" s="174"/>
-      <c r="M21" s="175"/>
-      <c r="N21" s="189"/>
-      <c r="O21" s="190"/>
-      <c r="P21" s="191"/>
+      <c r="C21" s="73"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="71"/>
+      <c r="L21" s="71"/>
+      <c r="M21" s="72"/>
+      <c r="N21" s="85"/>
+      <c r="O21" s="86"/>
+      <c r="P21" s="87"/>
       <c r="Q21" s="43"/>
-      <c r="R21" s="188"/>
-      <c r="S21" s="188"/>
+      <c r="R21" s="90"/>
+      <c r="S21" s="90"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="43"/>
       <c r="B22" s="43"/>
-      <c r="C22" s="176"/>
-      <c r="D22" s="176"/>
-      <c r="E22" s="176"/>
-      <c r="F22" s="176"/>
-      <c r="G22" s="176"/>
-      <c r="H22" s="173"/>
-      <c r="I22" s="174"/>
-      <c r="J22" s="174"/>
-      <c r="K22" s="174"/>
-      <c r="L22" s="174"/>
-      <c r="M22" s="175"/>
-      <c r="N22" s="189"/>
-      <c r="O22" s="190"/>
-      <c r="P22" s="191"/>
+      <c r="C22" s="73"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="71"/>
+      <c r="K22" s="71"/>
+      <c r="L22" s="71"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="85"/>
+      <c r="O22" s="86"/>
+      <c r="P22" s="87"/>
       <c r="Q22" s="43"/>
-      <c r="R22" s="188"/>
-      <c r="S22" s="188"/>
+      <c r="R22" s="90"/>
+      <c r="S22" s="90"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="43"/>
       <c r="B23" s="43"/>
-      <c r="C23" s="176"/>
-      <c r="D23" s="176"/>
-      <c r="E23" s="176"/>
-      <c r="F23" s="176"/>
-      <c r="G23" s="176"/>
-      <c r="H23" s="173"/>
-      <c r="I23" s="174"/>
-      <c r="J23" s="174"/>
-      <c r="K23" s="174"/>
-      <c r="L23" s="174"/>
-      <c r="M23" s="175"/>
-      <c r="N23" s="189"/>
-      <c r="O23" s="190"/>
-      <c r="P23" s="191"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="71"/>
+      <c r="L23" s="71"/>
+      <c r="M23" s="72"/>
+      <c r="N23" s="85"/>
+      <c r="O23" s="86"/>
+      <c r="P23" s="87"/>
       <c r="Q23" s="43"/>
-      <c r="R23" s="188"/>
-      <c r="S23" s="188"/>
+      <c r="R23" s="90"/>
+      <c r="S23" s="90"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="43"/>
       <c r="B24" s="43"/>
-      <c r="C24" s="176"/>
-      <c r="D24" s="176"/>
-      <c r="E24" s="176"/>
-      <c r="F24" s="176"/>
-      <c r="G24" s="176"/>
-      <c r="H24" s="173"/>
-      <c r="I24" s="174"/>
-      <c r="J24" s="174"/>
-      <c r="K24" s="174"/>
-      <c r="L24" s="174"/>
-      <c r="M24" s="175"/>
-      <c r="N24" s="189"/>
-      <c r="O24" s="190"/>
-      <c r="P24" s="191"/>
+      <c r="C24" s="73"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="71"/>
+      <c r="L24" s="71"/>
+      <c r="M24" s="72"/>
+      <c r="N24" s="85"/>
+      <c r="O24" s="86"/>
+      <c r="P24" s="87"/>
       <c r="Q24" s="43"/>
-      <c r="R24" s="188"/>
-      <c r="S24" s="188"/>
+      <c r="R24" s="90"/>
+      <c r="S24" s="90"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="43"/>
       <c r="B25" s="43"/>
-      <c r="C25" s="176"/>
-      <c r="D25" s="176"/>
-      <c r="E25" s="176"/>
-      <c r="F25" s="176"/>
-      <c r="G25" s="176"/>
-      <c r="H25" s="173"/>
-      <c r="I25" s="174"/>
-      <c r="J25" s="174"/>
-      <c r="K25" s="174"/>
-      <c r="L25" s="174"/>
-      <c r="M25" s="175"/>
-      <c r="N25" s="189"/>
-      <c r="O25" s="190"/>
-      <c r="P25" s="191"/>
+      <c r="C25" s="73"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="71"/>
+      <c r="K25" s="71"/>
+      <c r="L25" s="71"/>
+      <c r="M25" s="72"/>
+      <c r="N25" s="85"/>
+      <c r="O25" s="86"/>
+      <c r="P25" s="87"/>
       <c r="Q25" s="43"/>
-      <c r="R25" s="188"/>
-      <c r="S25" s="188"/>
+      <c r="R25" s="90"/>
+      <c r="S25" s="90"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="43"/>
       <c r="B26" s="43"/>
-      <c r="C26" s="176"/>
-      <c r="D26" s="176"/>
-      <c r="E26" s="176"/>
-      <c r="F26" s="176"/>
-      <c r="G26" s="176"/>
-      <c r="H26" s="173"/>
-      <c r="I26" s="174"/>
-      <c r="J26" s="174"/>
-      <c r="K26" s="174"/>
-      <c r="L26" s="174"/>
-      <c r="M26" s="175"/>
-      <c r="N26" s="189"/>
-      <c r="O26" s="190"/>
-      <c r="P26" s="191"/>
+      <c r="C26" s="73"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="73"/>
+      <c r="G26" s="73"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="71"/>
+      <c r="L26" s="71"/>
+      <c r="M26" s="72"/>
+      <c r="N26" s="85"/>
+      <c r="O26" s="86"/>
+      <c r="P26" s="87"/>
       <c r="Q26" s="43"/>
-      <c r="R26" s="188"/>
-      <c r="S26" s="188"/>
+      <c r="R26" s="90"/>
+      <c r="S26" s="90"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="43"/>
       <c r="B27" s="43"/>
-      <c r="C27" s="176"/>
-      <c r="D27" s="176"/>
-      <c r="E27" s="176"/>
-      <c r="F27" s="176"/>
-      <c r="G27" s="176"/>
-      <c r="H27" s="173"/>
-      <c r="I27" s="174"/>
-      <c r="J27" s="174"/>
-      <c r="K27" s="174"/>
-      <c r="L27" s="174"/>
-      <c r="M27" s="175"/>
-      <c r="N27" s="189"/>
-      <c r="O27" s="190"/>
-      <c r="P27" s="191"/>
+      <c r="C27" s="73"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="73"/>
+      <c r="G27" s="73"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="71"/>
+      <c r="L27" s="71"/>
+      <c r="M27" s="72"/>
+      <c r="N27" s="85"/>
+      <c r="O27" s="86"/>
+      <c r="P27" s="87"/>
       <c r="Q27" s="43"/>
-      <c r="R27" s="188"/>
-      <c r="S27" s="188"/>
+      <c r="R27" s="90"/>
+      <c r="S27" s="90"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="43"/>
       <c r="B28" s="43"/>
-      <c r="C28" s="176"/>
-      <c r="D28" s="176"/>
-      <c r="E28" s="176"/>
-      <c r="F28" s="176"/>
-      <c r="G28" s="176"/>
-      <c r="H28" s="173"/>
-      <c r="I28" s="174"/>
-      <c r="J28" s="174"/>
-      <c r="K28" s="174"/>
-      <c r="L28" s="174"/>
-      <c r="M28" s="175"/>
-      <c r="N28" s="189"/>
-      <c r="O28" s="190"/>
-      <c r="P28" s="191"/>
+      <c r="C28" s="73"/>
+      <c r="D28" s="73"/>
+      <c r="E28" s="73"/>
+      <c r="F28" s="73"/>
+      <c r="G28" s="73"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="71"/>
+      <c r="L28" s="71"/>
+      <c r="M28" s="72"/>
+      <c r="N28" s="85"/>
+      <c r="O28" s="86"/>
+      <c r="P28" s="87"/>
       <c r="Q28" s="43"/>
-      <c r="R28" s="188"/>
-      <c r="S28" s="188"/>
+      <c r="R28" s="90"/>
+      <c r="S28" s="90"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="43"/>
       <c r="B29" s="43"/>
-      <c r="C29" s="176"/>
-      <c r="D29" s="176"/>
-      <c r="E29" s="176"/>
-      <c r="F29" s="176"/>
-      <c r="G29" s="176"/>
-      <c r="H29" s="173"/>
-      <c r="I29" s="174"/>
-      <c r="J29" s="174"/>
-      <c r="K29" s="174"/>
-      <c r="L29" s="174"/>
-      <c r="M29" s="175"/>
-      <c r="N29" s="189"/>
-      <c r="O29" s="190"/>
-      <c r="P29" s="191"/>
+      <c r="C29" s="73"/>
+      <c r="D29" s="73"/>
+      <c r="E29" s="73"/>
+      <c r="F29" s="73"/>
+      <c r="G29" s="73"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="71"/>
+      <c r="K29" s="71"/>
+      <c r="L29" s="71"/>
+      <c r="M29" s="72"/>
+      <c r="N29" s="85"/>
+      <c r="O29" s="86"/>
+      <c r="P29" s="87"/>
       <c r="Q29" s="43"/>
-      <c r="R29" s="188"/>
-      <c r="S29" s="188"/>
+      <c r="R29" s="90"/>
+      <c r="S29" s="90"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="43"/>
       <c r="B30" s="43"/>
-      <c r="C30" s="176"/>
-      <c r="D30" s="176"/>
-      <c r="E30" s="176"/>
-      <c r="F30" s="176"/>
-      <c r="G30" s="176"/>
-      <c r="H30" s="173"/>
-      <c r="I30" s="174"/>
-      <c r="J30" s="174"/>
-      <c r="K30" s="174"/>
-      <c r="L30" s="174"/>
-      <c r="M30" s="175"/>
-      <c r="N30" s="189"/>
-      <c r="O30" s="190"/>
-      <c r="P30" s="191"/>
+      <c r="C30" s="73"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="73"/>
+      <c r="F30" s="73"/>
+      <c r="G30" s="73"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="71"/>
+      <c r="L30" s="71"/>
+      <c r="M30" s="72"/>
+      <c r="N30" s="85"/>
+      <c r="O30" s="86"/>
+      <c r="P30" s="87"/>
       <c r="Q30" s="43"/>
-      <c r="R30" s="188"/>
-      <c r="S30" s="188"/>
+      <c r="R30" s="90"/>
+      <c r="S30" s="90"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="43"/>
       <c r="B31" s="43"/>
-      <c r="C31" s="176"/>
-      <c r="D31" s="176"/>
-      <c r="E31" s="176"/>
-      <c r="F31" s="176"/>
-      <c r="G31" s="176"/>
-      <c r="H31" s="173"/>
-      <c r="I31" s="174"/>
-      <c r="J31" s="174"/>
-      <c r="K31" s="174"/>
-      <c r="L31" s="174"/>
-      <c r="M31" s="175"/>
-      <c r="N31" s="189"/>
-      <c r="O31" s="190"/>
-      <c r="P31" s="191"/>
+      <c r="C31" s="73"/>
+      <c r="D31" s="73"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="73"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="71"/>
+      <c r="L31" s="71"/>
+      <c r="M31" s="72"/>
+      <c r="N31" s="85"/>
+      <c r="O31" s="86"/>
+      <c r="P31" s="87"/>
       <c r="Q31" s="43"/>
-      <c r="R31" s="188"/>
-      <c r="S31" s="188"/>
+      <c r="R31" s="90"/>
+      <c r="S31" s="90"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="43"/>
       <c r="B32" s="43"/>
-      <c r="C32" s="176"/>
-      <c r="D32" s="176"/>
-      <c r="E32" s="176"/>
-      <c r="F32" s="176"/>
-      <c r="G32" s="176"/>
-      <c r="H32" s="173"/>
-      <c r="I32" s="174"/>
-      <c r="J32" s="174"/>
-      <c r="K32" s="174"/>
-      <c r="L32" s="174"/>
-      <c r="M32" s="175"/>
-      <c r="N32" s="189"/>
-      <c r="O32" s="190"/>
-      <c r="P32" s="191"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="73"/>
+      <c r="E32" s="73"/>
+      <c r="F32" s="73"/>
+      <c r="G32" s="73"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="71"/>
+      <c r="L32" s="71"/>
+      <c r="M32" s="72"/>
+      <c r="N32" s="85"/>
+      <c r="O32" s="86"/>
+      <c r="P32" s="87"/>
       <c r="Q32" s="43"/>
-      <c r="R32" s="188"/>
-      <c r="S32" s="188"/>
+      <c r="R32" s="90"/>
+      <c r="S32" s="90"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="43"/>
       <c r="B33" s="43"/>
-      <c r="C33" s="176"/>
-      <c r="D33" s="176"/>
-      <c r="E33" s="176"/>
-      <c r="F33" s="176"/>
-      <c r="G33" s="176"/>
-      <c r="H33" s="173"/>
-      <c r="I33" s="174"/>
-      <c r="J33" s="174"/>
-      <c r="K33" s="174"/>
-      <c r="L33" s="174"/>
-      <c r="M33" s="175"/>
-      <c r="N33" s="189"/>
-      <c r="O33" s="190"/>
-      <c r="P33" s="191"/>
+      <c r="C33" s="73"/>
+      <c r="D33" s="73"/>
+      <c r="E33" s="73"/>
+      <c r="F33" s="73"/>
+      <c r="G33" s="73"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="71"/>
+      <c r="L33" s="71"/>
+      <c r="M33" s="72"/>
+      <c r="N33" s="85"/>
+      <c r="O33" s="86"/>
+      <c r="P33" s="87"/>
       <c r="Q33" s="43"/>
-      <c r="R33" s="188"/>
-      <c r="S33" s="188"/>
+      <c r="R33" s="90"/>
+      <c r="S33" s="90"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="43"/>
       <c r="B34" s="43"/>
-      <c r="C34" s="176"/>
-      <c r="D34" s="176"/>
-      <c r="E34" s="176"/>
-      <c r="F34" s="176"/>
-      <c r="G34" s="176"/>
-      <c r="H34" s="173"/>
-      <c r="I34" s="174"/>
-      <c r="J34" s="174"/>
-      <c r="K34" s="174"/>
-      <c r="L34" s="174"/>
-      <c r="M34" s="175"/>
-      <c r="N34" s="189"/>
-      <c r="O34" s="190"/>
-      <c r="P34" s="191"/>
+      <c r="C34" s="73"/>
+      <c r="D34" s="73"/>
+      <c r="E34" s="73"/>
+      <c r="F34" s="73"/>
+      <c r="G34" s="73"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="71"/>
+      <c r="K34" s="71"/>
+      <c r="L34" s="71"/>
+      <c r="M34" s="72"/>
+      <c r="N34" s="85"/>
+      <c r="O34" s="86"/>
+      <c r="P34" s="87"/>
       <c r="Q34" s="43"/>
-      <c r="R34" s="188"/>
-      <c r="S34" s="188"/>
+      <c r="R34" s="90"/>
+      <c r="S34" s="90"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="43"/>
       <c r="B35" s="43"/>
-      <c r="C35" s="176"/>
-      <c r="D35" s="176"/>
-      <c r="E35" s="176"/>
-      <c r="F35" s="176"/>
-      <c r="G35" s="176"/>
-      <c r="H35" s="173"/>
-      <c r="I35" s="174"/>
-      <c r="J35" s="174"/>
-      <c r="K35" s="174"/>
-      <c r="L35" s="174"/>
-      <c r="M35" s="175"/>
-      <c r="N35" s="189"/>
-      <c r="O35" s="190"/>
-      <c r="P35" s="191"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="73"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="71"/>
+      <c r="L35" s="71"/>
+      <c r="M35" s="72"/>
+      <c r="N35" s="85"/>
+      <c r="O35" s="86"/>
+      <c r="P35" s="87"/>
       <c r="Q35" s="43"/>
-      <c r="R35" s="188"/>
-      <c r="S35" s="188"/>
+      <c r="R35" s="90"/>
+      <c r="S35" s="90"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="43"/>
       <c r="B36" s="43"/>
-      <c r="C36" s="176"/>
-      <c r="D36" s="176"/>
-      <c r="E36" s="176"/>
-      <c r="F36" s="176"/>
-      <c r="G36" s="176"/>
-      <c r="H36" s="173"/>
-      <c r="I36" s="174"/>
-      <c r="J36" s="174"/>
-      <c r="K36" s="174"/>
-      <c r="L36" s="174"/>
-      <c r="M36" s="175"/>
-      <c r="N36" s="189"/>
-      <c r="O36" s="190"/>
-      <c r="P36" s="191"/>
+      <c r="C36" s="73"/>
+      <c r="D36" s="73"/>
+      <c r="E36" s="73"/>
+      <c r="F36" s="73"/>
+      <c r="G36" s="73"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="71"/>
+      <c r="L36" s="71"/>
+      <c r="M36" s="72"/>
+      <c r="N36" s="85"/>
+      <c r="O36" s="86"/>
+      <c r="P36" s="87"/>
       <c r="Q36" s="43"/>
-      <c r="R36" s="188"/>
-      <c r="S36" s="188"/>
+      <c r="R36" s="90"/>
+      <c r="S36" s="90"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="43"/>
       <c r="B37" s="43"/>
-      <c r="C37" s="176"/>
-      <c r="D37" s="176"/>
-      <c r="E37" s="176"/>
-      <c r="F37" s="176"/>
-      <c r="G37" s="176"/>
-      <c r="H37" s="173"/>
-      <c r="I37" s="174"/>
-      <c r="J37" s="174"/>
-      <c r="K37" s="174"/>
-      <c r="L37" s="174"/>
-      <c r="M37" s="175"/>
-      <c r="N37" s="189"/>
-      <c r="O37" s="190"/>
-      <c r="P37" s="191"/>
+      <c r="C37" s="73"/>
+      <c r="D37" s="73"/>
+      <c r="E37" s="73"/>
+      <c r="F37" s="73"/>
+      <c r="G37" s="73"/>
+      <c r="H37" s="70"/>
+      <c r="I37" s="71"/>
+      <c r="J37" s="71"/>
+      <c r="K37" s="71"/>
+      <c r="L37" s="71"/>
+      <c r="M37" s="72"/>
+      <c r="N37" s="85"/>
+      <c r="O37" s="86"/>
+      <c r="P37" s="87"/>
       <c r="Q37" s="43"/>
-      <c r="R37" s="188"/>
-      <c r="S37" s="188"/>
+      <c r="R37" s="90"/>
+      <c r="S37" s="90"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="43"/>
       <c r="B38" s="43"/>
-      <c r="C38" s="176"/>
-      <c r="D38" s="176"/>
-      <c r="E38" s="176"/>
-      <c r="F38" s="176"/>
-      <c r="G38" s="176"/>
-      <c r="H38" s="173"/>
-      <c r="I38" s="174"/>
-      <c r="J38" s="174"/>
-      <c r="K38" s="174"/>
-      <c r="L38" s="174"/>
-      <c r="M38" s="175"/>
-      <c r="N38" s="189"/>
-      <c r="O38" s="190"/>
-      <c r="P38" s="191"/>
+      <c r="C38" s="73"/>
+      <c r="D38" s="73"/>
+      <c r="E38" s="73"/>
+      <c r="F38" s="73"/>
+      <c r="G38" s="73"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="71"/>
+      <c r="L38" s="71"/>
+      <c r="M38" s="72"/>
+      <c r="N38" s="85"/>
+      <c r="O38" s="86"/>
+      <c r="P38" s="87"/>
       <c r="Q38" s="43"/>
-      <c r="R38" s="188"/>
-      <c r="S38" s="188"/>
+      <c r="R38" s="90"/>
+      <c r="S38" s="90"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="43"/>
       <c r="B39" s="43"/>
-      <c r="C39" s="176"/>
-      <c r="D39" s="176"/>
-      <c r="E39" s="176"/>
-      <c r="F39" s="176"/>
-      <c r="G39" s="176"/>
-      <c r="H39" s="173"/>
-      <c r="I39" s="174"/>
-      <c r="J39" s="174"/>
-      <c r="K39" s="174"/>
-      <c r="L39" s="174"/>
-      <c r="M39" s="175"/>
-      <c r="N39" s="189"/>
-      <c r="O39" s="190"/>
-      <c r="P39" s="191"/>
+      <c r="C39" s="73"/>
+      <c r="D39" s="73"/>
+      <c r="E39" s="73"/>
+      <c r="F39" s="73"/>
+      <c r="G39" s="73"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
+      <c r="K39" s="71"/>
+      <c r="L39" s="71"/>
+      <c r="M39" s="72"/>
+      <c r="N39" s="85"/>
+      <c r="O39" s="86"/>
+      <c r="P39" s="87"/>
       <c r="Q39" s="43"/>
-      <c r="R39" s="188"/>
-      <c r="S39" s="188"/>
+      <c r="R39" s="90"/>
+      <c r="S39" s="90"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="43"/>
       <c r="B40" s="43"/>
-      <c r="C40" s="176"/>
-      <c r="D40" s="176"/>
-      <c r="E40" s="176"/>
-      <c r="F40" s="176"/>
-      <c r="G40" s="176"/>
-      <c r="H40" s="173"/>
-      <c r="I40" s="174"/>
-      <c r="J40" s="174"/>
-      <c r="K40" s="174"/>
-      <c r="L40" s="174"/>
-      <c r="M40" s="175"/>
-      <c r="N40" s="189"/>
-      <c r="O40" s="190"/>
-      <c r="P40" s="191"/>
+      <c r="C40" s="73"/>
+      <c r="D40" s="73"/>
+      <c r="E40" s="73"/>
+      <c r="F40" s="73"/>
+      <c r="G40" s="73"/>
+      <c r="H40" s="70"/>
+      <c r="I40" s="71"/>
+      <c r="J40" s="71"/>
+      <c r="K40" s="71"/>
+      <c r="L40" s="71"/>
+      <c r="M40" s="72"/>
+      <c r="N40" s="85"/>
+      <c r="O40" s="86"/>
+      <c r="P40" s="87"/>
       <c r="Q40" s="43"/>
-      <c r="R40" s="188"/>
-      <c r="S40" s="188"/>
+      <c r="R40" s="90"/>
+      <c r="S40" s="90"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="43"/>
       <c r="B41" s="43"/>
-      <c r="C41" s="176"/>
-      <c r="D41" s="176"/>
-      <c r="E41" s="176"/>
-      <c r="F41" s="176"/>
-      <c r="G41" s="176"/>
-      <c r="H41" s="173"/>
-      <c r="I41" s="174"/>
-      <c r="J41" s="174"/>
-      <c r="K41" s="174"/>
-      <c r="L41" s="174"/>
-      <c r="M41" s="175"/>
-      <c r="N41" s="189"/>
-      <c r="O41" s="190"/>
-      <c r="P41" s="191"/>
+      <c r="C41" s="73"/>
+      <c r="D41" s="73"/>
+      <c r="E41" s="73"/>
+      <c r="F41" s="73"/>
+      <c r="G41" s="73"/>
+      <c r="H41" s="70"/>
+      <c r="I41" s="71"/>
+      <c r="J41" s="71"/>
+      <c r="K41" s="71"/>
+      <c r="L41" s="71"/>
+      <c r="M41" s="72"/>
+      <c r="N41" s="85"/>
+      <c r="O41" s="86"/>
+      <c r="P41" s="87"/>
       <c r="Q41" s="43"/>
-      <c r="R41" s="188"/>
-      <c r="S41" s="188"/>
+      <c r="R41" s="90"/>
+      <c r="S41" s="90"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="43"/>
       <c r="B42" s="43"/>
-      <c r="C42" s="176"/>
-      <c r="D42" s="176"/>
-      <c r="E42" s="176"/>
-      <c r="F42" s="176"/>
-      <c r="G42" s="176"/>
-      <c r="H42" s="173"/>
-      <c r="I42" s="174"/>
-      <c r="J42" s="174"/>
-      <c r="K42" s="174"/>
-      <c r="L42" s="174"/>
-      <c r="M42" s="175"/>
-      <c r="N42" s="189"/>
-      <c r="O42" s="190"/>
-      <c r="P42" s="191"/>
+      <c r="C42" s="73"/>
+      <c r="D42" s="73"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="73"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="71"/>
+      <c r="L42" s="71"/>
+      <c r="M42" s="72"/>
+      <c r="N42" s="85"/>
+      <c r="O42" s="86"/>
+      <c r="P42" s="87"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="188"/>
-      <c r="S42" s="188"/>
+      <c r="R42" s="90"/>
+      <c r="S42" s="90"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="43"/>
       <c r="B43" s="43"/>
-      <c r="C43" s="176"/>
-      <c r="D43" s="176"/>
-      <c r="E43" s="176"/>
-      <c r="F43" s="176"/>
-      <c r="G43" s="176"/>
-      <c r="H43" s="173"/>
-      <c r="I43" s="174"/>
-      <c r="J43" s="174"/>
-      <c r="K43" s="174"/>
-      <c r="L43" s="174"/>
-      <c r="M43" s="175"/>
-      <c r="N43" s="189"/>
-      <c r="O43" s="190"/>
-      <c r="P43" s="191"/>
+      <c r="C43" s="73"/>
+      <c r="D43" s="73"/>
+      <c r="E43" s="73"/>
+      <c r="F43" s="73"/>
+      <c r="G43" s="73"/>
+      <c r="H43" s="70"/>
+      <c r="I43" s="71"/>
+      <c r="J43" s="71"/>
+      <c r="K43" s="71"/>
+      <c r="L43" s="71"/>
+      <c r="M43" s="72"/>
+      <c r="N43" s="85"/>
+      <c r="O43" s="86"/>
+      <c r="P43" s="87"/>
       <c r="Q43" s="43"/>
-      <c r="R43" s="188"/>
-      <c r="S43" s="188"/>
+      <c r="R43" s="90"/>
+      <c r="S43" s="90"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="43"/>
       <c r="B44" s="43"/>
-      <c r="C44" s="176"/>
-      <c r="D44" s="176"/>
-      <c r="E44" s="176"/>
-      <c r="F44" s="176"/>
-      <c r="G44" s="176"/>
-      <c r="H44" s="173"/>
-      <c r="I44" s="174"/>
-      <c r="J44" s="174"/>
-      <c r="K44" s="174"/>
-      <c r="L44" s="174"/>
-      <c r="M44" s="175"/>
-      <c r="N44" s="189"/>
-      <c r="O44" s="190"/>
-      <c r="P44" s="191"/>
+      <c r="C44" s="73"/>
+      <c r="D44" s="73"/>
+      <c r="E44" s="73"/>
+      <c r="F44" s="73"/>
+      <c r="G44" s="73"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="71"/>
+      <c r="L44" s="71"/>
+      <c r="M44" s="72"/>
+      <c r="N44" s="85"/>
+      <c r="O44" s="86"/>
+      <c r="P44" s="87"/>
       <c r="Q44" s="43"/>
-      <c r="R44" s="188"/>
-      <c r="S44" s="188"/>
+      <c r="R44" s="90"/>
+      <c r="S44" s="90"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="43"/>
       <c r="B45" s="43"/>
-      <c r="C45" s="176"/>
-      <c r="D45" s="176"/>
-      <c r="E45" s="176"/>
-      <c r="F45" s="176"/>
-      <c r="G45" s="176"/>
-      <c r="H45" s="173"/>
-      <c r="I45" s="174"/>
-      <c r="J45" s="174"/>
-      <c r="K45" s="174"/>
-      <c r="L45" s="174"/>
-      <c r="M45" s="175"/>
-      <c r="N45" s="189"/>
-      <c r="O45" s="190"/>
-      <c r="P45" s="191"/>
+      <c r="C45" s="73"/>
+      <c r="D45" s="73"/>
+      <c r="E45" s="73"/>
+      <c r="F45" s="73"/>
+      <c r="G45" s="73"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="71"/>
+      <c r="L45" s="71"/>
+      <c r="M45" s="72"/>
+      <c r="N45" s="85"/>
+      <c r="O45" s="86"/>
+      <c r="P45" s="87"/>
       <c r="Q45" s="43"/>
-      <c r="R45" s="188"/>
-      <c r="S45" s="188"/>
+      <c r="R45" s="90"/>
+      <c r="S45" s="90"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="43"/>
       <c r="B46" s="43"/>
-      <c r="C46" s="176"/>
-      <c r="D46" s="176"/>
-      <c r="E46" s="176"/>
-      <c r="F46" s="176"/>
-      <c r="G46" s="176"/>
-      <c r="H46" s="173"/>
-      <c r="I46" s="174"/>
-      <c r="J46" s="174"/>
-      <c r="K46" s="174"/>
-      <c r="L46" s="174"/>
-      <c r="M46" s="175"/>
-      <c r="N46" s="189"/>
-      <c r="O46" s="190"/>
-      <c r="P46" s="191"/>
+      <c r="C46" s="73"/>
+      <c r="D46" s="73"/>
+      <c r="E46" s="73"/>
+      <c r="F46" s="73"/>
+      <c r="G46" s="73"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="71"/>
+      <c r="L46" s="71"/>
+      <c r="M46" s="72"/>
+      <c r="N46" s="85"/>
+      <c r="O46" s="86"/>
+      <c r="P46" s="87"/>
       <c r="Q46" s="43"/>
-      <c r="R46" s="188"/>
-      <c r="S46" s="188"/>
+      <c r="R46" s="90"/>
+      <c r="S46" s="90"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="43"/>
       <c r="B47" s="43"/>
-      <c r="C47" s="176"/>
-      <c r="D47" s="176"/>
-      <c r="E47" s="176"/>
-      <c r="F47" s="176"/>
-      <c r="G47" s="176"/>
-      <c r="H47" s="173"/>
-      <c r="I47" s="174"/>
-      <c r="J47" s="174"/>
-      <c r="K47" s="174"/>
-      <c r="L47" s="174"/>
-      <c r="M47" s="175"/>
-      <c r="N47" s="189"/>
-      <c r="O47" s="190"/>
-      <c r="P47" s="191"/>
+      <c r="C47" s="73"/>
+      <c r="D47" s="73"/>
+      <c r="E47" s="73"/>
+      <c r="F47" s="73"/>
+      <c r="G47" s="73"/>
+      <c r="H47" s="70"/>
+      <c r="I47" s="71"/>
+      <c r="J47" s="71"/>
+      <c r="K47" s="71"/>
+      <c r="L47" s="71"/>
+      <c r="M47" s="72"/>
+      <c r="N47" s="85"/>
+      <c r="O47" s="86"/>
+      <c r="P47" s="87"/>
       <c r="Q47" s="43"/>
-      <c r="R47" s="188"/>
-      <c r="S47" s="188"/>
+      <c r="R47" s="90"/>
+      <c r="S47" s="90"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="43"/>
       <c r="B48" s="43"/>
-      <c r="C48" s="176"/>
-      <c r="D48" s="176"/>
-      <c r="E48" s="176"/>
-      <c r="F48" s="176"/>
-      <c r="G48" s="176"/>
-      <c r="H48" s="173"/>
-      <c r="I48" s="174"/>
-      <c r="J48" s="174"/>
-      <c r="K48" s="174"/>
-      <c r="L48" s="174"/>
-      <c r="M48" s="175"/>
-      <c r="N48" s="189"/>
-      <c r="O48" s="190"/>
-      <c r="P48" s="191"/>
+      <c r="C48" s="73"/>
+      <c r="D48" s="73"/>
+      <c r="E48" s="73"/>
+      <c r="F48" s="73"/>
+      <c r="G48" s="73"/>
+      <c r="H48" s="70"/>
+      <c r="I48" s="71"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="71"/>
+      <c r="L48" s="71"/>
+      <c r="M48" s="72"/>
+      <c r="N48" s="85"/>
+      <c r="O48" s="86"/>
+      <c r="P48" s="87"/>
       <c r="Q48" s="43"/>
-      <c r="R48" s="188"/>
-      <c r="S48" s="188"/>
+      <c r="R48" s="90"/>
+      <c r="S48" s="90"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="43"/>
       <c r="B49" s="43"/>
-      <c r="C49" s="176"/>
-      <c r="D49" s="176"/>
-      <c r="E49" s="176"/>
-      <c r="F49" s="176"/>
-      <c r="G49" s="176"/>
-      <c r="H49" s="173"/>
-      <c r="I49" s="174"/>
-      <c r="J49" s="174"/>
-      <c r="K49" s="174"/>
-      <c r="L49" s="174"/>
-      <c r="M49" s="175"/>
-      <c r="N49" s="189"/>
-      <c r="O49" s="190"/>
-      <c r="P49" s="191"/>
+      <c r="C49" s="73"/>
+      <c r="D49" s="73"/>
+      <c r="E49" s="73"/>
+      <c r="F49" s="73"/>
+      <c r="G49" s="73"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="71"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="71"/>
+      <c r="L49" s="71"/>
+      <c r="M49" s="72"/>
+      <c r="N49" s="85"/>
+      <c r="O49" s="86"/>
+      <c r="P49" s="87"/>
       <c r="Q49" s="43"/>
-      <c r="R49" s="188"/>
-      <c r="S49" s="188"/>
+      <c r="R49" s="90"/>
+      <c r="S49" s="90"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="43"/>
       <c r="B50" s="43"/>
-      <c r="C50" s="176"/>
-      <c r="D50" s="176"/>
-      <c r="E50" s="176"/>
-      <c r="F50" s="176"/>
-      <c r="G50" s="176"/>
-      <c r="H50" s="173"/>
-      <c r="I50" s="174"/>
-      <c r="J50" s="174"/>
-      <c r="K50" s="174"/>
-      <c r="L50" s="174"/>
-      <c r="M50" s="175"/>
-      <c r="N50" s="189"/>
-      <c r="O50" s="190"/>
-      <c r="P50" s="191"/>
+      <c r="C50" s="73"/>
+      <c r="D50" s="73"/>
+      <c r="E50" s="73"/>
+      <c r="F50" s="73"/>
+      <c r="G50" s="73"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="71"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="71"/>
+      <c r="L50" s="71"/>
+      <c r="M50" s="72"/>
+      <c r="N50" s="85"/>
+      <c r="O50" s="86"/>
+      <c r="P50" s="87"/>
       <c r="Q50" s="43"/>
-      <c r="R50" s="188"/>
-      <c r="S50" s="188"/>
+      <c r="R50" s="90"/>
+      <c r="S50" s="90"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="43"/>
       <c r="B51" s="43"/>
-      <c r="C51" s="176"/>
-      <c r="D51" s="176"/>
-      <c r="E51" s="176"/>
-      <c r="F51" s="176"/>
-      <c r="G51" s="176"/>
-      <c r="H51" s="173"/>
-      <c r="I51" s="174"/>
-      <c r="J51" s="174"/>
-      <c r="K51" s="174"/>
-      <c r="L51" s="174"/>
-      <c r="M51" s="175"/>
-      <c r="N51" s="189"/>
-      <c r="O51" s="190"/>
-      <c r="P51" s="191"/>
+      <c r="C51" s="73"/>
+      <c r="D51" s="73"/>
+      <c r="E51" s="73"/>
+      <c r="F51" s="73"/>
+      <c r="G51" s="73"/>
+      <c r="H51" s="70"/>
+      <c r="I51" s="71"/>
+      <c r="J51" s="71"/>
+      <c r="K51" s="71"/>
+      <c r="L51" s="71"/>
+      <c r="M51" s="72"/>
+      <c r="N51" s="85"/>
+      <c r="O51" s="86"/>
+      <c r="P51" s="87"/>
       <c r="Q51" s="43"/>
-      <c r="R51" s="188"/>
-      <c r="S51" s="188"/>
+      <c r="R51" s="90"/>
+      <c r="S51" s="90"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="43"/>
       <c r="B52" s="43"/>
-      <c r="C52" s="176"/>
-      <c r="D52" s="176"/>
-      <c r="E52" s="176"/>
-      <c r="F52" s="176"/>
-      <c r="G52" s="176"/>
-      <c r="H52" s="173"/>
-      <c r="I52" s="174"/>
-      <c r="J52" s="174"/>
-      <c r="K52" s="174"/>
-      <c r="L52" s="174"/>
-      <c r="M52" s="175"/>
-      <c r="N52" s="189"/>
-      <c r="O52" s="190"/>
-      <c r="P52" s="191"/>
+      <c r="C52" s="73"/>
+      <c r="D52" s="73"/>
+      <c r="E52" s="73"/>
+      <c r="F52" s="73"/>
+      <c r="G52" s="73"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="71"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="71"/>
+      <c r="L52" s="71"/>
+      <c r="M52" s="72"/>
+      <c r="N52" s="85"/>
+      <c r="O52" s="86"/>
+      <c r="P52" s="87"/>
       <c r="Q52" s="43"/>
-      <c r="R52" s="188"/>
-      <c r="S52" s="188"/>
+      <c r="R52" s="90"/>
+      <c r="S52" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="205">
@@ -13207,6 +13171,9 @@
     <mergeCell ref="N18:P18"/>
     <mergeCell ref="N19:P19"/>
     <mergeCell ref="N27:P27"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="N32:P32"/>
     <mergeCell ref="R51:S51"/>
     <mergeCell ref="R52:S52"/>
     <mergeCell ref="R42:S42"/>
@@ -13222,9 +13189,6 @@
     <mergeCell ref="R39:S39"/>
     <mergeCell ref="N51:P51"/>
     <mergeCell ref="N52:P52"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="N32:P32"/>
     <mergeCell ref="N33:P33"/>
     <mergeCell ref="R46:S46"/>
     <mergeCell ref="R47:S47"/>
@@ -13377,7 +13341,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{856D1627-8005-4B47-8BAF-6B30EC10C042}">
-  <dimension ref="A1:BA59"/>
+  <dimension ref="A1:BA55"/>
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="3" style="47" customWidth="1"/>
@@ -13438,7 +13402,7 @@
       <c r="AR1" s="213"/>
       <c r="AS1" s="213"/>
       <c r="AT1" s="207">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="AU1" s="208"/>
       <c r="AV1" s="208"/>
@@ -14924,81 +14888,98 @@
       <c r="AK42" s="54"/>
       <c r="BA42" s="53"/>
     </row>
-    <row r="43" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A43" s="55"/>
-      <c r="B43" s="54"/>
-      <c r="C43" s="54"/>
-      <c r="D43" s="54"/>
-      <c r="E43" s="54"/>
-      <c r="F43" s="54"/>
-      <c r="G43" s="54"/>
-      <c r="H43" s="54"/>
-      <c r="I43" s="54"/>
-      <c r="J43" s="54"/>
-      <c r="K43" s="54"/>
-      <c r="L43" s="54"/>
-      <c r="M43" s="54"/>
-      <c r="N43" s="54"/>
-      <c r="O43" s="54"/>
-      <c r="P43" s="54"/>
-      <c r="Q43" s="54"/>
-      <c r="R43" s="54"/>
-      <c r="S43" s="54"/>
-      <c r="T43" s="54"/>
-      <c r="U43" s="54"/>
-      <c r="V43" s="54"/>
-      <c r="W43" s="54"/>
-      <c r="X43" s="54"/>
-      <c r="Y43" s="54"/>
-      <c r="Z43" s="54"/>
-      <c r="AA43" s="54"/>
-      <c r="AB43" s="54"/>
-      <c r="AC43" s="54"/>
-      <c r="AD43" s="54"/>
-      <c r="AE43" s="54"/>
-      <c r="AF43" s="54"/>
-      <c r="AG43" s="54"/>
-      <c r="AH43" s="54"/>
-      <c r="AI43" s="54"/>
-      <c r="AJ43" s="54"/>
-      <c r="AK43" s="54"/>
-      <c r="BA43" s="53"/>
+    <row r="43" spans="1:53" ht="18" customHeight="1">
+      <c r="A43" s="204" t="s">
+        <v>91</v>
+      </c>
+      <c r="B43" s="205"/>
+      <c r="C43" s="205"/>
+      <c r="D43" s="205"/>
+      <c r="E43" s="205"/>
+      <c r="F43" s="205"/>
+      <c r="G43" s="205"/>
+      <c r="H43" s="205"/>
+      <c r="I43" s="205"/>
+      <c r="J43" s="205"/>
+      <c r="K43" s="205"/>
+      <c r="L43" s="205"/>
+      <c r="M43" s="205"/>
+      <c r="N43" s="205"/>
+      <c r="O43" s="205"/>
+      <c r="P43" s="205"/>
+      <c r="Q43" s="205"/>
+      <c r="R43" s="205"/>
+      <c r="S43" s="205"/>
+      <c r="T43" s="205"/>
+      <c r="U43" s="205"/>
+      <c r="V43" s="205"/>
+      <c r="W43" s="205"/>
+      <c r="X43" s="205"/>
+      <c r="Y43" s="205"/>
+      <c r="Z43" s="205"/>
+      <c r="AA43" s="205"/>
+      <c r="AB43" s="205"/>
+      <c r="AC43" s="205"/>
+      <c r="AD43" s="205"/>
+      <c r="AE43" s="205"/>
+      <c r="AF43" s="205"/>
+      <c r="AG43" s="205"/>
+      <c r="AH43" s="205"/>
+      <c r="AI43" s="205"/>
+      <c r="AJ43" s="205"/>
+      <c r="AK43" s="205"/>
+      <c r="AL43" s="205"/>
+      <c r="AM43" s="205"/>
+      <c r="AN43" s="205"/>
+      <c r="AO43" s="205"/>
+      <c r="AP43" s="205"/>
+      <c r="AQ43" s="205"/>
+      <c r="AR43" s="205"/>
+      <c r="AS43" s="205"/>
+      <c r="AT43" s="205"/>
+      <c r="AU43" s="205"/>
+      <c r="AV43" s="205"/>
+      <c r="AW43" s="205"/>
+      <c r="AX43" s="205"/>
+      <c r="AY43" s="205"/>
+      <c r="AZ43" s="205"/>
+      <c r="BA43" s="206"/>
     </row>
     <row r="44" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A44" s="55"/>
-      <c r="B44" s="54"/>
-      <c r="C44" s="54"/>
-      <c r="D44" s="54"/>
-      <c r="E44" s="54"/>
-      <c r="F44" s="54"/>
-      <c r="G44" s="54"/>
-      <c r="H44" s="54"/>
-      <c r="I44" s="54"/>
-      <c r="J44" s="54"/>
-      <c r="K44" s="54"/>
-      <c r="L44" s="54"/>
-      <c r="M44" s="54"/>
-      <c r="N44" s="54"/>
-      <c r="O44" s="54"/>
-      <c r="P44" s="54"/>
-      <c r="Q44" s="54"/>
-      <c r="R44" s="54"/>
-      <c r="S44" s="54"/>
-      <c r="T44" s="54"/>
-      <c r="U44" s="54"/>
-      <c r="V44" s="54"/>
-      <c r="W44" s="54"/>
-      <c r="X44" s="54"/>
-      <c r="Y44" s="54"/>
-      <c r="Z44" s="54"/>
-      <c r="AA44" s="54"/>
-      <c r="AB44" s="54"/>
-      <c r="AC44" s="54"/>
-      <c r="AD44" s="54"/>
-      <c r="AE44" s="54"/>
-      <c r="AF44" s="54"/>
-      <c r="AG44" s="54"/>
-      <c r="AH44" s="54"/>
+      <c r="A44" s="57"/>
+      <c r="B44" s="56"/>
+      <c r="C44" s="56"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="56"/>
+      <c r="F44" s="56"/>
+      <c r="G44" s="56"/>
+      <c r="H44" s="56"/>
+      <c r="I44" s="56"/>
+      <c r="J44" s="56"/>
+      <c r="K44" s="56"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="56"/>
+      <c r="N44" s="56"/>
+      <c r="O44" s="56"/>
+      <c r="P44" s="56"/>
+      <c r="Q44" s="56"/>
+      <c r="R44" s="56"/>
+      <c r="S44" s="56"/>
+      <c r="T44" s="56"/>
+      <c r="U44" s="56"/>
+      <c r="V44" s="56"/>
+      <c r="W44" s="56"/>
+      <c r="X44" s="56"/>
+      <c r="Y44" s="56"/>
+      <c r="Z44" s="56"/>
+      <c r="AA44" s="56"/>
+      <c r="AB44" s="56"/>
+      <c r="AC44" s="56"/>
+      <c r="AD44" s="56"/>
+      <c r="AE44" s="56"/>
+      <c r="AF44" s="56"/>
+      <c r="AG44" s="56"/>
+      <c r="AH44" s="56"/>
       <c r="AI44" s="54"/>
       <c r="AJ44" s="54"/>
       <c r="AK44" s="54"/>
@@ -15084,98 +15065,81 @@
       <c r="AK46" s="54"/>
       <c r="BA46" s="53"/>
     </row>
-    <row r="47" spans="1:53" ht="18" customHeight="1">
-      <c r="A47" s="204" t="s">
-        <v>91</v>
-      </c>
-      <c r="B47" s="205"/>
-      <c r="C47" s="205"/>
-      <c r="D47" s="205"/>
-      <c r="E47" s="205"/>
-      <c r="F47" s="205"/>
-      <c r="G47" s="205"/>
-      <c r="H47" s="205"/>
-      <c r="I47" s="205"/>
-      <c r="J47" s="205"/>
-      <c r="K47" s="205"/>
-      <c r="L47" s="205"/>
-      <c r="M47" s="205"/>
-      <c r="N47" s="205"/>
-      <c r="O47" s="205"/>
-      <c r="P47" s="205"/>
-      <c r="Q47" s="205"/>
-      <c r="R47" s="205"/>
-      <c r="S47" s="205"/>
-      <c r="T47" s="205"/>
-      <c r="U47" s="205"/>
-      <c r="V47" s="205"/>
-      <c r="W47" s="205"/>
-      <c r="X47" s="205"/>
-      <c r="Y47" s="205"/>
-      <c r="Z47" s="205"/>
-      <c r="AA47" s="205"/>
-      <c r="AB47" s="205"/>
-      <c r="AC47" s="205"/>
-      <c r="AD47" s="205"/>
-      <c r="AE47" s="205"/>
-      <c r="AF47" s="205"/>
-      <c r="AG47" s="205"/>
-      <c r="AH47" s="205"/>
-      <c r="AI47" s="205"/>
-      <c r="AJ47" s="205"/>
-      <c r="AK47" s="205"/>
-      <c r="AL47" s="205"/>
-      <c r="AM47" s="205"/>
-      <c r="AN47" s="205"/>
-      <c r="AO47" s="205"/>
-      <c r="AP47" s="205"/>
-      <c r="AQ47" s="205"/>
-      <c r="AR47" s="205"/>
-      <c r="AS47" s="205"/>
-      <c r="AT47" s="205"/>
-      <c r="AU47" s="205"/>
-      <c r="AV47" s="205"/>
-      <c r="AW47" s="205"/>
-      <c r="AX47" s="205"/>
-      <c r="AY47" s="205"/>
-      <c r="AZ47" s="205"/>
-      <c r="BA47" s="206"/>
+    <row r="47" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A47" s="55"/>
+      <c r="B47" s="54"/>
+      <c r="C47" s="54"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="54"/>
+      <c r="J47" s="54"/>
+      <c r="K47" s="54"/>
+      <c r="L47" s="54"/>
+      <c r="M47" s="54"/>
+      <c r="N47" s="54"/>
+      <c r="O47" s="54"/>
+      <c r="P47" s="54"/>
+      <c r="Q47" s="54"/>
+      <c r="R47" s="54"/>
+      <c r="S47" s="54"/>
+      <c r="T47" s="54"/>
+      <c r="U47" s="54"/>
+      <c r="V47" s="54"/>
+      <c r="W47" s="54"/>
+      <c r="X47" s="54"/>
+      <c r="Y47" s="54"/>
+      <c r="Z47" s="54"/>
+      <c r="AA47" s="54"/>
+      <c r="AB47" s="54"/>
+      <c r="AC47" s="54"/>
+      <c r="AD47" s="54"/>
+      <c r="AE47" s="54"/>
+      <c r="AF47" s="54"/>
+      <c r="AG47" s="54"/>
+      <c r="AH47" s="54"/>
+      <c r="AI47" s="54"/>
+      <c r="AJ47" s="54"/>
+      <c r="AK47" s="54"/>
+      <c r="BA47" s="53"/>
     </row>
     <row r="48" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A48" s="57"/>
-      <c r="B48" s="56"/>
-      <c r="C48" s="56"/>
-      <c r="D48" s="56"/>
-      <c r="E48" s="56"/>
-      <c r="F48" s="56"/>
-      <c r="G48" s="56"/>
-      <c r="H48" s="56"/>
-      <c r="I48" s="56"/>
-      <c r="J48" s="56"/>
-      <c r="K48" s="56"/>
-      <c r="L48" s="56"/>
-      <c r="M48" s="56"/>
-      <c r="N48" s="56"/>
-      <c r="O48" s="56"/>
-      <c r="P48" s="56"/>
-      <c r="Q48" s="56"/>
-      <c r="R48" s="56"/>
-      <c r="S48" s="56"/>
-      <c r="T48" s="56"/>
-      <c r="U48" s="56"/>
-      <c r="V48" s="56"/>
-      <c r="W48" s="56"/>
-      <c r="X48" s="56"/>
-      <c r="Y48" s="56"/>
-      <c r="Z48" s="56"/>
-      <c r="AA48" s="56"/>
-      <c r="AB48" s="56"/>
-      <c r="AC48" s="56"/>
-      <c r="AD48" s="56"/>
-      <c r="AE48" s="56"/>
-      <c r="AF48" s="56"/>
-      <c r="AG48" s="56"/>
-      <c r="AH48" s="56"/>
+      <c r="A48" s="55"/>
+      <c r="B48" s="54"/>
+      <c r="C48" s="54"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="54"/>
+      <c r="J48" s="54"/>
+      <c r="K48" s="54"/>
+      <c r="L48" s="54"/>
+      <c r="M48" s="54"/>
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
+      <c r="R48" s="54"/>
+      <c r="S48" s="54"/>
+      <c r="T48" s="54"/>
+      <c r="U48" s="54"/>
+      <c r="V48" s="54"/>
+      <c r="W48" s="54"/>
+      <c r="X48" s="54"/>
+      <c r="Y48" s="54"/>
+      <c r="Z48" s="54"/>
+      <c r="AA48" s="54"/>
+      <c r="AB48" s="54"/>
+      <c r="AC48" s="54"/>
+      <c r="AD48" s="54"/>
+      <c r="AE48" s="54"/>
+      <c r="AF48" s="54"/>
+      <c r="AG48" s="54"/>
+      <c r="AH48" s="54"/>
       <c r="AI48" s="54"/>
       <c r="AJ48" s="54"/>
       <c r="AK48" s="54"/>
@@ -15262,122 +15226,139 @@
       <c r="BA50" s="53"/>
     </row>
     <row r="51" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A51" s="55"/>
-      <c r="B51" s="54"/>
-      <c r="C51" s="54"/>
-      <c r="D51" s="54"/>
-      <c r="E51" s="54"/>
-      <c r="F51" s="54"/>
-      <c r="G51" s="54"/>
-      <c r="H51" s="54"/>
-      <c r="I51" s="54"/>
-      <c r="J51" s="54"/>
-      <c r="K51" s="54"/>
-      <c r="L51" s="54"/>
-      <c r="M51" s="54"/>
-      <c r="N51" s="54"/>
-      <c r="O51" s="54"/>
-      <c r="P51" s="54"/>
-      <c r="Q51" s="54"/>
-      <c r="R51" s="54"/>
-      <c r="S51" s="54"/>
-      <c r="T51" s="54"/>
-      <c r="U51" s="54"/>
-      <c r="V51" s="54"/>
-      <c r="W51" s="54"/>
-      <c r="X51" s="54"/>
-      <c r="Y51" s="54"/>
-      <c r="Z51" s="54"/>
-      <c r="AA51" s="54"/>
-      <c r="AB51" s="54"/>
-      <c r="AC51" s="54"/>
-      <c r="AD51" s="54"/>
-      <c r="AE51" s="54"/>
-      <c r="AF51" s="54"/>
-      <c r="AG51" s="54"/>
-      <c r="AH51" s="54"/>
-      <c r="AI51" s="54"/>
-      <c r="AJ51" s="54"/>
+      <c r="A51" s="52"/>
+      <c r="B51" s="51"/>
+      <c r="C51" s="51"/>
+      <c r="D51" s="51"/>
+      <c r="E51" s="51"/>
+      <c r="F51" s="51"/>
+      <c r="G51" s="51"/>
+      <c r="H51" s="51"/>
+      <c r="I51" s="51"/>
+      <c r="J51" s="51"/>
+      <c r="K51" s="51"/>
+      <c r="L51" s="51"/>
+      <c r="M51" s="51"/>
+      <c r="N51" s="51"/>
+      <c r="O51" s="51"/>
+      <c r="P51" s="51"/>
+      <c r="Q51" s="51"/>
+      <c r="R51" s="51"/>
+      <c r="S51" s="51"/>
+      <c r="T51" s="51"/>
+      <c r="U51" s="51"/>
+      <c r="V51" s="51"/>
+      <c r="W51" s="51"/>
+      <c r="X51" s="51"/>
+      <c r="Y51" s="51"/>
+      <c r="Z51" s="51"/>
+      <c r="AA51" s="51"/>
+      <c r="AB51" s="51"/>
+      <c r="AC51" s="51"/>
+      <c r="AD51" s="51"/>
+      <c r="AE51" s="51"/>
+      <c r="AF51" s="51"/>
+      <c r="AG51" s="51"/>
+      <c r="AH51" s="51"/>
+      <c r="AI51" s="51"/>
+      <c r="AJ51" s="51"/>
       <c r="AK51" s="54"/>
       <c r="BA51" s="53"/>
     </row>
-    <row r="52" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A52" s="55"/>
-      <c r="B52" s="54"/>
-      <c r="C52" s="54"/>
-      <c r="D52" s="54"/>
-      <c r="E52" s="54"/>
-      <c r="F52" s="54"/>
-      <c r="G52" s="54"/>
-      <c r="H52" s="54"/>
-      <c r="I52" s="54"/>
-      <c r="J52" s="54"/>
-      <c r="K52" s="54"/>
-      <c r="L52" s="54"/>
-      <c r="M52" s="54"/>
-      <c r="N52" s="54"/>
-      <c r="O52" s="54"/>
-      <c r="P52" s="54"/>
-      <c r="Q52" s="54"/>
-      <c r="R52" s="54"/>
-      <c r="S52" s="54"/>
-      <c r="T52" s="54"/>
-      <c r="U52" s="54"/>
-      <c r="V52" s="54"/>
-      <c r="W52" s="54"/>
-      <c r="X52" s="54"/>
-      <c r="Y52" s="54"/>
-      <c r="Z52" s="54"/>
-      <c r="AA52" s="54"/>
-      <c r="AB52" s="54"/>
-      <c r="AC52" s="54"/>
-      <c r="AD52" s="54"/>
-      <c r="AE52" s="54"/>
-      <c r="AF52" s="54"/>
-      <c r="AG52" s="54"/>
-      <c r="AH52" s="54"/>
-      <c r="AI52" s="54"/>
-      <c r="AJ52" s="54"/>
-      <c r="AK52" s="54"/>
-      <c r="BA52" s="53"/>
+    <row r="52" spans="1:53" ht="18" customHeight="1">
+      <c r="A52" s="204" t="s">
+        <v>90</v>
+      </c>
+      <c r="B52" s="205"/>
+      <c r="C52" s="205"/>
+      <c r="D52" s="205"/>
+      <c r="E52" s="205"/>
+      <c r="F52" s="205"/>
+      <c r="G52" s="205"/>
+      <c r="H52" s="205"/>
+      <c r="I52" s="205"/>
+      <c r="J52" s="205"/>
+      <c r="K52" s="205"/>
+      <c r="L52" s="205"/>
+      <c r="M52" s="205"/>
+      <c r="N52" s="205"/>
+      <c r="O52" s="205"/>
+      <c r="P52" s="205"/>
+      <c r="Q52" s="205"/>
+      <c r="R52" s="205"/>
+      <c r="S52" s="205"/>
+      <c r="T52" s="205"/>
+      <c r="U52" s="205"/>
+      <c r="V52" s="205"/>
+      <c r="W52" s="205"/>
+      <c r="X52" s="205"/>
+      <c r="Y52" s="205"/>
+      <c r="Z52" s="205"/>
+      <c r="AA52" s="205"/>
+      <c r="AB52" s="205"/>
+      <c r="AC52" s="205"/>
+      <c r="AD52" s="205"/>
+      <c r="AE52" s="205"/>
+      <c r="AF52" s="205"/>
+      <c r="AG52" s="205"/>
+      <c r="AH52" s="205"/>
+      <c r="AI52" s="205"/>
+      <c r="AJ52" s="205"/>
+      <c r="AK52" s="205"/>
+      <c r="AL52" s="205"/>
+      <c r="AM52" s="205"/>
+      <c r="AN52" s="205"/>
+      <c r="AO52" s="205"/>
+      <c r="AP52" s="205"/>
+      <c r="AQ52" s="205"/>
+      <c r="AR52" s="205"/>
+      <c r="AS52" s="205"/>
+      <c r="AT52" s="205"/>
+      <c r="AU52" s="205"/>
+      <c r="AV52" s="205"/>
+      <c r="AW52" s="205"/>
+      <c r="AX52" s="205"/>
+      <c r="AY52" s="205"/>
+      <c r="AZ52" s="205"/>
+      <c r="BA52" s="205"/>
     </row>
     <row r="53" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A53" s="55"/>
-      <c r="B53" s="54"/>
-      <c r="C53" s="54"/>
-      <c r="D53" s="54"/>
-      <c r="E53" s="54"/>
-      <c r="F53" s="54"/>
-      <c r="G53" s="54"/>
-      <c r="H53" s="54"/>
-      <c r="I53" s="54"/>
-      <c r="J53" s="54"/>
-      <c r="K53" s="54"/>
-      <c r="L53" s="54"/>
-      <c r="M53" s="54"/>
-      <c r="N53" s="54"/>
-      <c r="O53" s="54"/>
-      <c r="P53" s="54"/>
-      <c r="Q53" s="54"/>
-      <c r="R53" s="54"/>
-      <c r="S53" s="54"/>
-      <c r="T53" s="54"/>
-      <c r="U53" s="54"/>
-      <c r="V53" s="54"/>
-      <c r="W53" s="54"/>
-      <c r="X53" s="54"/>
-      <c r="Y53" s="54"/>
-      <c r="Z53" s="54"/>
-      <c r="AA53" s="54"/>
-      <c r="AB53" s="54"/>
-      <c r="AC53" s="54"/>
-      <c r="AD53" s="54"/>
-      <c r="AE53" s="54"/>
-      <c r="AF53" s="54"/>
-      <c r="AG53" s="54"/>
-      <c r="AH53" s="54"/>
-      <c r="AI53" s="54"/>
-      <c r="AJ53" s="54"/>
+      <c r="A53" s="57"/>
+      <c r="B53" s="56"/>
+      <c r="C53" s="56"/>
+      <c r="D53" s="56"/>
+      <c r="E53" s="56"/>
+      <c r="F53" s="56"/>
+      <c r="G53" s="56"/>
+      <c r="H53" s="56"/>
+      <c r="I53" s="56"/>
+      <c r="J53" s="56"/>
+      <c r="K53" s="56"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="56"/>
+      <c r="N53" s="56"/>
+      <c r="O53" s="56"/>
+      <c r="P53" s="56"/>
+      <c r="Q53" s="56"/>
+      <c r="R53" s="56"/>
+      <c r="S53" s="56"/>
+      <c r="T53" s="56"/>
+      <c r="U53" s="56"/>
+      <c r="V53" s="56"/>
+      <c r="W53" s="56"/>
+      <c r="X53" s="56"/>
+      <c r="Y53" s="56"/>
+      <c r="Z53" s="56"/>
+      <c r="AA53" s="56"/>
+      <c r="AB53" s="56"/>
+      <c r="AC53" s="56"/>
+      <c r="AD53" s="56"/>
+      <c r="AE53" s="56"/>
+      <c r="AF53" s="56"/>
+      <c r="AG53" s="56"/>
+      <c r="AH53" s="56"/>
+      <c r="AI53" s="56"/>
+      <c r="AJ53" s="56"/>
       <c r="AK53" s="54"/>
       <c r="BA53" s="53"/>
     </row>
@@ -15458,206 +15439,29 @@
       <c r="AH55" s="51"/>
       <c r="AI55" s="51"/>
       <c r="AJ55" s="51"/>
-      <c r="AK55" s="54"/>
-      <c r="BA55" s="53"/>
-    </row>
-    <row r="56" spans="1:53" ht="18" customHeight="1">
-      <c r="A56" s="204" t="s">
-        <v>90</v>
-      </c>
-      <c r="B56" s="205"/>
-      <c r="C56" s="205"/>
-      <c r="D56" s="205"/>
-      <c r="E56" s="205"/>
-      <c r="F56" s="205"/>
-      <c r="G56" s="205"/>
-      <c r="H56" s="205"/>
-      <c r="I56" s="205"/>
-      <c r="J56" s="205"/>
-      <c r="K56" s="205"/>
-      <c r="L56" s="205"/>
-      <c r="M56" s="205"/>
-      <c r="N56" s="205"/>
-      <c r="O56" s="205"/>
-      <c r="P56" s="205"/>
-      <c r="Q56" s="205"/>
-      <c r="R56" s="205"/>
-      <c r="S56" s="205"/>
-      <c r="T56" s="205"/>
-      <c r="U56" s="205"/>
-      <c r="V56" s="205"/>
-      <c r="W56" s="205"/>
-      <c r="X56" s="205"/>
-      <c r="Y56" s="205"/>
-      <c r="Z56" s="205"/>
-      <c r="AA56" s="205"/>
-      <c r="AB56" s="205"/>
-      <c r="AC56" s="205"/>
-      <c r="AD56" s="205"/>
-      <c r="AE56" s="205"/>
-      <c r="AF56" s="205"/>
-      <c r="AG56" s="205"/>
-      <c r="AH56" s="205"/>
-      <c r="AI56" s="205"/>
-      <c r="AJ56" s="205"/>
-      <c r="AK56" s="205"/>
-      <c r="AL56" s="205"/>
-      <c r="AM56" s="205"/>
-      <c r="AN56" s="205"/>
-      <c r="AO56" s="205"/>
-      <c r="AP56" s="205"/>
-      <c r="AQ56" s="205"/>
-      <c r="AR56" s="205"/>
-      <c r="AS56" s="205"/>
-      <c r="AT56" s="205"/>
-      <c r="AU56" s="205"/>
-      <c r="AV56" s="205"/>
-      <c r="AW56" s="205"/>
-      <c r="AX56" s="205"/>
-      <c r="AY56" s="205"/>
-      <c r="AZ56" s="205"/>
-      <c r="BA56" s="205"/>
-    </row>
-    <row r="57" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A57" s="57"/>
-      <c r="B57" s="56"/>
-      <c r="C57" s="56"/>
-      <c r="D57" s="56"/>
-      <c r="E57" s="56"/>
-      <c r="F57" s="56"/>
-      <c r="G57" s="56"/>
-      <c r="H57" s="56"/>
-      <c r="I57" s="56"/>
-      <c r="J57" s="56"/>
-      <c r="K57" s="56"/>
-      <c r="L57" s="56"/>
-      <c r="M57" s="56"/>
-      <c r="N57" s="56"/>
-      <c r="O57" s="56"/>
-      <c r="P57" s="56"/>
-      <c r="Q57" s="56"/>
-      <c r="R57" s="56"/>
-      <c r="S57" s="56"/>
-      <c r="T57" s="56"/>
-      <c r="U57" s="56"/>
-      <c r="V57" s="56"/>
-      <c r="W57" s="56"/>
-      <c r="X57" s="56"/>
-      <c r="Y57" s="56"/>
-      <c r="Z57" s="56"/>
-      <c r="AA57" s="56"/>
-      <c r="AB57" s="56"/>
-      <c r="AC57" s="56"/>
-      <c r="AD57" s="56"/>
-      <c r="AE57" s="56"/>
-      <c r="AF57" s="56"/>
-      <c r="AG57" s="56"/>
-      <c r="AH57" s="56"/>
-      <c r="AI57" s="56"/>
-      <c r="AJ57" s="56"/>
-      <c r="AK57" s="54"/>
-      <c r="BA57" s="53"/>
-    </row>
-    <row r="58" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A58" s="55"/>
-      <c r="B58" s="54"/>
-      <c r="C58" s="54"/>
-      <c r="D58" s="54"/>
-      <c r="E58" s="54"/>
-      <c r="F58" s="54"/>
-      <c r="G58" s="54"/>
-      <c r="H58" s="54"/>
-      <c r="I58" s="54"/>
-      <c r="J58" s="54"/>
-      <c r="K58" s="54"/>
-      <c r="L58" s="54"/>
-      <c r="M58" s="54"/>
-      <c r="N58" s="54"/>
-      <c r="O58" s="54"/>
-      <c r="P58" s="54"/>
-      <c r="Q58" s="54"/>
-      <c r="R58" s="54"/>
-      <c r="S58" s="54"/>
-      <c r="T58" s="54"/>
-      <c r="U58" s="54"/>
-      <c r="V58" s="54"/>
-      <c r="W58" s="54"/>
-      <c r="X58" s="54"/>
-      <c r="Y58" s="54"/>
-      <c r="Z58" s="54"/>
-      <c r="AA58" s="54"/>
-      <c r="AB58" s="54"/>
-      <c r="AC58" s="54"/>
-      <c r="AD58" s="54"/>
-      <c r="AE58" s="54"/>
-      <c r="AF58" s="54"/>
-      <c r="AG58" s="54"/>
-      <c r="AH58" s="54"/>
-      <c r="AI58" s="54"/>
-      <c r="AJ58" s="54"/>
-      <c r="AK58" s="54"/>
-      <c r="BA58" s="53"/>
-    </row>
-    <row r="59" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A59" s="52"/>
-      <c r="B59" s="51"/>
-      <c r="C59" s="51"/>
-      <c r="D59" s="51"/>
-      <c r="E59" s="51"/>
-      <c r="F59" s="51"/>
-      <c r="G59" s="51"/>
-      <c r="H59" s="51"/>
-      <c r="I59" s="51"/>
-      <c r="J59" s="51"/>
-      <c r="K59" s="51"/>
-      <c r="L59" s="51"/>
-      <c r="M59" s="51"/>
-      <c r="N59" s="51"/>
-      <c r="O59" s="51"/>
-      <c r="P59" s="51"/>
-      <c r="Q59" s="51"/>
-      <c r="R59" s="51"/>
-      <c r="S59" s="51"/>
-      <c r="T59" s="51"/>
-      <c r="U59" s="51"/>
-      <c r="V59" s="51"/>
-      <c r="W59" s="51"/>
-      <c r="X59" s="51"/>
-      <c r="Y59" s="51"/>
-      <c r="Z59" s="51"/>
-      <c r="AA59" s="51"/>
-      <c r="AB59" s="51"/>
-      <c r="AC59" s="51"/>
-      <c r="AD59" s="51"/>
-      <c r="AE59" s="51"/>
-      <c r="AF59" s="51"/>
-      <c r="AG59" s="51"/>
-      <c r="AH59" s="51"/>
-      <c r="AI59" s="51"/>
-      <c r="AJ59" s="51"/>
-      <c r="AK59" s="51"/>
-      <c r="AL59" s="50"/>
-      <c r="AM59" s="50"/>
-      <c r="AN59" s="50"/>
-      <c r="AO59" s="50"/>
-      <c r="AP59" s="50"/>
-      <c r="AQ59" s="50"/>
-      <c r="AR59" s="50"/>
-      <c r="AS59" s="50"/>
-      <c r="AT59" s="50"/>
-      <c r="AU59" s="50"/>
-      <c r="AV59" s="50"/>
-      <c r="AW59" s="50"/>
-      <c r="AX59" s="50"/>
-      <c r="AY59" s="50"/>
-      <c r="AZ59" s="50"/>
-      <c r="BA59" s="49"/>
+      <c r="AK55" s="51"/>
+      <c r="AL55" s="50"/>
+      <c r="AM55" s="50"/>
+      <c r="AN55" s="50"/>
+      <c r="AO55" s="50"/>
+      <c r="AP55" s="50"/>
+      <c r="AQ55" s="50"/>
+      <c r="AR55" s="50"/>
+      <c r="AS55" s="50"/>
+      <c r="AT55" s="50"/>
+      <c r="AU55" s="50"/>
+      <c r="AV55" s="50"/>
+      <c r="AW55" s="50"/>
+      <c r="AX55" s="50"/>
+      <c r="AY55" s="50"/>
+      <c r="AZ55" s="50"/>
+      <c r="BA55" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A9:BA9"/>
-    <mergeCell ref="A47:BA47"/>
-    <mergeCell ref="A56:BA56"/>
+    <mergeCell ref="A43:BA43"/>
+    <mergeCell ref="A52:BA52"/>
     <mergeCell ref="AT1:BA1"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:S5"/>
@@ -15667,7 +15471,7 @@
   </mergeCells>
   <phoneticPr fontId="8"/>
   <dataValidations count="2">
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1:O1 I1:L1 A57:AK59 G5:G6 V1 AC1 AE1 A48:AK55 A10:AK46" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1:O1 I1:L1 A53:AK55 G5:G6 V1 AC1 AE1 A44:AK51 A10:AK42" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
     <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO1:AS1" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
